--- a/data/credit_bond_all_2026-09-07.xlsx
+++ b/data/credit_bond_all_2026-09-07.xlsx
@@ -159,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ42"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.1700/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -1524,7 +1524,11 @@
           <t>09-07 18:00</t>
         </is>
       </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>102683546.IB</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -1748,7 +1752,11 @@
           <t>09-07 18:00</t>
         </is>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>102683545.IB</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -1972,7 +1980,11 @@
           <t>09-07 18:00</t>
         </is>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>012682212.IB</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
           <t>0.31Y</t>
@@ -2011,7 +2023,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4700/--</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -2192,7 +2204,11 @@
           <t>09-07 18:00</t>
         </is>
       </c>
-      <c r="C10" s="3"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>012682214.IB</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t>0.33Y</t>
@@ -2231,7 +2247,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5100/1.4700</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -2399,7 +2415,9 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AZ10" s="3"/>
+      <c r="AZ10" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
@@ -2412,7 +2430,11 @@
           <t>09-07 18:00</t>
         </is>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>102683540.IB</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>3+2</t>
@@ -2451,7 +2473,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7200/--</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -2632,7 +2654,11 @@
           <t>09-07 18:00</t>
         </is>
       </c>
-      <c r="C12" s="3"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>012682213.IB</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t>0.24Y</t>
@@ -2671,7 +2697,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5100/1.3992</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -2852,7 +2878,11 @@
           <t>09-07 18:00</t>
         </is>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>102683544.IB</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
           <t>3+2</t>
@@ -2891,7 +2921,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.6700</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -3076,7 +3106,11 @@
           <t>09-07 18:00</t>
         </is>
       </c>
-      <c r="C14" s="3"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>102683542.IB</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t>30Y</t>
@@ -3115,7 +3149,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.3800/2.3500</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -3283,7 +3317,9 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AZ14" s="3"/>
+      <c r="AZ14" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
@@ -3339,7 +3375,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9900/1.9300</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -3563,7 +3599,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6900</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -3682,7 +3718,7 @@
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>其它</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP16" s="3" t="inlineStr">
@@ -3791,7 +3827,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.2000/2.1400</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -4431,7 +4467,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.3900/2.0900</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -4887,7 +4923,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8700/1.8600</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -5932,7 +5968,11 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C27" s="3"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>102683547.IB</t>
+        </is>
+      </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
           <t>2Y</t>
@@ -6148,7 +6188,7 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26义乌农商三农债01A</t>
+          <t>26黄发04</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6156,41 +6196,45 @@
           <t>09-07 18:00</t>
         </is>
       </c>
-      <c r="C28" s="3"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>283938.SH</t>
+        </is>
+      </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.0</v>
+        <v>6.75</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>24义乌农商三农债02</t>
+          <t>26黄发01</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>1.23Y</t>
+          <t>4.51Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.5344</t>
+          <t>2.1094</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -6200,12 +6244,12 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>浙江义乌农村商业银行股份有限公司</t>
+          <t>黄石市城市发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>D 4.33</t>
+          <t>B- 37.25</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6215,7 +6259,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -6225,7 +6269,7 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U28" s="3"/>
@@ -6237,7 +6281,7 @@
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>2.19%~2.29%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -6245,62 +6289,54 @@
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z28" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+      <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
+          <t>湖北省-黄石市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金将依据适用法律和监管部门的批准用于发放涉农贷款</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金[26黄发D2,26黄发D1]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>西部证券股份有限公司,华源证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>2026年浙江义乌农村商业银行股份有限公司"三农"专项金融债券(品种一)</t>
+          <t>黄石市城市发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK28" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-08</t>
+        </is>
+      </c>
+      <c r="AK28" s="3"/>
       <c r="AL28" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6308,17 +6344,17 @@
       </c>
       <c r="AM28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
@@ -6328,22 +6364,22 @@
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>农商行</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6376,7 +6412,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26川高速SCP001</t>
+          <t>26横琴Y3</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6386,60 +6422,58 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>012682211.IB</t>
+          <t>283861.SH</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>11.0</v>
+      </c>
+      <c r="F29" s="3"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>21川高速MTN008</t>
+          <t>26横琴Y2</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>80D</t>
+          <t>2.89Y+N</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.4955</t>
+          <t>1.9307</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9400/1.9000</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>四川高速公路建设开发集团有限公司</t>
+          <t>珠海大横琴集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C- 19.79</t>
+          <t>B- 38.95</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6449,7 +6483,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6459,19 +6493,19 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6482,23 +6516,23 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>广东省-珠海市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具拟募集资金10亿元,拟全部用于偿付到期债务融资工具【21川高速MTN007】</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司有息债务。</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>招商证券股份有限公司,国金证券股份有限公司,华泰联合证券有限责任公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6508,40 +6542,44 @@
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>四川高速公路建设开发集团有限公司2026年度第一期超短期融资券</t>
+          <t>珠海大横琴集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
-        </is>
-      </c>
-      <c r="AK29" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK29" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL29" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AM29" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
           <t>类城投</t>
@@ -6559,17 +6597,17 @@
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6584,7 +6622,7 @@
       </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX29" s="3" t="inlineStr">
@@ -6602,7 +6640,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26核保02</t>
+          <t>26义乌农商三农债01A</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6610,45 +6648,41 @@
           <t>09-07 18:00</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>246006.SH</t>
-        </is>
-      </c>
+      <c r="C30" s="3"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26核保01</t>
+          <t>24义乌农商三农债02</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>1.36Y</t>
+          <t>1.23Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.9037</t>
+          <t>1.5344</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -6658,12 +6692,12 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>中核商业保理有限公司</t>
+          <t>浙江义乌农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>D+ 6.12</t>
+          <t>D 4.33</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6673,7 +6707,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -6683,19 +6717,19 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -6703,41 +6737,45 @@
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z30" s="3"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江省-金华市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金5亿元拟用于偿还有息债务</t>
+          <t>本期债券募集资金将依据适用法律和监管部门的批准用于发放涉农贷款</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>招商证券股份有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>中核商业保理有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>2026年浙江义乌农村商业银行股份有限公司"三农"专项金融债券(品种一)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -6747,10 +6785,14 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2028-09-08</t>
-        </is>
-      </c>
-      <c r="AK30" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK30" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL30" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6758,12 +6800,12 @@
       </c>
       <c r="AM30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AN30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO30" s="3" t="inlineStr">
@@ -6771,25 +6813,29 @@
           <t>金融</t>
         </is>
       </c>
-      <c r="AP30" s="3"/>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>保理</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>保理</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -6822,70 +6868,70 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26沈阳地铁MTN004</t>
+          <t>26川高速SCP001</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>09-08 18:00</t>
+          <t>09-07 18:00</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>102683539.IB</t>
+          <t>012682211.IB</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.70</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>24沈阳地铁MTN006B</t>
+          <t>21川高速MTN008</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>4.95Y+N</t>
+          <t>80D</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>2.3235</t>
+          <t>1.4955</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5000/--</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>沈阳地铁集团有限公司</t>
+          <t>四川高速公路建设开发集团有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.71</t>
+          <t>C- 19.79</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -6905,19 +6951,19 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>2.22%~2.32%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -6925,30 +6971,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z31" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>辽宁省-沈阳市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为人民币0亿元,发行金额上限为人民币15亿元,本次债券募集资金拟用于偿还公司有息债务。[24沈阳地铁MTN007,25沈阳地铁MTN004]</t>
+          <t>发行人本期债务融资工具拟募集资金10亿元,拟全部用于偿付到期债务融资工具【21川高速MTN007】</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>中国邮政储蓄银行股份有限公司,光大证券股份有限公司</t>
+          <t>中国光大银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
@@ -6963,7 +7005,7 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>沈阳地铁集团有限公司2026年度第四期中期票据</t>
+          <t>四川高速公路建设开发集团有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -6973,13 +7015,13 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM31" s="3" t="inlineStr">
@@ -6989,17 +7031,17 @@
       </c>
       <c r="AN31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
@@ -7009,17 +7051,17 @@
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7034,7 +7076,7 @@
       </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX31" s="3" t="inlineStr">
@@ -7044,7 +7086,7 @@
       </c>
       <c r="AY31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AZ31" s="3"/>
@@ -7052,7 +7094,7 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>义乌KY02</t>
+          <t>26核保02</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7062,12 +7104,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>282563.SH</t>
+          <t>246006.SH</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
@@ -7076,44 +7118,44 @@
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26义乌Y1</t>
+          <t>26核保01</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2.73Y+N</t>
+          <t>1.36Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.7852</t>
+          <t>1.9037</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>1.8200/--</t>
+          <t>1.9900/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>义乌市国有资本运营有限公司</t>
+          <t>中核商业保理有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>B- 35.53</t>
+          <t>D+ 6.12</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7140,37 +7182,33 @@
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.91%~2.01%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过5亿元(含5亿元),拟将募集资金不低于70%通过基金出资用于支持科技创新领域发展(含置换发行前12个月内用于支持科技创新领域发展的基金出资),剩余不超过30%用于偿还到期债务。</t>
+          <t>本期债券募集资金5亿元拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
@@ -7181,7 +7219,7 @@
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
@@ -7191,17 +7229,17 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>义乌市国有资本运营有限公司2026年面向专业投资者非公开发行科技创新可续期公司债券(第一期)</t>
+          <t>中核商业保理有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
+          <t>2028-09-08</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
@@ -7222,32 +7260,28 @@
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP32" s="3"/>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>保理</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>保理</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7262,12 +7296,12 @@
       </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX32" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY32" s="3" t="inlineStr">
@@ -7280,70 +7314,70 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26厦门产投MTN003(科创债)</t>
+          <t>26沈阳地铁MTN004</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-08 18:00</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>102683466.IB</t>
+          <t>102683539.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>2.00 ~ 2.70</t>
         </is>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26厦门产投MTN002(科创债)</t>
+          <t>24沈阳地铁MTN006B</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>4.95Y+N</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.8952</t>
+          <t>2.3235</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.2400</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>厦门市产业投资有限公司</t>
+          <t>沈阳地铁集团有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>A 75.38</t>
+          <t>C+ 30.71</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7353,7 +7387,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>09-07 11:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -7363,7 +7397,7 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U33" s="3"/>
@@ -7375,7 +7409,7 @@
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>2.22%~2.32%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -7390,17 +7424,17 @@
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>辽宁省-沈阳市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债券发行金额为5亿元，本期发行的募集资金扣除承销费后，拟全部用于科技创新领域股权投资以及置换发行人本期科技创新债券发行之日起一年以内科技创新领域股权投资；本期债券募集资金中5亿元拟用于对中创新航科技（福建）有限公司的科技创新领域股权投资以及置换一年之内的自有资金投入。</t>
+          <t>本期中期票据基础发行规模为人民币0亿元,发行金额上限为人民币15亿元,本次债券募集资金拟用于偿还公司有息债务。[24沈阳地铁MTN007,25沈阳地铁MTN004]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,厦门银行股份有限公司</t>
+          <t>中国邮政储蓄银行股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
@@ -7421,7 +7455,7 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>厦门市产业投资有限公司2026年度第三期科技创新债券</t>
+          <t>沈阳地铁集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7431,74 +7465,78 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
+          <t>2031-09-09</t>
         </is>
       </c>
       <c r="AK33" s="3"/>
       <c r="AL33" s="3" t="inlineStr">
         <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AM33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AN33" s="3" t="inlineStr">
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>铁路运输</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AX33" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY33" s="3" t="inlineStr">
         <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AO33" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP33" s="3"/>
-      <c r="AQ33" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR33" s="3" t="inlineStr">
-        <is>
-          <t>其他非银</t>
-        </is>
-      </c>
-      <c r="AS33" s="3" t="inlineStr">
-        <is>
-          <t>其他非银</t>
-        </is>
-      </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU33" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV33" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW33" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX33" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AZ33" s="3"/>
@@ -7506,7 +7544,7 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26金融街MTN005A</t>
+          <t>义乌KY02</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7514,56 +7552,60 @@
           <t>09-07 18:00</t>
         </is>
       </c>
-      <c r="C34" s="3"/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>282563.SH</t>
+        </is>
+      </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>2+2</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.3</v>
+        <v>5.0</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2.05 ~ 2.75</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26金融街MTN004A</t>
+          <t>26义乌Y1</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>1.93Y+2.00Y</t>
+          <t>2.73Y+N</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>2.5181</t>
+          <t>1.7852</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8000/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司</t>
+          <t>义乌市国有资本运营有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C- 22.82</t>
+          <t>B- 35.53</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7573,7 +7615,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>09-07 14:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -7590,12 +7632,12 @@
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>2.54%~2.64%</t>
+          <t>1.91%~2.01%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -7610,23 +7652,23 @@
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江省-金华市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为0亿元，发行规模上限为10.30亿元，拟将募集资金全部用于偿还发行人债务融资工具的本金和利息[23金融街MTN006]</t>
+          <t>本期债券发行规模不超过5亿元(含5亿元),拟将募集资金不低于70%通过基金出资用于支持科技创新领域发展(含置换发行前12个月内用于支持科技创新领域发展的基金出资),剩余不超过30%用于偿还到期债务。</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -7636,37 +7678,33 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司2026年度第五期中期票据(品种一)</t>
+          <t>义乌市国有资本运营有限公司2026年面向专业投资者非公开发行科技创新可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2030-09-08</t>
-        </is>
-      </c>
-      <c r="AK34" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-08</t>
+        </is>
+      </c>
+      <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t/>
         </is>
       </c>
       <c r="AM34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AN34" s="3" t="inlineStr">
@@ -7676,37 +7714,37 @@
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>住宅楼房</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
         <is>
-          <t>2028-09-08</t>
+          <t/>
         </is>
       </c>
       <c r="AV34" s="3" t="inlineStr">
@@ -7716,12 +7754,12 @@
       </c>
       <c r="AW34" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX34" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY34" s="3" t="inlineStr">
@@ -7734,7 +7772,7 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26扬子G6</t>
+          <t>26厦门产投MTN003(科创债)</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -7744,7 +7782,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>246021.SH</t>
+          <t>102683466.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -7753,49 +7791,51 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="F35" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>26扬子G4</t>
+          <t>26厦门产投MTN002(科创债)</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>4.97Y</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.7379</t>
+          <t>1.8952</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8700</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>南京扬子国资投资集团有限责任公司</t>
+          <t>厦门市产业投资有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C 25.89</t>
+          <t>A 75.38</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -7805,7 +7845,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 11:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -7815,19 +7855,19 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -7835,26 +7875,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z35" s="3"/>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本次债券募集资金用途为偿还到期的公司债券本金[23扬子G3]</t>
+          <t>本期科技创新债券发行金额为5亿元，本期发行的募集资金扣除承销费后，拟全部用于科技创新领域股权投资以及置换发行人本期科技创新债券发行之日起一年以内科技创新领域股权投资；本期债券募集资金中5亿元拟用于对中创新航科技（福建）有限公司的科技创新领域股权投资以及置换一年之内的自有资金投入。</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,国开证券股份有限公司,广发证券股份有限公司</t>
+          <t>兴业银行股份有限公司,厦门银行股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
@@ -7864,12 +7908,12 @@
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>南京扬子国资投资集团有限责任公司2026年面向专业投资者公开发行公司债券(第三期)(品种二)</t>
+          <t>厦门市产业投资有限公司2026年度第三期科技创新债券</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -7879,13 +7923,13 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
+          <t>2031-09-08</t>
         </is>
       </c>
       <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM35" s="3" t="inlineStr">
@@ -7895,37 +7939,33 @@
       </c>
       <c r="AN35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP35" s="3"/>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -7958,7 +7998,7 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26扬子G5</t>
+          <t>26金融街MTN005A</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -7968,58 +8008,58 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>246020.SH</t>
+          <t>102683543.IB</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2+2</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>6.0</v>
+        <v>5.3</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>2.05 ~ 2.75</t>
         </is>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26扬子G3</t>
+          <t>26金融街MTN004A</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>1.93Y+2.00Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.6669</t>
+          <t>2.5181</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.4800</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>南京扬子国资投资集团有限责任公司</t>
+          <t>金融街控股股份有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C 25.89</t>
+          <t>C- 22.82</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8029,7 +8069,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 14:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8039,19 +8079,19 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>2.54%~2.64%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -8059,26 +8099,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z36" s="3"/>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本次债券募集资金用途为偿还到期的公司债券本金[23扬子G3]</t>
+          <t>本期中期票据基础发行规模为0亿元，发行规模上限为10.30亿元，拟将募集资金全部用于偿还发行人债务融资工具的本金和利息[23金融街MTN006]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,国开证券股份有限公司,广发证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
@@ -8088,12 +8132,12 @@
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>南京扬子国资投资集团有限责任公司2026年面向专业投资者公开发行公司债券(第三期)(品种一)</t>
+          <t>金融街控股股份有限公司2026年度第五期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8103,7 +8147,7 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
+          <t>2030-09-08</t>
         </is>
       </c>
       <c r="AK36" s="3" t="inlineStr">
@@ -8113,7 +8157,7 @@
       </c>
       <c r="AL36" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM36" s="3" t="inlineStr">
@@ -8123,12 +8167,12 @@
       </c>
       <c r="AN36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
@@ -8138,27 +8182,27 @@
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>住宅楼房</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2028-09-08</t>
         </is>
       </c>
       <c r="AV36" s="3" t="inlineStr">
@@ -8168,7 +8212,7 @@
       </c>
       <c r="AW36" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX36" s="3" t="inlineStr">
@@ -8186,7 +8230,7 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26海兴01</t>
+          <t>26扬子G6</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8196,7 +8240,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>283921.SH</t>
+          <t>246021.SH</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -8205,49 +8249,49 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.50</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>25海兴09</t>
+          <t>26扬子G4</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>4.28Y</t>
+          <t>4.97Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>2.0053</t>
+          <t>1.7379</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8000/1.7700</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>盐城市海兴集团有限公司</t>
+          <t>南京扬子国资投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C- 16.75</t>
+          <t>C 25.89</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8267,40 +8311,40 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>2.06%~2.16%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>江苏省-盐城市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还回售的公司债券本金[23海兴02]</t>
+          <t>本次债券募集资金用途为偿还到期的公司债券本金[23扬子G3]</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,中邮证券有限责任公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,国开证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
@@ -8321,17 +8365,17 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>盐城市海兴集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>南京扬子国资投资集团有限责任公司2026年面向专业投资者公开发行公司债券(第三期)(品种二)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
+          <t>2031-09-09</t>
         </is>
       </c>
       <c r="AK37" s="3"/>
@@ -8347,22 +8391,34 @@
       </c>
       <c r="AN37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ37" s="3"/>
-      <c r="AR37" s="3"/>
-      <c r="AS37" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
           <t>基础建设</t>
@@ -8398,7 +8454,7 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26西投K2</t>
+          <t>26扬子G5</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8408,7 +8464,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>283804.SH</t>
+          <t>246020.SH</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -8417,49 +8473,49 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>2.5</v>
+        <v>6.0</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.30</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>26西投01</t>
+          <t>26扬子G3</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>2.3754</t>
+          <t>1.6669</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6900/1.6600</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>西安投资控股有限公司</t>
+          <t>南京扬子国资投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C- 23.16</t>
+          <t>C 25.89</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8486,33 +8542,33 @@
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.96%~2.06%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金扣除相关发行费用后,拟将不低于70%募集资金用于置换前12个月内科技创新领域的基金出资款,剩余部分用于偿还有息债务</t>
+          <t>本次债券募集资金用途为偿还到期的公司债券本金[23扬子G3]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国投证券股份有限公司,首创证券股份有限公司,开源证券股份有限公司,联储证券股份有限公司,国金证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,国开证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
@@ -8533,12 +8589,12 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>西安投资控股有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)(品种一)</t>
+          <t>南京扬子国资投资集团有限责任公司2026年面向专业投资者公开发行公司债券(第三期)(品种一)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
@@ -8568,7 +8624,7 @@
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
@@ -8578,22 +8634,22 @@
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -8626,7 +8682,7 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26西投K3</t>
+          <t>26海兴01</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8636,7 +8692,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>283805.SH</t>
+          <t>283921.SH</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -8645,7 +8701,7 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>2.5</v>
+        <v>5.0</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="inlineStr">
@@ -8657,22 +8713,22 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26西投K1</t>
+          <t>25海兴09</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>4.90Y</t>
+          <t>4.28Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>2.3695</t>
+          <t>2.0053</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -8682,12 +8738,12 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>西安投资控股有限公司</t>
+          <t>盐城市海兴集团有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 23.16</t>
+          <t>C- 16.75</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -8707,19 +8763,19 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>2.14%~2.24%</t>
+          <t>2.06%~2.16%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
@@ -8730,17 +8786,17 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金扣除相关发行费用后,拟将不低于70%募集资金用于置换前12个月内科技创新领域的基金出资款,剩余部分用于偿还有息债务</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还回售的公司债券本金[23海兴02]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国投证券股份有限公司,首创证券股份有限公司,开源证券股份有限公司,联储证券股份有限公司,国金证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,中邮证券有限责任公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
@@ -8761,7 +8817,7 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>西安投资控股有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)(品种二)</t>
+          <t>盐城市海兴集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -8771,7 +8827,7 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
+          <t>2031-09-08</t>
         </is>
       </c>
       <c r="AK39" s="3"/>
@@ -8787,37 +8843,25 @@
       </c>
       <c r="AN39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ39" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR39" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS39" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ39" s="3"/>
+      <c r="AR39" s="3"/>
+      <c r="AS39" s="3"/>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -8850,7 +8894,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26徐经01</t>
+          <t>26西投K2</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -8860,58 +8904,58 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>283791.SH</t>
+          <t>283804.SH</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>13.0</v>
+        <v>2.5</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.60 ~ 2.30</t>
         </is>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>24徐州经开PPN002</t>
+          <t>26西投01</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>2.88Y</t>
+          <t>4.77Y</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.7945</t>
+          <t>2.3754</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.0900</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>徐州经济技术开发区国有资产经营有限责任公司</t>
+          <t>西安投资控股有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C 27.90</t>
+          <t>C- 23.16</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -8921,7 +8965,7 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
@@ -8943,7 +8987,7 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.99%~2.09%</t>
+          <t>1.96%~2.06%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -8954,17 +8998,17 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>江苏省-徐州市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本次公司债券募集资金扣除发行费用后,拟将13.00亿元用于偿还到期的公司债券本金。[23徐经01]</t>
+          <t>本期债券的募集资金扣除相关发行费用后,拟将不低于70%募集资金用于置换前12个月内科技创新领域的基金出资款,剩余部分用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中国国际金融股份有限公司,东吴证券股份有限公司,广发证券股份有限公司,中信证券股份有限公司</t>
+          <t>中信证券股份有限公司,国投证券股份有限公司,首创证券股份有限公司,开源证券股份有限公司,联储证券股份有限公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
@@ -8985,7 +9029,7 @@
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>徐州经济技术开发区国有资产经营有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>西安投资控股有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -8995,10 +9039,14 @@
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
-        </is>
-      </c>
-      <c r="AK40" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK40" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL40" s="3" t="inlineStr">
         <is>
           <t/>
@@ -9016,32 +9064,32 @@
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -9074,7 +9122,7 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26航港01</t>
+          <t>26西投K3</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9084,58 +9132,58 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>283909.SH</t>
+          <t>283805.SH</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>10.0</v>
+        <v>2.5</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.80 ~ 2.50</t>
         </is>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>24港投04</t>
+          <t>26西投K1</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>2.91Y</t>
+          <t>4.90Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.8312</t>
+          <t>2.3695</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>1.9100/--</t>
+          <t>--/2.3300</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>河南航空港投资集团有限公司</t>
+          <t>西安投资控股有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>B- 44.02</t>
+          <t>C- 23.16</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9145,7 +9193,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -9155,40 +9203,40 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>2.14%~2.24%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>河南省-郑州市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,将全部用于偿还到期公司债券本金[21兴港03]</t>
+          <t>本期债券的募集资金扣除相关发行费用后,拟将不低于70%募集资金用于置换前12个月内科技创新领域的基金出资款,剩余部分用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,国投证券股份有限公司,东方证券股份有限公司,平安证券股份有限公司,中国银河证券股份有限公司</t>
+          <t>中信证券股份有限公司,国投证券股份有限公司,首创证券股份有限公司,开源证券股份有限公司,联储证券股份有限公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
@@ -9209,7 +9257,7 @@
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>河南航空港投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>西安投资控股有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)(品种二)</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
@@ -9219,14 +9267,10 @@
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2029-09-08</t>
-        </is>
-      </c>
-      <c r="AK41" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-09</t>
+        </is>
+      </c>
+      <c r="AK41" s="3"/>
       <c r="AL41" s="3" t="inlineStr">
         <is>
           <t/>
@@ -9239,37 +9283,37 @@
       </c>
       <c r="AN41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP41" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU41" s="3" t="inlineStr">
@@ -9302,7 +9346,7 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26深城01</t>
+          <t>26徐经01</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -9312,58 +9356,58 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>520466.SZ</t>
+          <t>283791.SH</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>25深汕01</t>
+          <t>24徐州经开PPN002</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>1.78Y+2.00Y</t>
+          <t>2.88Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.6792</t>
+          <t>1.7945</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8200/--</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>深圳市深汕特别合作区城市建设投资发展有限公司</t>
+          <t>徐州经济技术开发区国有资产经营有限责任公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.57</t>
+          <t>C 27.90</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9373,7 +9417,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -9383,43 +9427,43 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
-      <c r="W42" s="3"/>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>5-</t>
+        </is>
+      </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.99%~2.09%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>江苏省-徐州市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还回售的公司债券本金[23深汕01]</t>
+          <t>本次公司债券募集资金扣除发行费用后,拟将13.00亿元用于偿还到期的公司债券本金。[23徐经01]</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD42" s="3" t="inlineStr">
-        <is>
-          <t>深圳市深担增信融资担保有限公司</t>
-        </is>
-      </c>
+          <t>华泰联合证券有限责任公司,中国国际金融股份有限公司,东吴证券股份有限公司,广发证券股份有限公司,中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -9432,12 +9476,12 @@
       </c>
       <c r="AG42" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>深圳市深汕特别合作区城市建设投资发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>徐州经济技术开发区国有资产经营有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
@@ -9447,7 +9491,7 @@
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
+          <t>2031-09-09</t>
         </is>
       </c>
       <c r="AK42" s="3"/>
@@ -9463,65 +9507,1425 @@
       </c>
       <c r="AN42" s="3" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX42" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AZ42" s="3"/>
+    </row>
+    <row r="43" customHeight="true" ht="18.0">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>26航港01</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>09-07 18:00</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>283909.SH</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>24港投04</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>2.91Y</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>1.8312</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>1.8400/1.8000</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>河南航空港投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>B- 44.02</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>09-07 15:00</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AO42" s="3" t="inlineStr">
+      <c r="U43" s="3"/>
+      <c r="V43" s="3"/>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>1.84%~1.94%</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z43" s="3"/>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>河南省-郑州市</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>本期债券的募集资金在扣除发行费用后,将全部用于偿还到期公司债券本金[21兴港03]</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,国投证券股份有限公司,东方证券股份有限公司,平安证券股份有限公司,中国银河证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD43" s="3"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr">
+        <is>
+          <t>河南航空港投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr">
+        <is>
+          <t>2029-09-08</t>
+        </is>
+      </c>
+      <c r="AK43" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
         <is>
           <t>类城投</t>
         </is>
       </c>
-      <c r="AP42" s="3" t="inlineStr">
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AZ43" s="3"/>
+    </row>
+    <row r="44" customHeight="true" ht="18.0">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>26深城01</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>09-07 18:00</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>520466.SZ</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>3+2</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>25深汕01</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>1.78Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>1.6792</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>深圳市深汕特别合作区城市建设投资发展有限公司</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>D+ 8.57</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>09-07 16:00</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U44" s="3"/>
+      <c r="V44" s="3"/>
+      <c r="W44" s="3"/>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>1.72%~1.82%</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z44" s="3"/>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>广东省-深圳市</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还回售的公司债券本金[23深汕01]</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr">
+        <is>
+          <t>深圳市深担增信融资担保有限公司</t>
+        </is>
+      </c>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr">
+        <is>
+          <t>深圳市深汕特别合作区城市建设投资发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-08</t>
+        </is>
+      </c>
+      <c r="AK44" s="3"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
-      <c r="AQ42" s="3" t="inlineStr">
+      <c r="AQ44" s="3" t="inlineStr">
         <is>
           <t>基础设施投融资</t>
         </is>
       </c>
-      <c r="AR42" s="3" t="inlineStr">
+      <c r="AR44" s="3" t="inlineStr">
         <is>
           <t>城市基础设施投融资建设</t>
         </is>
       </c>
-      <c r="AS42" s="3" t="inlineStr">
+      <c r="AS44" s="3" t="inlineStr">
         <is>
           <t>城市基础设施投融资建设</t>
         </is>
       </c>
-      <c r="AT42" s="3" t="inlineStr">
+      <c r="AT44" s="3" t="inlineStr">
         <is>
           <t>基础建设</t>
         </is>
       </c>
-      <c r="AU42" s="3" t="inlineStr">
+      <c r="AU44" s="3" t="inlineStr">
         <is>
           <t>2029-09-08</t>
         </is>
       </c>
-      <c r="AV42" s="3" t="inlineStr">
+      <c r="AV44" s="3" t="inlineStr">
         <is>
           <t>有担保</t>
         </is>
       </c>
-      <c r="AW42" s="3" t="inlineStr">
+      <c r="AW44" s="3" t="inlineStr">
         <is>
           <t>含权</t>
         </is>
       </c>
-      <c r="AX42" s="3" t="inlineStr">
+      <c r="AX44" s="3" t="inlineStr">
         <is>
           <t>普通债权</t>
         </is>
       </c>
-      <c r="AY42" s="3" t="inlineStr">
+      <c r="AY44" s="3" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AZ42" s="3"/>
+      <c r="AZ44" s="3"/>
+    </row>
+    <row r="45" customHeight="true" ht="18.0">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>26平经03</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>09-07 18:00</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>283879.SH</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>3+2</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>26平经02</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>2.76Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>1.7110</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>1.7600/1.6600</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>平湖经济技术开发区投资发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>D 4.80</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>09-07 16:00</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T45" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U45" s="3"/>
+      <c r="V45" s="3"/>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>7+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>1.72%~1.82%</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3"/>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>浙江省-嘉兴市</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金扣除发行费用后,公司拟将本期债券募集资金全部用于偿还公司债券本金[23平经03]</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr">
+        <is>
+          <t>平湖国发投控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr">
+        <is>
+          <t>平湖经济技术开发区投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+        </is>
+      </c>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-09</t>
+        </is>
+      </c>
+      <c r="AK45" s="3"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>6.5*无效</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AX45" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY45" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AZ45" s="3"/>
+    </row>
+    <row r="46" customHeight="true" ht="18.0">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>26建城01</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>09-07 18:00</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>283858.SH</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>26建湖城投PPN003</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>4.97Y</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>2.1973</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>--/2.1500</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>建湖县城市建设投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>D+ 8.81</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>09-07 15:00</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U46" s="3"/>
+      <c r="V46" s="3"/>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>2.15%~2.25%</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z46" s="3"/>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>江苏省-盐城市</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[24建城01,23建城03]</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>长城证券股份有限公司,东吴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD46" s="3"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr">
+        <is>
+          <t>建湖县城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="AI46" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ46" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-09</t>
+        </is>
+      </c>
+      <c r="AK46" s="3"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX46" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AZ46" s="3"/>
+    </row>
+    <row r="47" customHeight="true" ht="18.0">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>26深铁09</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>09-07 18:00</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>520467.SZ</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>26深铁07</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>2.97Y</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>1.7828</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>1.7900/1.7800</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>深圳市地铁集团有限公司</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>C+ 32.92</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>09-07 16:00</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U47" s="3"/>
+      <c r="V47" s="3"/>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>1.78%~1.88%</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>广东省-深圳市</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>本期债券发行规模不超过15亿元(含)，扣除发行费用后拟用于偿还公司有息债务[23深铁13,25深圳地铁MTN003A,25深圳地铁MTN003B,24深圳地铁MTN007A,24深圳地铁MTN007B]</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD47" s="3"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr">
+        <is>
+          <t>深圳市地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种一)</t>
+        </is>
+      </c>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr">
+        <is>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK47" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>公交</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX47" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AZ47" s="3"/>
+    </row>
+    <row r="48" customHeight="true" ht="18.0">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>26深铁10</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>09-07 18:00</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>520468.SZ</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>5+2</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>26深铁08</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>4.97Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>2.0263</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>2.1000/--</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>深圳市地铁集团有限公司</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>C+ 32.92</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>09-07 16:00</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U48" s="3"/>
+      <c r="V48" s="3"/>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>1.98%~2.08%</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z48" s="3"/>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>广东省-深圳市</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>本期债券发行规模不超过15亿元(含)，扣除发行费用后拟用于偿还公司有息债务[23深铁13,25深圳地铁MTN003A,25深圳地铁MTN003B,24深圳地铁MTN007A,24深圳地铁MTN007B]</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD48" s="3"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr">
+        <is>
+          <t>深圳市地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种二)</t>
+        </is>
+      </c>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr">
+        <is>
+          <t>2033-09-09</t>
+        </is>
+      </c>
+      <c r="AK48" s="3"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>公交</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-09</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AX48" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AZ48" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_all_2026-09-07.xlsx
+++ b/data/credit_bond_all_2026-09-07.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-07" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-08" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,9 @@
       <c r="E7" s="4" t="n">
         <v>4.6</v>
       </c>
-      <c r="F7" s="3"/>
+      <c r="F7" s="4" t="n">
+        <v>4.6</v>
+      </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
           <t>1.40 ~ 1.90</t>
@@ -1739,7 +1741,9 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AZ7" s="3"/>
+      <c r="AZ7" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
@@ -1765,7 +1769,9 @@
       <c r="E8" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F8" s="3"/>
+      <c r="F8" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.00</t>
@@ -1805,7 +1811,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>C- 23.18</t>
+          <t>C- 24.51</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1967,7 +1973,9 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AZ8" s="3"/>
+      <c r="AZ8" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
@@ -1993,7 +2001,9 @@
       <c r="E9" s="4" t="n">
         <v>15.0</v>
       </c>
-      <c r="F9" s="3"/>
+      <c r="F9" s="4" t="n">
+        <v>15.0</v>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t>1.30 ~ 1.46</t>
@@ -2033,7 +2043,7 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>B- 37.36</t>
+          <t>B- 36.06</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2217,7 +2227,9 @@
       <c r="E10" s="4" t="n">
         <v>6.0</v>
       </c>
-      <c r="F10" s="3"/>
+      <c r="F10" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
           <t>1.35 ~ 1.48</t>
@@ -2242,12 +2254,12 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.4916</t>
+          <t>1.4946</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>1.5100/1.4700</t>
+          <t>--/1.4700</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -2443,7 +2455,9 @@
       <c r="E11" s="4" t="n">
         <v>13.35</v>
       </c>
-      <c r="F11" s="3"/>
+      <c r="F11" s="4" t="n">
+        <v>13.35</v>
+      </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.10</t>
@@ -2483,7 +2497,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>D+ 9.59</t>
+          <t>D+ 7.87</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2667,7 +2681,9 @@
       <c r="E12" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F12" s="3"/>
+      <c r="F12" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
           <t>1.30 ~ 1.70</t>
@@ -2707,7 +2723,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.47</t>
+          <t>C 29.00</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2891,7 +2907,9 @@
       <c r="E13" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F13" s="3"/>
+      <c r="F13" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
           <t>2.20 ~ 2.90</t>
@@ -2921,7 +2939,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>--/2.6700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -2931,7 +2949,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C- 22.82</t>
+          <t>C- 22.25</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3119,7 +3137,9 @@
       <c r="E14" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F14" s="3"/>
+      <c r="F14" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
           <t>2.00 ~ 2.50</t>
@@ -3149,7 +3169,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>2.3800/2.3500</t>
+          <t>2.3800/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -3159,7 +3179,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C- 23.59</t>
+          <t>C- 22.73</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3324,68 +3344,70 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26东控02</t>
+          <t>26宁国建投MTN001</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-08 18:00</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>283923.SH</t>
+          <t>102683547.IB</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F15" s="3"/>
+        <v>1.26</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>1.26</v>
+      </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.60 ~ 2.40</t>
         </is>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>26东控01</t>
+          <t>25宁国建投MTN002</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>4.76Y</t>
+          <t>2.26Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.9477</t>
+          <t>2.0201</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>1.9900/1.9300</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>东阳市国控控股集团有限公司</t>
+          <t>安徽省宁国建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>B 55.00</t>
+          <t>C- 19.41</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3395,7 +3417,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -3412,39 +3434,39 @@
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.99%~2.09%</t>
+          <t>1.93%~2.03%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
+          <t>安徽省-宣城市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期债券的发行总额为不超过人民币5亿元(含5亿元),本期债券的募集资金在扣除发行费用后,拟用于偿还子公司东阳国投回售的公司债券本金。[23 东阳03]</t>
+          <t>发行人拟发行1.26亿元中期票据,拟全部用于偿还发行人存量债务融资工具本金。[25宁国建投CP002]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,财通证券股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
+          <t>徽商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3454,75 +3476,79 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>东阳市国控控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>安徽省宁国建设投资集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
-        </is>
-      </c>
-      <c r="AK15" s="3"/>
+          <t>2028-09-09</t>
+        </is>
+      </c>
+      <c r="AK15" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL15" s="3" t="inlineStr">
         <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AO15" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ15" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR15" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS15" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT15" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -3540,25 +3566,27 @@
       </c>
       <c r="AY15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AZ15" s="3"/>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AZ15" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26河西02</t>
+          <t>26扬子G5</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>283883.SH</t>
+          <t>246020.SH</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -3567,49 +3595,53 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>39.47</v>
+      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26河西01</t>
+          <t>26扬子G3</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2.70Y</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.7237</t>
+          <t>1.6665</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/1.6900</t>
+          <t>1.6900/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>南京市河西新城区国有资产经营控股(集团)有限责任公司</t>
+          <t>南京扬子国资投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.34</t>
+          <t>C 27.19</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3619,7 +3651,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -3629,7 +3661,7 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U16" s="3"/>
@@ -3641,7 +3673,7 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -3657,12 +3689,12 @@
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将不超过4.00亿元用于偿还到期公司债券本金[21河西03]</t>
+          <t>本次债券募集资金用途为偿还到期的公司债券本金[23扬子G3]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,国开证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
@@ -3683,22 +3715,22 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>南京市河西新城区国有资产经营控股(集团)有限责任公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>南京扬子国资投资集团有限责任公司2026年面向专业投资者公开发行公司债券(第三期)(品种一)</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2029-09-08</t>
+          <t>2029-09-09</t>
         </is>
       </c>
       <c r="AK16" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL16" s="3" t="inlineStr">
@@ -3713,7 +3745,7 @@
       </c>
       <c r="AN16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO16" s="3" t="inlineStr">
@@ -3723,7 +3755,7 @@
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
@@ -3733,12 +3765,12 @@
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
@@ -3776,17 +3808,17 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26德兴01</t>
+          <t>26扬子G6</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>283890.SH</t>
+          <t>246021.SH</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -3795,49 +3827,53 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>36.78</v>
+      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>25德兴02</t>
+          <t>26扬子G4</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>4.19Y</t>
+          <t>4.97Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>2.1843</t>
+          <t>1.7718</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>2.2000/2.1400</t>
+          <t>1.7800/1.7489</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>德兴市投资控股集团有限公司</t>
+          <t>南京扬子国资投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>B- 47.40</t>
+          <t>C 27.19</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3847,7 +3883,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -3864,40 +3900,36 @@
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>2.25%~2.35%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>江西省-上饶市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券的本金[23德兴02]</t>
+          <t>本次债券募集资金用途为偿还到期的公司债券本金[23扬子G3]</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD17" s="3" t="inlineStr">
-        <is>
-          <t>德兴市铜都国资运营控股发展有限公司</t>
-        </is>
-      </c>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,国开证券股份有限公司,广发证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -3915,12 +3947,12 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>德兴市投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>南京扬子国资投资集团有限责任公司2026年面向专业投资者公开发行公司债券(第三期)(品种二)</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="inlineStr">
@@ -3946,27 +3978,27 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
@@ -3981,7 +4013,7 @@
       </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW17" s="3" t="inlineStr">
@@ -4009,7 +4041,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>09-07 17:00</t>
+          <t>09-07 18:00</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -4031,8 +4063,12 @@
           <t>1.50 ~ 2.80</t>
         </is>
       </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+      <c r="H18" s="4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>57.78</v>
+      </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
           <t>--</t>
@@ -4078,10 +4114,26 @@
       </c>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>2.02%~2.12%</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>河北省-石家庄市</t>
@@ -4097,7 +4149,11 @@
           <t>财达证券股份有限公司</t>
         </is>
       </c>
-      <c r="AD18" s="3"/>
+      <c r="AD18" s="3" t="inlineStr">
+        <is>
+          <t>湖北省融资担保集团有限责任公司</t>
+        </is>
+      </c>
       <c r="AE18" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -4165,7 +4221,7 @@
       </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW18" s="3" t="inlineStr">
@@ -4188,68 +4244,72 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26南新06</t>
+          <t>26建城01</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>283665.SH</t>
+          <t>283858.SH</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.6</v>
+        <v>9.0</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+          <t>1.70 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>78.78</v>
+      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26南新05</t>
+          <t>26建湖城投PPN003</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>4.97Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.8375</t>
+          <t>2.1973</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.1500</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>重庆市南部新城产业投资集团有限公司</t>
+          <t>建湖县城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C- 19.30</t>
+          <t>D+ 8.81</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4269,40 +4329,40 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>2.15%~2.25%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>重庆市-巴南区</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,仅全部用于偿还“25南新D6”到期的公司债本金[25 南新D3,21 南新02,23 南司02,21 南司02,25 南新D4,25 南新D5,25 南新D6,23 南新03,26 南新D1]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[24建城01,23建城03]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>华源证券股份有限公司,西南证券股份有限公司</t>
+          <t>长城证券股份有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
@@ -4323,7 +4383,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>重庆市南部新城产业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第六期)</t>
+          <t>建湖县城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4333,14 +4393,10 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2029-09-08</t>
-        </is>
-      </c>
-      <c r="AK19" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-09</t>
+        </is>
+      </c>
+      <c r="AK19" s="3"/>
       <c r="AL19" s="3" t="inlineStr">
         <is>
           <t/>
@@ -4348,22 +4404,22 @@
       </c>
       <c r="AM19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AN19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
@@ -4383,7 +4439,7 @@
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4416,68 +4472,72 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26资产K2</t>
+          <t>26航港01</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>520454.SZ</t>
+          <t>283909.SH</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>43.47</v>
+      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26资产K1</t>
+          <t>24港投04</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>4.72Y</t>
+          <t>2.91Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>2.1259</t>
+          <t>1.8223</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>2.3900/2.0900</t>
+          <t>--/1.8000</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>资阳产业投资集团有限公司</t>
+          <t>河南航空港投资集团有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>B+ 56.67</t>
+          <t>B- 45.76</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4497,47 +4557,43 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>2.27%~2.37%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>四川省-资阳市</t>
+          <t>河南省-郑州市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,发行人将不低于(含)3.50亿元的募集资金通过发行人子公司对投资于科技创新类企业的基金出资或用于置换一年以内投资于科技创新企业的基金出资,剩余不超过(含)1.50亿元的募集资金用于偿还有息债务。</t>
+          <t>本期债券的募集资金在扣除发行费用后,将全部用于偿还到期公司债券本金[21兴港03]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD20" s="3" t="inlineStr">
-        <is>
-          <t>中合中小企业融资担保股份有限公司</t>
-        </is>
-      </c>
+          <t>国泰海通证券股份有限公司,国投证券股份有限公司,东方证券股份有限公司,平安证券股份有限公司,中国银河证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -4550,12 +4606,12 @@
       </c>
       <c r="AG20" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>资阳产业投资集团有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)</t>
+          <t>河南航空港投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4565,10 +4621,14 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
-        </is>
-      </c>
-      <c r="AK20" s="3"/>
+          <t>2029-09-08</t>
+        </is>
+      </c>
+      <c r="AK20" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL20" s="3" t="inlineStr">
         <is>
           <t/>
@@ -4581,37 +4641,37 @@
       </c>
       <c r="AN20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4621,7 +4681,7 @@
       </c>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW20" s="3" t="inlineStr">
@@ -4644,22 +4704,22 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26高城01</t>
+          <t>26东控02</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>520464.SZ</t>
+          <t>283923.SH</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
@@ -4668,44 +4728,44 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>24合高01</t>
+          <t>26东控01</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>300D+2.00Y</t>
+          <t>4.76Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.5507</t>
+          <t>1.9406</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.9300</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>合肥高新城市发展集团有限公司</t>
+          <t>东阳市国控控股集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C- 18.80</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4725,40 +4785,40 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.99%~2.09%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>安徽省-合肥市</t>
+          <t>浙江省-金华市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司有息债务[23合高01]</t>
+          <t>本期债券的发行总额为不超过人民币5亿元(含5亿元),本期债券的募集资金在扣除发行费用后,拟用于偿还子公司东阳国投回售的公司债券本金。[23 东阳03]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,财通证券股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
@@ -4774,12 +4834,12 @@
       </c>
       <c r="AG21" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>合肥高新城市发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>东阳市国控控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -4789,14 +4849,10 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2029-09-08</t>
-        </is>
-      </c>
-      <c r="AK21" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-09</t>
+        </is>
+      </c>
+      <c r="AK21" s="3"/>
       <c r="AL21" s="3" t="inlineStr">
         <is>
           <t/>
@@ -4809,12 +4865,12 @@
       </c>
       <c r="AN21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
@@ -4824,22 +4880,22 @@
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -4872,68 +4928,72 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26黔高04</t>
+          <t>26深铁09</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>246012.SH</t>
+          <t>520467.SZ</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>10.0</v>
+        <v>7.5</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>53.47</v>
+      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26贵州高速MTN003</t>
+          <t>26深铁07</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.8747</t>
+          <t>1.7764</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>1.8700/1.8600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>贵州高速公路集团有限公司</t>
+          <t>深圳市地铁集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>B- 45.40</t>
+          <t>C+ 32.18</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -4943,7 +5003,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
@@ -4960,12 +5020,12 @@
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -4973,20 +5033,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z22" s="3"/>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金10.00亿元拟用于偿还到期公司债券本金[23黔高02]</t>
+          <t>本期债券发行规模不超过15亿元(含)，扣除发行费用后拟用于偿还公司有息债务[23深铁13,25深圳地铁MTN003A,25深圳地铁MTN003B,24深圳地铁MTN007A,24深圳地铁MTN007B]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
@@ -5002,25 +5066,29 @@
       </c>
       <c r="AG22" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>贵州高速公路集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
+          <t>深圳市地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种一)</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
-        </is>
-      </c>
-      <c r="AK22" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK22" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL22" s="3" t="inlineStr">
         <is>
           <t/>
@@ -5028,7 +5096,7 @@
       </c>
       <c r="AM22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AN22" s="3" t="inlineStr">
@@ -5043,7 +5111,7 @@
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
@@ -5053,17 +5121,17 @@
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5096,17 +5164,17 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26张高02</t>
+          <t>26海兴01</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>283818.SH</t>
+          <t>283921.SH</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -5115,34 +5183,38 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+          <t>1.80 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>69.78</v>
+      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26张高01</t>
+          <t>25海兴09</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>4.59Y</t>
+          <t>4.28Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.8884</t>
+          <t>1.9873</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -5152,12 +5224,12 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>张家港市高铁投资发展(集团)有限公司</t>
+          <t>盐城市海兴集团有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.58</t>
+          <t>C- 17.80</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5167,7 +5239,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -5177,19 +5249,19 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.96%~2.06%</t>
+          <t>2.06%~2.16%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -5200,17 +5272,17 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过6亿元,募集资金在扣除发行费用后,拟用于偿还公司债券本金[23张高02]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还回售的公司债券本金[23海兴02]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,中邮证券有限责任公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
@@ -5231,7 +5303,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>张家港市高铁投资发展(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>盐城市海兴集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5241,7 +5313,7 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
+          <t>2031-09-08</t>
         </is>
       </c>
       <c r="AK23" s="3"/>
@@ -5257,7 +5329,7 @@
       </c>
       <c r="AN23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO23" s="3" t="inlineStr">
@@ -5270,21 +5342,9 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="AQ23" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR23" s="3" t="inlineStr">
-        <is>
-          <t>综合基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS23" s="3" t="inlineStr">
-        <is>
-          <t>综合基础设施投融资建设</t>
-        </is>
-      </c>
+      <c r="AQ23" s="3"/>
+      <c r="AR23" s="3"/>
+      <c r="AS23" s="3"/>
       <c r="AT23" s="3" t="inlineStr">
         <is>
           <t>基础建设</t>
@@ -5320,104 +5380,128 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26周高01</t>
+          <t>26河西02</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>283872.SH</t>
+          <t>283883.SH</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>45.47</v>
+      </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>26河西01</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>2.70Y</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>1.7209</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>--/1.6900</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>南京市河西新城区国有资产经营控股(集团)有限责任公司</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>C+ 31.86</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>09-07 15:00</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>周口高新科技产业发展有限公司</t>
-        </is>
-      </c>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t>09-07 15:00</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
-      <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>1.75%~1.85%</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>河南省-周口市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司到期债务等监管机构认可的用途。</t>
+          <t>本期债券募集资金扣除发行费用后,拟将不超过4.00亿元用于偿还到期公司债券本金[21河西03]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD24" s="3" t="inlineStr">
-        <is>
-          <t>河南中豫信用增进有限公司</t>
-        </is>
-      </c>
+          <t>华泰联合证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -5435,7 +5519,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>周口高新科技产业发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>南京市河西新城区国有资产经营控股(集团)有限责任公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5445,10 +5529,14 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
-        </is>
-      </c>
-      <c r="AK24" s="3"/>
+          <t>2029-09-08</t>
+        </is>
+      </c>
+      <c r="AK24" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL24" s="3" t="inlineStr">
         <is>
           <t/>
@@ -5461,21 +5549,37 @@
       </c>
       <c r="AN24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="AP24" s="3"/>
-      <c r="AQ24" s="3"/>
-      <c r="AR24" s="3"/>
-      <c r="AS24" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5485,7 +5589,7 @@
       </c>
       <c r="AV24" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW24" s="3" t="inlineStr">
@@ -5508,22 +5612,22 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26西居01</t>
+          <t>26平经03</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>283842.SH</t>
+          <t>283879.SH</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
@@ -5532,44 +5636,48 @@
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>31.78</v>
+      </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>25西居01</t>
+          <t>26平经02</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>3.62Y</t>
+          <t>2.76Y+2.00Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.9747</t>
+          <t>1.7109</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7600/1.6600</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>西安市安居建设管理集团有限公司</t>
+          <t>平湖经济技术开发区投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>D- 0.83</t>
+          <t>D 3.20</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5579,7 +5687,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -5596,36 +5704,40 @@
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>浙江省-嘉兴市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金规模为不超过5亿元(含5亿元),扣除发行费用后,拟全部用于偿还有息债务。</t>
+          <t>本期债券募集资金扣除发行费用后,公司拟将本期债券募集资金全部用于偿还公司债券本金[23平经03]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD25" s="3"/>
+          <t>中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr">
+        <is>
+          <t>平湖国发投控股集团有限公司</t>
+        </is>
+      </c>
       <c r="AE25" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -5643,7 +5755,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>西安市安居建设管理集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>平湖经济技术开发区投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5653,72 +5765,68 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
+          <t>2031-09-09</t>
+        </is>
+      </c>
+      <c r="AK25" s="3"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>6.5*无效</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
           <t>2029-09-09</t>
         </is>
       </c>
-      <c r="AK25" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
-      <c r="AL25" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM25" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AO25" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ25" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR25" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS25" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT25" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU25" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV25" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW25" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX25" s="3" t="inlineStr">
@@ -5736,53 +5844,49 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26光明建发02</t>
+          <t>26周高01</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>520463.SZ</t>
+          <t>283872.SH</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+          <t>2.00 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>83.78</v>
+      </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>26光明建发01</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>2.42Y+2.00Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.7647</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -5792,14 +5896,10 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>深圳市光明区建设发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t>C+ 35.00</t>
-        </is>
-      </c>
+          <t>周口高新科技产业发展有限公司</t>
+        </is>
+      </c>
+      <c r="P26" s="3"/>
       <c r="Q26" s="3" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -5817,43 +5917,43 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
-        </is>
-      </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+          <t>2.16%~2.26%</t>
+        </is>
+      </c>
+      <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>河南省-周口市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过5亿元(含),发行人拟使用不少于4.7815亿元用于偿还公司有息债务,剩余部分用于补充公司本部及子公司生产经营所需流动资金</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司到期债务等监管机构认可的用途。</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD26" s="3"/>
+          <t>平安证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr">
+        <is>
+          <t>河南中豫信用增进有限公司</t>
+        </is>
+      </c>
       <c r="AE26" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -5866,12 +5966,12 @@
       </c>
       <c r="AG26" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>深圳市光明区建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>周口高新科技产业发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -5881,7 +5981,7 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
+          <t>2031-09-09</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
@@ -5897,52 +5997,36 @@
       </c>
       <c r="AN26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ26" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR26" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS26" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="AP26" s="3"/>
+      <c r="AQ26" s="3"/>
+      <c r="AR26" s="3"/>
+      <c r="AS26" s="3"/>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
         <is>
-          <t>2029-09-10</t>
+          <t/>
         </is>
       </c>
       <c r="AV26" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW26" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX26" s="3" t="inlineStr">
@@ -5960,53 +6044,57 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26宁国建投MTN001</t>
+          <t>26张高02</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>09-08 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>102683547.IB</t>
+          <t>283818.SH</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.26</v>
+        <v>6.0</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>49.78</v>
+      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>25宁国建投MTN002</t>
+          <t>26张高01</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>2.26Y</t>
+          <t>4.59Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>2.0338</t>
+          <t>1.8746</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -6016,12 +6104,12 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>安徽省宁国建设投资集团有限公司</t>
+          <t>张家港市高铁投资发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C- 19.41</t>
+          <t>B- 40.33</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6031,7 +6119,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -6048,39 +6136,39 @@
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.93%~2.03%</t>
+          <t>1.96%~2.06%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>安徽省-宣城市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>发行人拟发行1.26亿元中期票据,拟全部用于偿还发行人存量债务融资工具本金。[25宁国建投CP002]</t>
+          <t>本期债券发行规模为不超过6亿元,募集资金在扣除发行费用后,拟用于偿还公司债券本金[23张高02]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>徽商银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6090,32 +6178,28 @@
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>安徽省宁国建设投资集团有限公司2026年度第一期中期票据</t>
+          <t>张家港市高铁投资发展(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2028-09-09</t>
-        </is>
-      </c>
-      <c r="AK27" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-09</t>
+        </is>
+      </c>
+      <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
@@ -6135,7 +6219,7 @@
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
@@ -6145,12 +6229,12 @@
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
@@ -6180,7 +6264,7 @@
       </c>
       <c r="AY27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AZ27" s="3"/>
@@ -6188,53 +6272,57 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26黄发04</t>
+          <t>26西居01</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>283938.SH</t>
+          <t>283842.SH</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.75</v>
+        <v>5.0</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>59.47</v>
+      </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>26黄发01</t>
+          <t>25西居01</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>4.51Y</t>
+          <t>3.62Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>2.1094</t>
+          <t>1.9656</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -6244,12 +6332,12 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>黄石市城市发展投资集团有限公司</t>
+          <t>西安市安居建设管理集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>B- 37.25</t>
+          <t>D- 0.83</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6269,40 +6357,40 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>2.19%~2.29%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>湖北省-黄石市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金[26黄发D2,26黄发D1]</t>
+          <t>本期债券募集资金规模为不超过5亿元(含5亿元),扣除发行费用后,拟全部用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>西部证券股份有限公司,华源证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
@@ -6323,7 +6411,7 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>黄石市城市发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>西安市安居建设管理集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6333,10 +6421,14 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
-        </is>
-      </c>
-      <c r="AK28" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK28" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL28" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6349,12 +6441,12 @@
       </c>
       <c r="AN28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
@@ -6364,17 +6456,17 @@
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
@@ -6412,68 +6504,68 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26横琴Y3</t>
+          <t>26西投K3(取消发行)</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>283861.SH</t>
+          <t>DY283805.SH</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>11.0</v>
+        <v>2.5</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.80 ~ 2.50</t>
         </is>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26横琴Y2</t>
+          <t>26西投K1</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>2.89Y+N</t>
+          <t>4.90Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.9307</t>
+          <t>2.3599</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>1.9400/1.9000</t>
+          <t>2.3600/2.3300</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>珠海大横琴集团有限公司</t>
+          <t>西安投资控股有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>B- 38.95</t>
+          <t>C- 23.16</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6483,7 +6575,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6500,33 +6592,33 @@
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>2.14%~2.24%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>广东省-珠海市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司有息债务。</t>
+          <t>本期债券的募集资金扣除相关发行费用后,拟将不低于70%募集资金用于置换前12个月内科技创新领域的基金出资款,剩余部分用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>招商证券股份有限公司,国金证券股份有限公司,华泰联合证券有限责任公司</t>
+          <t>中信证券股份有限公司,国投证券股份有限公司,首创证券股份有限公司,开源证券股份有限公司,联储证券股份有限公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
@@ -6547,7 +6639,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>珠海大横琴集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第三期)</t>
+          <t>西安投资控股有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)(品种二)(取消发行)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6557,14 +6649,10 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK29" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-09</t>
+        </is>
+      </c>
+      <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6572,7 +6660,7 @@
       </c>
       <c r="AM29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN29" s="3" t="inlineStr">
@@ -6582,32 +6670,32 @@
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6622,7 +6710,7 @@
       </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX29" s="3" t="inlineStr">
@@ -6640,64 +6728,68 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26义乌农商三农债01A</t>
+          <t>26徐经01</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
-        </is>
-      </c>
-      <c r="C30" s="3"/>
+          <t>09-07 19:00</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>283791.SH</t>
+        </is>
+      </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>24义乌农商三农债02</t>
+          <t>24徐州经开PPN002</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>1.23Y</t>
+          <t>2.88Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.5344</t>
+          <t>1.7945</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8200/--</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>浙江义乌农村商业银行股份有限公司</t>
+          <t>徐州经济技术开发区国有资产经营有限责任公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>D 4.33</t>
+          <t>C 27.93</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6707,7 +6799,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -6724,12 +6816,12 @@
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>1.99%~2.09%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -6737,62 +6829,54 @@
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z30" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+      <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
+          <t>江苏省-徐州市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金将依据适用法律和监管部门的批准用于发放涉农贷款</t>
+          <t>本次公司债券募集资金扣除发行费用后,拟将13.00亿元用于偿还到期的公司债券本金。[23徐经01]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司,中国国际金融股份有限公司,东吴证券股份有限公司,广发证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>2026年浙江义乌农村商业银行股份有限公司"三农"专项金融债券(品种一)</t>
+          <t>徐州经济技术开发区国有资产经营有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK30" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-09</t>
+        </is>
+      </c>
+      <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6800,7 +6884,7 @@
       </c>
       <c r="AM30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN30" s="3" t="inlineStr">
@@ -6810,7 +6894,7 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
@@ -6820,22 +6904,22 @@
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>农商行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -6868,70 +6952,72 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26川高速SCP001</t>
+          <t>26南新06</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 18:30</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>012682211.IB</t>
+          <t>283665.SH</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="F31" s="3"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
-        </is>
-      </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>57.47</v>
+      </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>21川高速MTN008</t>
+          <t>26南新05</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>80D</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.4955</t>
+          <t>1.8290</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>1.5000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>四川高速公路建设开发集团有限公司</t>
+          <t>重庆市南部新城产业投资集团有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C- 19.79</t>
+          <t>C- 17.10</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -6941,7 +7027,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -6958,39 +7044,39 @@
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>重庆市-巴南区</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具拟募集资金10亿元,拟全部用于偿付到期债务融资工具【21川高速MTN007】</t>
+          <t>本期公司债券募集资金扣除发行费用后,仅全部用于偿还“25南新D6”到期的公司债本金[25 南新D3,21 南新02,23 南司02,21 南司02,25 南新D4,25 南新D5,25 南新D6,23 南新03,26 南新D1]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>华源证券股份有限公司,西南证券股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
@@ -7000,33 +7086,37 @@
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>四川高速公路建设开发集团有限公司2026年度第一期超短期融资券</t>
+          <t>重庆市南部新城产业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第六期)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
-        </is>
-      </c>
-      <c r="AK31" s="3"/>
+          <t>2029-09-08</t>
+        </is>
+      </c>
+      <c r="AK31" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t/>
         </is>
       </c>
       <c r="AM31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN31" s="3" t="inlineStr">
@@ -7041,27 +7131,27 @@
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7094,22 +7184,22 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26核保02</t>
+          <t>义乌KY02</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>246006.SH</t>
+          <t>282563.SH</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
@@ -7118,44 +7208,48 @@
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>56.78</v>
+      </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26核保01</t>
+          <t>26义乌Y1</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>1.36Y</t>
+          <t>2.73Y+N</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.9037</t>
+          <t>1.8069</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>1.9900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>中核商业保理有限公司</t>
+          <t>义乌市国有资本运营有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>D+ 6.12</t>
+          <t>B- 35.38</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7182,33 +7276,37 @@
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.91%~2.01%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z32" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江省-金华市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金5亿元拟用于偿还有息债务</t>
+          <t>本期债券发行规模不超过5亿元(含5亿元),拟将募集资金不低于70%通过基金出资用于支持科技创新领域发展(含置换发行前12个月内用于支持科技创新领域发展的基金出资),剩余不超过30%用于偿还到期债务。</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>招商证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
@@ -7219,7 +7317,7 @@
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
@@ -7229,17 +7327,17 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>中核商业保理有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>义乌市国有资本运营有限公司2026年面向专业投资者非公开发行科技创新可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2028-09-08</t>
+          <t>2031-09-08</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
@@ -7260,28 +7358,32 @@
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP32" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>保理</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>保理</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7296,12 +7398,12 @@
       </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX32" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY32" s="3" t="inlineStr">
@@ -7314,70 +7416,72 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26沈阳地铁MTN004</t>
+          <t>26资产K2</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>09-08 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>102683539.IB</t>
+          <t>520454.SZ</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>15.0</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F33" s="3"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>89.78</v>
+      </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>24沈阳地铁MTN006B</t>
+          <t>26资产K1</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>4.95Y+N</t>
+          <t>4.72Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>2.3235</t>
+          <t>2.1235</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>--/2.2400</t>
+          <t>2.3900/2.0900</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>沈阳地铁集团有限公司</t>
+          <t>资阳产业投资集团有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.71</t>
+          <t>B+ 56.67</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7387,7 +7491,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -7404,43 +7508,47 @@
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>2.22%~2.32%</t>
+          <t>2.27%~2.37%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z33" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>辽宁省-沈阳市</t>
+          <t>四川省-资阳市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为人民币0亿元,发行金额上限为人民币15亿元,本次债券募集资金拟用于偿还公司有息债务。[24沈阳地铁MTN007,25沈阳地铁MTN004]</t>
+          <t>本期公司债券募集资金扣除发行费用后,发行人将不低于(含)3.50亿元的募集资金通过发行人子公司对投资于科技创新类企业的基金出资或用于置换一年以内投资于科技创新企业的基金出资,剩余不超过(含)1.50亿元的募集资金用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>中国邮政储蓄银行股份有限公司,光大证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD33" s="3"/>
+          <t>天风证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr">
+        <is>
+          <t>中合中小企业融资担保股份有限公司</t>
+        </is>
+      </c>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
@@ -7450,17 +7558,17 @@
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>沈阳地铁集团有限公司2026年度第四期中期票据</t>
+          <t>资阳产业投资集团有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
@@ -7471,12 +7579,12 @@
       <c r="AK33" s="3"/>
       <c r="AL33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN33" s="3" t="inlineStr">
@@ -7486,32 +7594,32 @@
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7521,12 +7629,12 @@
       </c>
       <c r="AV33" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX33" s="3" t="inlineStr">
@@ -7536,7 +7644,7 @@
       </c>
       <c r="AY33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AZ33" s="3"/>
@@ -7544,68 +7652,72 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>义乌KY02</t>
+          <t>26西投K2</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>282563.SH</t>
+          <t>283804.SH</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.0</v>
+        <v>2.5</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
+          <t>1.60 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>70.47</v>
+      </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26义乌Y1</t>
+          <t>26西投01</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2.73Y+N</t>
+          <t>4.77Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.7852</t>
+          <t>2.3710</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>1.8000/--</t>
+          <t>--/2.0900</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>义乌市国有资本运营有限公司</t>
+          <t>西安投资控股有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>B- 35.53</t>
+          <t>C- 23.16</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7615,7 +7727,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -7625,44 +7737,40 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.91%~2.01%</t>
+          <t>1.96%~2.06%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z34" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过5亿元(含5亿元),拟将募集资金不低于70%通过基金出资用于支持科技创新领域发展(含置换发行前12个月内用于支持科技创新领域发展的基金出资),剩余不超过30%用于偿还到期债务。</t>
+          <t>本期债券的募集资金扣除相关发行费用后,拟将不低于70%募集资金用于置换前12个月内科技创新领域的基金出资款,剩余部分用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>中信证券股份有限公司,国投证券股份有限公司,首创证券股份有限公司,开源证券股份有限公司,联储证券股份有限公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
@@ -7683,7 +7791,7 @@
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>义乌市国有资本运营有限公司2026年面向专业投资者非公开发行科技创新可续期公司债券(第一期)</t>
+          <t>西安投资控股有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -7693,10 +7801,14 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
-        </is>
-      </c>
-      <c r="AK34" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK34" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL34" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7704,22 +7816,22 @@
       </c>
       <c r="AM34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
@@ -7729,12 +7841,12 @@
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
@@ -7754,12 +7866,12 @@
       </c>
       <c r="AW34" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX34" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY34" s="3" t="inlineStr">
@@ -7772,70 +7884,72 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26厦门产投MTN003(科创债)</t>
+          <t>26深铁10</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>102683466.IB</t>
+          <t>520468.SZ</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+2</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>7.5</v>
+      </c>
+      <c r="F35" s="3"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
+      <c r="H35" s="4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>46.72</v>
+      </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>26厦门产投MTN002(科创债)</t>
+          <t>26深铁08</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>4.97Y+2.00Y</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.8952</t>
+          <t>2.0276</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>--/1.8700</t>
+          <t>2.1000/--</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>厦门市产业投资有限公司</t>
+          <t>深圳市地铁集团有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>A 75.38</t>
+          <t>C+ 32.18</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -7845,7 +7959,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>09-07 11:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -7855,19 +7969,19 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.98%~2.08%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -7882,23 +7996,23 @@
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债券发行金额为5亿元，本期发行的募集资金扣除承销费后，拟全部用于科技创新领域股权投资以及置换发行人本期科技创新债券发行之日起一年以内科技创新领域股权投资；本期债券募集资金中5亿元拟用于对中创新航科技（福建）有限公司的科技创新领域股权投资以及置换一年之内的自有资金投入。</t>
+          <t>本期债券发行规模不超过15亿元(含)，扣除发行费用后拟用于偿还公司有息债务[23深铁13,25深圳地铁MTN003A,25深圳地铁MTN003B,24深圳地铁MTN007A,24深圳地铁MTN007B]</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,厦门银行股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
@@ -7908,69 +8022,73 @@
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>厦门市产业投资有限公司2026年度第三期科技创新债券</t>
+          <t>深圳市地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种二)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
+          <t>2033-09-09</t>
         </is>
       </c>
       <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AM35" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP35" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-09</t>
         </is>
       </c>
       <c r="AV35" s="3" t="inlineStr">
@@ -7980,7 +8098,7 @@
       </c>
       <c r="AW35" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX35" s="3" t="inlineStr">
@@ -7998,68 +8116,72 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26金融街MTN005A</t>
+          <t>26横琴Y3</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>102683543.IB</t>
+          <t>283861.SH</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>2+2</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>5.3</v>
+        <v>11.0</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2.05 ~ 2.75</t>
-        </is>
-      </c>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>65.47</v>
+      </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26金融街MTN004A</t>
+          <t>26横琴Y2</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>1.93Y+2.00Y</t>
+          <t>2.89Y+N</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>2.5181</t>
+          <t>1.9244</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/2.4800</t>
+          <t>--/1.9000</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司</t>
+          <t>珠海大横琴集团有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C- 22.82</t>
+          <t>B- 37.79</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8069,7 +8191,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>09-07 14:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8079,19 +8201,19 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>2.54%~2.64%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -8099,30 +8221,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z36" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>广东省-珠海市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为0亿元，发行规模上限为10.30亿元，拟将募集资金全部用于偿还发行人债务融资工具的本金和利息[23金融街MTN006]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司有息债务。</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司</t>
+          <t>招商证券股份有限公司,国金证券股份有限公司,华泰联合证券有限责任公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
@@ -8132,22 +8250,22 @@
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司2026年度第五期中期票据(品种一)</t>
+          <t>珠海大横琴集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2030-09-08</t>
+          <t>2029-09-09</t>
         </is>
       </c>
       <c r="AK36" s="3" t="inlineStr">
@@ -8157,52 +8275,52 @@
       </c>
       <c r="AL36" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AM36" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>住宅楼房</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
         <is>
-          <t>2028-09-08</t>
+          <t/>
         </is>
       </c>
       <c r="AV36" s="3" t="inlineStr">
@@ -8212,7 +8330,7 @@
       </c>
       <c r="AW36" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX36" s="3" t="inlineStr">
@@ -8230,68 +8348,72 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26扬子G6</t>
+          <t>26核保02</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>246021.SH</t>
+          <t>246006.SH</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>49.19</v>
+      </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>26扬子G4</t>
+          <t>26核保01</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>4.97Y</t>
+          <t>1.36Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.7379</t>
+          <t>1.9000</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>1.8000/1.7700</t>
+          <t>1.9900/--</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>南京扬子国资投资集团有限责任公司</t>
+          <t>中核商业保理有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C 25.89</t>
+          <t>D+ 6.12</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8301,7 +8423,7 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
@@ -8311,40 +8433,40 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本次债券募集资金用途为偿还到期的公司债券本金[23扬子G3]</t>
+          <t>本期债券募集资金5亿元拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,国开证券股份有限公司,广发证券股份有限公司</t>
+          <t>招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
@@ -8355,7 +8477,7 @@
       </c>
       <c r="AF37" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG37" s="3" t="inlineStr">
@@ -8365,7 +8487,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>南京扬子国资投资集团有限责任公司2026年面向专业投资者公开发行公司债券(第三期)(品种二)</t>
+          <t>中核商业保理有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8375,7 +8497,7 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
+          <t>2028-09-08</t>
         </is>
       </c>
       <c r="AK37" s="3"/>
@@ -8386,42 +8508,38 @@
       </c>
       <c r="AM37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AN37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP37" s="3"/>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>保理</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>保理</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8454,68 +8572,72 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26扬子G5</t>
+          <t>26德兴01</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>246020.SH</t>
+          <t>283890.SH</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>80.78</v>
+      </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>26扬子G3</t>
+          <t>25德兴02</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>4.19Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.6669</t>
+          <t>2.1649</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>1.6900/1.6600</t>
+          <t>2.2000/--</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>南京扬子国资投资集团有限责任公司</t>
+          <t>德兴市投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C 25.89</t>
+          <t>B- 47.40</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8525,7 +8647,7 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -8542,36 +8664,44 @@
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>2.25%~2.35%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z38" s="3"/>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>江西省-上饶市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本次债券募集资金用途为偿还到期的公司债券本金[23扬子G3]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券的本金[23德兴02]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,国开证券股份有限公司,广发证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD38" s="3"/>
+          <t>长城证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr">
+        <is>
+          <t>德兴市铜都国资运营控股发展有限公司</t>
+        </is>
+      </c>
       <c r="AE38" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -8589,24 +8719,20 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>南京扬子国资投资集团有限责任公司2026年面向专业投资者公开发行公司债券(第三期)(品种一)</t>
+          <t>德兴市投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK38" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-09</t>
+        </is>
+      </c>
+      <c r="AK38" s="3"/>
       <c r="AL38" s="3" t="inlineStr">
         <is>
           <t/>
@@ -8624,27 +8750,27 @@
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
@@ -8659,7 +8785,7 @@
       </c>
       <c r="AV38" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW38" s="3" t="inlineStr">
@@ -8682,7 +8808,7 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26海兴01</t>
+          <t>26义乌农商三农债01A</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8690,45 +8816,41 @@
           <t>09-07 18:00</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>283921.SH</t>
-        </is>
-      </c>
+      <c r="C39" s="3"/>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.50</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>25海兴09</t>
+          <t>24义乌农商三农债02</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>4.28Y</t>
+          <t>1.23Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>2.0053</t>
+          <t>1.5344</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -8738,12 +8860,12 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>盐城市海兴集团有限公司</t>
+          <t>浙江义乌农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 16.75</t>
+          <t>D 4.33</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -8753,7 +8875,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -8763,19 +8885,19 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>2.06%~2.16%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
@@ -8783,54 +8905,62 @@
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z39" s="3"/>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>江苏省-盐城市</t>
+          <t>浙江省-金华市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还回售的公司债券本金[23海兴02]</t>
+          <t>本期债券募集资金将依据适用法律和监管部门的批准用于发放涉农贷款</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,中邮证券有限责任公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG39" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>盐城市海兴集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>2026年浙江义乌农村商业银行股份有限公司"三农"专项金融债券(品种一)</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
-        </is>
-      </c>
-      <c r="AK39" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK39" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL39" s="3" t="inlineStr">
         <is>
           <t/>
@@ -8838,17 +8968,17 @@
       </c>
       <c r="AM39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AN39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
@@ -8856,12 +8986,24 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="AQ39" s="3"/>
-      <c r="AR39" s="3"/>
-      <c r="AS39" s="3"/>
+      <c r="AQ39" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>农商行</t>
+        </is>
+      </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -8894,7 +9036,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26西投K2</t>
+          <t>26川高速SCP001</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -8904,58 +9046,60 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>283804.SH</t>
+          <t>012682211.IB</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F40" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.30</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26西投01</t>
+          <t>21川高速MTN008</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>80D</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>2.3754</t>
+          <t>1.4955</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>--/2.0900</t>
+          <t>1.5000/--</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>西安投资控股有限公司</t>
+          <t>四川高速公路建设开发集团有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C- 23.16</t>
+          <t>C- 20.05</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -8965,7 +9109,7 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
@@ -8975,46 +9119,46 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.96%~2.06%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金扣除相关发行费用后,拟将不低于70%募集资金用于置换前12个月内科技创新领域的基金出资款,剩余部分用于偿还有息债务</t>
+          <t>发行人本期债务融资工具拟募集资金10亿元,拟全部用于偿付到期债务融资工具【21川高速MTN007】</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国投证券股份有限公司,首创证券股份有限公司,开源证券股份有限公司,联储证券股份有限公司,国金证券股份有限公司</t>
+          <t>中国光大银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
@@ -9024,72 +9168,68 @@
       </c>
       <c r="AG40" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>西安投资控股有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)(品种一)</t>
+          <t>四川高速公路建设开发集团有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK40" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="AK40" s="3"/>
       <c r="AL40" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AN40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -9122,68 +9262,70 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26西投K3</t>
+          <t>26沈阳地铁MTN004</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-08 18:00</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>283805.SH</t>
+          <t>102683539.IB</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F41" s="3"/>
+        <v>15.0</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>15.0</v>
+      </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.50</t>
+          <t>2.00 ~ 2.70</t>
         </is>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>26西投K1</t>
+          <t>24沈阳地铁MTN006B</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>4.90Y</t>
+          <t>4.95Y+N</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>2.3695</t>
+          <t>2.3096</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>--/2.3300</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>西安投资控股有限公司</t>
+          <t>沈阳地铁集团有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>C- 23.16</t>
+          <t>C+ 30.06</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9193,7 +9335,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -9215,34 +9357,38 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>2.14%~2.24%</t>
+          <t>2.22%~2.32%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z41" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>辽宁省-沈阳市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金扣除相关发行费用后,拟将不低于70%募集资金用于置换前12个月内科技创新领域的基金出资款,剩余部分用于偿还有息债务</t>
+          <t>本期中期票据基础发行规模为人民币0亿元,发行金额上限为人民币15亿元,本次债券募集资金拟用于偿还公司有息债务。[24沈阳地铁MTN007,25沈阳地铁MTN004]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国投证券股份有限公司,首创证券股份有限公司,开源证券股份有限公司,联储证券股份有限公司,国金证券股份有限公司</t>
+          <t>中国邮政储蓄银行股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF41" s="3" t="inlineStr">
@@ -9252,17 +9398,17 @@
       </c>
       <c r="AG41" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>西安投资控股有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)(品种二)</t>
+          <t>沈阳地铁集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ41" s="3" t="inlineStr">
@@ -9273,54 +9419,54 @@
       <c r="AK41" s="3"/>
       <c r="AL41" s="3" t="inlineStr">
         <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>铁路运输</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM41" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AO41" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ41" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR41" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS41" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT41" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU41" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV41" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -9328,7 +9474,7 @@
       </c>
       <c r="AW41" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX41" s="3" t="inlineStr">
@@ -9338,7 +9484,7 @@
       </c>
       <c r="AY41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AZ41" s="3"/>
@@ -9346,7 +9492,7 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26徐经01</t>
+          <t>26厦门产投MTN003(科创债)</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -9356,7 +9502,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>283791.SH</t>
+          <t>102683466.IB</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -9365,9 +9511,11 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="F42" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.50</t>
@@ -9377,37 +9525,37 @@
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>24徐州经开PPN002</t>
+          <t>26厦门产投MTN002(科创债)</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>2.88Y</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.7945</t>
+          <t>1.8952</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>1.8200/--</t>
+          <t>1.8900/1.8700</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>徐州经济技术开发区国有资产经营有限责任公司</t>
+          <t>厦门市产业投资有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C 27.90</t>
+          <t>A 70.17</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9417,7 +9565,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 11:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -9427,7 +9575,7 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U42" s="3"/>
@@ -9439,34 +9587,38 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>1.99%~2.09%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z42" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>江苏省-徐州市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本次公司债券募集资金扣除发行费用后,拟将13.00亿元用于偿还到期的公司债券本金。[23徐经01]</t>
+          <t>本期科技创新债券发行金额为5亿元，本期发行的募集资金扣除承销费后，拟全部用于科技创新领域股权投资以及置换发行人本期科技创新债券发行之日起一年以内科技创新领域股权投资；本期债券募集资金中5亿元拟用于对中创新航科技（福建）有限公司的科技创新领域股权投资以及置换一年之内的自有资金投入。</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中国国际金融股份有限公司,东吴证券股份有限公司,广发证券股份有限公司,中信证券股份有限公司</t>
+          <t>兴业银行股份有限公司,厦门银行股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF42" s="3" t="inlineStr">
@@ -9476,75 +9628,71 @@
       </c>
       <c r="AG42" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>徐州经济技术开发区国有资产经营有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>厦门市产业投资有限公司2026年度第三期科技创新债券</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
+          <t>2031-09-08</t>
         </is>
       </c>
       <c r="AK42" s="3"/>
       <c r="AL42" s="3" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP42" s="3"/>
+      <c r="AQ42" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM42" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AO42" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ42" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR42" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS42" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT42" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU42" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV42" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -9565,12 +9713,14 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AZ42" s="3"/>
+      <c r="AZ42" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26航港01</t>
+          <t>26金融街MTN005A</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -9580,58 +9730,60 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>283909.SH</t>
+          <t>102683543.IB</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2+2</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F43" s="3"/>
+        <v>5.3</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>5.3</v>
+      </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>2.05 ~ 2.75</t>
         </is>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>24港投04</t>
+          <t>26金融街MTN004A</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>2.91Y</t>
+          <t>1.93Y+2.00Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.8312</t>
+          <t>2.5181</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>1.8400/1.8000</t>
+          <t>--/2.4800</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>河南航空港投资集团有限公司</t>
+          <t>金融街控股股份有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>B- 44.02</t>
+          <t>C- 22.25</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -9641,7 +9793,7 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 14:00</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -9658,12 +9810,12 @@
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>2.54%~2.64%</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -9671,26 +9823,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z43" s="3"/>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>河南省-郑州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,将全部用于偿还到期公司债券本金[21兴港03]</t>
+          <t>本期中期票据基础发行规模为0亿元，发行规模上限为10.30亿元，拟将募集资金全部用于偿还发行人债务融资工具的本金和利息[23金融街MTN006]</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,国投证券股份有限公司,东方证券股份有限公司,平安证券股份有限公司,中国银河证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
@@ -9700,32 +9856,32 @@
       </c>
       <c r="AG43" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>河南航空港投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>金融街控股股份有限公司2026年度第五期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2029-09-08</t>
+          <t>2030-09-08</t>
         </is>
       </c>
       <c r="AK43" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL43" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM43" s="3" t="inlineStr">
@@ -9740,37 +9896,37 @@
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>住宅楼房</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2028-09-08</t>
         </is>
       </c>
       <c r="AV43" s="3" t="inlineStr">
@@ -9780,7 +9936,7 @@
       </c>
       <c r="AW43" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX43" s="3" t="inlineStr">
@@ -9798,68 +9954,72 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26深城01</t>
+          <t>26黄发04</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>520466.SZ</t>
+          <t>283938.SH</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>5.0</v>
+        <v>6.75</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>73.78</v>
+      </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>25深汕01</t>
+          <t>26黄发01</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>1.78Y+2.00Y</t>
+          <t>4.51Y</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.6792</t>
+          <t>2.0891</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.0900</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>深圳市深汕特别合作区城市建设投资发展有限公司</t>
+          <t>黄石市城市发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.57</t>
+          <t>B- 37.13</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -9869,7 +10029,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -9884,38 +10044,38 @@
       </c>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
-      <c r="W44" s="3"/>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>2.19%~2.29%</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>湖北省-黄石市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还回售的公司债券本金[23深汕01]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金[26黄发D2,26黄发D1]</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD44" s="3" t="inlineStr">
-        <is>
-          <t>深圳市深担增信融资担保有限公司</t>
-        </is>
-      </c>
+          <t>西部证券股份有限公司,华源证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -9928,12 +10088,12 @@
       </c>
       <c r="AG44" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>深圳市深汕特别合作区城市建设投资发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>黄石市城市发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -9964,27 +10124,27 @@
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP44" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT44" s="3" t="inlineStr">
@@ -9994,17 +10154,17 @@
       </c>
       <c r="AU44" s="3" t="inlineStr">
         <is>
-          <t>2029-09-08</t>
+          <t/>
         </is>
       </c>
       <c r="AV44" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW44" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX44" s="3" t="inlineStr">
@@ -10022,17 +10182,17 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26平经03</t>
+          <t>26光明建发02</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>283879.SH</t>
+          <t>520463.SZ</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -10046,44 +10206,48 @@
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>20.78</v>
+      </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>26平经02</t>
+          <t>26光明建发01</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>2.76Y+2.00Y</t>
+          <t>2.42Y+2.00Y</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.7110</t>
+          <t>1.7626</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>1.7600/1.6600</t>
+          <t>--/1.7000</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>平湖经济技术开发区投资发展集团有限公司</t>
+          <t>深圳市光明区建设发展集团有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>D 4.80</t>
+          <t>B+ 60.00</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10093,7 +10257,7 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -10103,19 +10267,19 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -10123,27 +10287,27 @@
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z45" s="3"/>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>浙江省-嘉兴市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,公司拟将本期债券募集资金全部用于偿还公司债券本金[23平经03]</t>
+          <t>本期债券发行规模为不超过5亿元(含),发行人拟使用不少于4.7815亿元用于偿还公司有息债务,剩余部分用于补充公司本部及子公司生产经营所需流动资金</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD45" s="3" t="inlineStr">
-        <is>
-          <t>平湖国发投控股集团有限公司</t>
-        </is>
-      </c>
+          <t>国信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -10156,12 +10320,12 @@
       </c>
       <c r="AG45" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>平湖经济技术开发区投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>深圳市光明区建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
@@ -10171,7 +10335,7 @@
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
+          <t>2031-09-10</t>
         </is>
       </c>
       <c r="AK45" s="3"/>
@@ -10187,17 +10351,17 @@
       </c>
       <c r="AN45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>6.5*无效</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
@@ -10217,17 +10381,17 @@
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
+          <t>2029-09-10</t>
         </is>
       </c>
       <c r="AV45" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW45" s="3" t="inlineStr">
@@ -10250,68 +10414,72 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26建城01</t>
+          <t>26深城01</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>283858.SH</t>
+          <t>520466.SZ</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>40.78</v>
+      </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>26建湖城投PPN003</t>
+          <t>25深汕01</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>4.97Y</t>
+          <t>1.78Y+2.00Y</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>2.1973</t>
+          <t>1.6744</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>--/2.1500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>建湖县城市建设投资集团有限公司</t>
+          <t>深圳市深汕特别合作区城市建设投资发展有限公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.81</t>
+          <t>D+ 8.57</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10321,7 +10489,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
@@ -10331,19 +10499,15 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t>7-</t>
-        </is>
-      </c>
+      <c r="W46" s="3"/>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>2.15%~2.25%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
@@ -10354,20 +10518,24 @@
       <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>江苏省-盐城市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[24建城01,23建城03]</t>
+          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还回售的公司债券本金[23深汕01]</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司,东吴证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD46" s="3"/>
+          <t>中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr">
+        <is>
+          <t>深圳市深担增信融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE46" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -10380,12 +10548,12 @@
       </c>
       <c r="AG46" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>建湖县城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>深圳市深汕特别合作区城市建设投资发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
@@ -10395,7 +10563,7 @@
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
+          <t>2031-09-08</t>
         </is>
       </c>
       <c r="AK46" s="3"/>
@@ -10406,37 +10574,37 @@
       </c>
       <c r="AM46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP46" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ46" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT46" s="3" t="inlineStr">
@@ -10446,17 +10614,17 @@
       </c>
       <c r="AU46" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-08</t>
         </is>
       </c>
       <c r="AV46" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW46" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX46" s="3" t="inlineStr">
@@ -10474,17 +10642,17 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26深铁09</t>
+          <t>26高城01</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>520467.SZ</t>
+          <t>520464.SZ</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -10493,49 +10661,53 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>7.5</v>
+        <v>5.0</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>48.47</v>
+      </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>26深铁07</t>
+          <t>24合高01</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>300D+2.00Y</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>1.7828</t>
+          <t>1.5586</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>1.7900/1.7800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>深圳市地铁集团有限公司</t>
+          <t>合肥高新城市发展集团有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.92</t>
+          <t>C- 18.80</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -10555,44 +10727,40 @@
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U47" s="3"/>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X47" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y47" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z47" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z47" s="3"/>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>安徽省-合肥市</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过15亿元(含)，扣除发行费用后拟用于偿还公司有息债务[23深铁13,25深圳地铁MTN003A,25深圳地铁MTN003B,24深圳地铁MTN007A,24深圳地铁MTN007B]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司有息债务[23合高01]</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD47" s="3"/>
@@ -10613,7 +10781,7 @@
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>深圳市地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种一)</t>
+          <t>合肥高新城市发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
@@ -10623,12 +10791,12 @@
       </c>
       <c r="AJ47" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
+          <t>2029-09-08</t>
         </is>
       </c>
       <c r="AK47" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL47" s="3" t="inlineStr">
@@ -10638,22 +10806,22 @@
       </c>
       <c r="AM47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP47" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ47" s="3" t="inlineStr">
@@ -10663,17 +10831,17 @@
       </c>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT47" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU47" s="3" t="inlineStr">
@@ -10706,26 +10874,26 @@
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26深铁10</t>
+          <t>26黔高04</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>520468.SZ</t>
+          <t>246012.SH</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>5+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>7.5</v>
+        <v>10.0</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="inlineStr">
@@ -10733,41 +10901,45 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
+      <c r="H48" s="4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>43.78</v>
+      </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>26深铁08</t>
+          <t>26贵州高速MTN003</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>4.97Y+2.00Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>2.0263</t>
+          <t>1.8747</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>2.1000/--</t>
+          <t>1.8700/1.8600</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>深圳市地铁集团有限公司</t>
+          <t>贵州高速公路集团有限公司</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.92</t>
+          <t>B- 45.72</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -10777,7 +10949,7 @@
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
@@ -10794,12 +10966,12 @@
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X48" s="3" t="inlineStr">
         <is>
-          <t>1.98%~2.08%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y48" s="3" t="inlineStr">
@@ -10810,17 +10982,17 @@
       <c r="Z48" s="3"/>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过15亿元(含)，扣除发行费用后拟用于偿还公司有息债务[23深铁13,25深圳地铁MTN003A,25深圳地铁MTN003B,24深圳地铁MTN007A,24深圳地铁MTN007B]</t>
+          <t>本期债券募集资金10.00亿元拟用于偿还到期公司债券本金[23黔高02]</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>广发证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD48" s="3"/>
@@ -10836,22 +11008,22 @@
       </c>
       <c r="AG48" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>深圳市地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种二)</t>
+          <t>贵州高速公路集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ48" s="3" t="inlineStr">
         <is>
-          <t>2033-09-09</t>
+          <t>2031-09-09</t>
         </is>
       </c>
       <c r="AK48" s="3"/>
@@ -10862,7 +11034,7 @@
       </c>
       <c r="AM48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN48" s="3" t="inlineStr">
@@ -10877,7 +11049,7 @@
       </c>
       <c r="AP48" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ48" s="3" t="inlineStr">
@@ -10887,22 +11059,22 @@
       </c>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT48" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU48" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV48" s="3" t="inlineStr">
@@ -10912,7 +11084,7 @@
       </c>
       <c r="AW48" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX48" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-07.xlsx
+++ b/data/credit_bond_all_2026-09-07.xlsx
@@ -1545,8 +1545,12 @@
           <t>1.40 ~ 1.90</t>
         </is>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="H7" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>45.47</v>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>1.68</t>
@@ -1602,8 +1606,12 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
+      <c r="U7" s="4" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>8.0</v>
+      </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
           <t>6+</t>
@@ -1741,9 +1749,7 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AZ7" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ7" s="3"/>
     </row>
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
@@ -1777,8 +1783,12 @@
           <t>1.50 ~ 2.00</t>
         </is>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="H8" s="4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>31.47</v>
+      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
           <t>1.67</t>
@@ -1834,8 +1844,12 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
+      <c r="U8" s="4" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -1973,9 +1987,7 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AZ8" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ8" s="3"/>
     </row>
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
@@ -2009,8 +2021,12 @@
           <t>1.30 ~ 1.46</t>
         </is>
       </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="H9" s="4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>13.13</v>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>1.46</t>
@@ -2066,8 +2082,12 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
+      <c r="U9" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -2235,8 +2255,12 @@
           <t>1.35 ~ 1.48</t>
         </is>
       </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="H10" s="4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>26.13</v>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>1.48</t>
@@ -2292,8 +2316,12 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
+      <c r="U10" s="4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>1.44</v>
+      </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
           <t>4+</t>
@@ -2427,9 +2455,7 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AZ10" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ10" s="3"/>
     </row>
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
@@ -2463,8 +2489,12 @@
           <t>1.50 ~ 2.10</t>
         </is>
       </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="H11" s="4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>28.78</v>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
           <t>1.70</t>
@@ -2520,8 +2550,12 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
+      <c r="U11" s="4" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>1.14</v>
+      </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -2660,7 +2694,7 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP018</t>
+          <t>26金融街MTN005B</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2670,12 +2704,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>012682213.IB</t>
+          <t>102683544.IB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>0.24Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
@@ -2686,44 +2720,44 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>2.20 ~ 2.90</t>
         </is>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP017</t>
+          <t>26金融街MTN004B</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>73D</t>
+          <t>2.93Y+2.00Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.4803</t>
+          <t>2.6988</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>1.5100/1.3992</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司</t>
+          <t>金融街控股股份有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C 29.00</t>
+          <t>C- 22.25</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2733,7 +2767,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 14:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -2750,12 +2784,12 @@
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>2.64%~2.74%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -2763,26 +2797,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z12" s="3"/>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>发行人本次拟发行5亿元超短期融资券，用于偿还发行人存量负债。</t>
+          <t>本期中期票据基础发行规模为0亿元,发行规模上限为10.30亿元,拟将募集金全部用于偿还发行人债务融资工具的本金和利息【23金融街MTN006】</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,华夏银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD12" s="3"/>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr">
@@ -2797,7 +2835,7 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司2026年度第十八期超短期融资券</t>
+          <t>金融街控股股份有限公司2026年度第五期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2807,7 +2845,7 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2031-09-08</t>
         </is>
       </c>
       <c r="AK12" s="3"/>
@@ -2833,32 +2871,32 @@
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>住宅楼房</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>种植业</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-08</t>
         </is>
       </c>
       <c r="AV12" s="3" t="inlineStr">
@@ -2868,7 +2906,7 @@
       </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX12" s="3" t="inlineStr">
@@ -2886,7 +2924,7 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26金融街MTN005B</t>
+          <t>26皖交控MTN008</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2896,60 +2934,64 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>102683544.IB</t>
+          <t>102683542.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>30Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 2.90</t>
-        </is>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+          <t>2.00 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>20.75</v>
+      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26金融街MTN004B</t>
+          <t>26皖交控MTN005</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>2.93Y+2.00Y</t>
+          <t>29.84Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>2.6988</t>
+          <t>2.3621</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.3800/--</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司</t>
+          <t>安徽省交通控股集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C- 22.25</t>
+          <t>C- 22.73</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -2959,7 +3001,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>09-07 14:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -2976,12 +3018,12 @@
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>2.64%~2.74%</t>
+          <t>2.27%~2.37%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -2989,24 +3031,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z13" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>安徽省</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为0亿元,发行规模上限为10.30亿元,拟将募集金全部用于偿还发行人债务融资工具的本金和利息【23金融街MTN006】</t>
+          <t>本期债券发行规模10亿元，其中37,000万元拟用于补充营运资金，7,057.5万元拟用于偿还银行借款本金，4,300万元拟用于偿还债券利息，51,642.5万元拟用于偿还银行借款利息。[24皖交控MTN005（两新）,25皖交02]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司</t>
+          <t>招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
@@ -3027,7 +3065,7 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司2026年度第五期中期票据(品种二)</t>
+          <t>安徽省交通控股集团有限公司2026年度第八期中期票据</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3037,7 +3075,7 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
+          <t>2056-09-08</t>
         </is>
       </c>
       <c r="AK13" s="3"/>
@@ -3058,37 +3096,37 @@
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>住宅楼房</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
         <is>
-          <t>2029-09-08</t>
+          <t/>
         </is>
       </c>
       <c r="AV13" s="3" t="inlineStr">
@@ -3098,7 +3136,7 @@
       </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX13" s="3" t="inlineStr">
@@ -3111,75 +3149,77 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AZ13" s="3"/>
+      <c r="AZ13" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26皖交控MTN008</t>
+          <t>26宁国建投MTN001</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-08 18:00</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>102683542.IB</t>
+          <t>102683547.IB</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>30Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>10.0</v>
+        <v>1.26</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10.0</v>
+        <v>1.26</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.50</t>
+          <t>1.60 ~ 2.40</t>
         </is>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>26皖交控MTN005</t>
+          <t>25宁国建投MTN002</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>29.84Y</t>
+          <t>2.26Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>2.3621</t>
+          <t>2.0201</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>2.3800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>安徽省交通控股集团有限公司</t>
+          <t>安徽省宁国建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C- 22.73</t>
+          <t>C- 19.41</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3199,40 +3239,40 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>2.27%~2.37%</t>
+          <t>1.93%~2.03%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>安徽省</t>
+          <t>安徽省-宣城市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模10亿元，其中37,000万元拟用于补充营运资金，7,057.5万元拟用于偿还银行借款本金，4,300万元拟用于偿还债券利息，51,642.5万元拟用于偿还银行借款利息。[24皖交控MTN005（两新）,25皖交02]</t>
+          <t>发行人拟发行1.26亿元中期票据,拟全部用于偿还发行人存量债务融资工具本金。[25宁国建投CP002]</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司</t>
+          <t>徽商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
@@ -3253,7 +3293,7 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>安徽省交通控股集团有限公司2026年度第八期中期票据</t>
+          <t>安徽省宁国建设投资集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3263,78 +3303,82 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2056-09-08</t>
-        </is>
-      </c>
-      <c r="AK14" s="3"/>
+          <t>2028-09-09</t>
+        </is>
+      </c>
+      <c r="AK14" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL14" s="3" t="inlineStr">
         <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AM14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AN14" s="3" t="inlineStr">
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY14" s="3" t="inlineStr">
         <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AO14" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ14" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR14" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AS14" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AT14" s="3" t="inlineStr">
-        <is>
-          <t>高速公路</t>
-        </is>
-      </c>
-      <c r="AU14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV14" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW14" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX14" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AZ14" s="4" t="n">
@@ -3344,70 +3388,72 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26宁国建投MTN001</t>
+          <t>26扬子G5</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>09-08 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>102683547.IB</t>
+          <t>246020.SH</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>1.26</v>
-      </c>
+        <v>6.0</v>
+      </c>
+      <c r="F15" s="3"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>39.47</v>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>25宁国建投MTN002</t>
+          <t>26扬子G3</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>2.26Y</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>2.0201</t>
+          <t>1.6665</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6900/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>安徽省宁国建设投资集团有限公司</t>
+          <t>南京扬子国资投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C- 19.41</t>
+          <t>C 27.19</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3417,7 +3463,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -3434,39 +3480,39 @@
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.93%~2.03%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>安徽省-宣城市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>发行人拟发行1.26亿元中期票据,拟全部用于偿还发行人存量债务融资工具本金。[25宁国建投CP002]</t>
+          <t>本次债券募集资金用途为偿还到期的公司债券本金[23扬子G3]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>徽商银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,国开证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3476,12 +3522,12 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>安徽省宁国建设投资集团有限公司2026年度第一期中期票据</t>
+          <t>南京扬子国资投资集团有限责任公司2026年面向专业投资者公开发行公司债券(第三期)(品种一)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3491,17 +3537,17 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2028-09-09</t>
+          <t>2029-09-09</t>
         </is>
       </c>
       <c r="AK15" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM15" s="3" t="inlineStr">
@@ -3516,12 +3562,12 @@
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP15" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ15" s="3" t="inlineStr">
@@ -3566,17 +3612,15 @@
       </c>
       <c r="AY15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AZ15" s="4" t="n">
-        <v>0.01</v>
-      </c>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AZ15" s="3"/>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26扬子G5</t>
+          <t>26扬子G6</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3586,12 +3630,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>246020.SH</t>
+          <t>246021.SH</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
@@ -3600,38 +3644,38 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>39.47</v>
+        <v>36.78</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26扬子G3</t>
+          <t>26扬子G4</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>4.97Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.6665</t>
+          <t>1.7718</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>1.6900/--</t>
+          <t>1.7800/1.7489</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -3673,7 +3717,7 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -3715,7 +3759,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>南京扬子国资投资集团有限责任公司2026年面向专业投资者公开发行公司债券(第三期)(品种一)</t>
+          <t>南京扬子国资投资集团有限责任公司2026年面向专业投资者公开发行公司债券(第三期)(品种二)</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3725,14 +3769,10 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK16" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-09</t>
+        </is>
+      </c>
+      <c r="AK16" s="3"/>
       <c r="AL16" s="3" t="inlineStr">
         <is>
           <t/>
@@ -3808,74 +3848,62 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26扬子G6</t>
+          <t>26冀资K1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>09-07 19:00</t>
+          <t>09-07 18:00</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>246021.SH</t>
+          <t>283860.SH</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>6.0</v>
+        <v>1.5</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.80</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>36.78</v>
+        <v>57.78</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>26扬子G4</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>4.97Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.7718</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>1.7800/1.7489</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>南京扬子国资投资集团有限责任公司</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t>C 27.19</t>
-        </is>
-      </c>
+          <t>河北国控资本管理有限公司</t>
+        </is>
+      </c>
+      <c r="P17" s="3"/>
       <c r="Q17" s="3" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -3883,7 +3911,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -3900,36 +3928,44 @@
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>2.02%~2.12%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>河北省-石家庄市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本次债券募集资金用途为偿还到期的公司债券本金[23扬子G3]</t>
+          <t>本期债券募集资金总额不超过1.50亿元(含1.50亿元)。本期债券募集资金扣除发行费用后,拟全部通过直接投资或以基金投资等方式,对科技创新领域的企业进行股权投资,或用于置换发行前12个月内投资于科技创新企业的基金出资或股权投资资金。</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,国开证券股份有限公司,广发证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD17" s="3"/>
+          <t>财达证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr">
+        <is>
+          <t>湖北省融资担保集团有限责任公司</t>
+        </is>
+      </c>
       <c r="AE17" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -3947,12 +3983,12 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>南京扬子国资投资集团有限责任公司2026年面向专业投资者公开发行公司债券(第三期)(品种二)</t>
+          <t>河北国控资本管理有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="inlineStr">
@@ -3978,47 +4014,31 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ17" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR17" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS17" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="AP17" s="3"/>
+      <c r="AQ17" s="3"/>
+      <c r="AR17" s="3"/>
+      <c r="AS17" s="3"/>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-09</t>
         </is>
       </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
@@ -4036,62 +4056,74 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26冀资K1</t>
+          <t>26建城01</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>283860.SH</t>
+          <t>283858.SH</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.5</v>
+        <v>9.0</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.80</t>
+          <t>1.70 ~ 2.50</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>57.78</v>
+        <v>78.78</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>26建湖城投PPN003</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>4.97Y</t>
+        </is>
+      </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.1973</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.1500</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>河北国控资本管理有限公司</t>
-        </is>
-      </c>
-      <c r="P18" s="3"/>
+          <t>建湖县城市建设投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>D+ 8.81</t>
+        </is>
+      </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -4116,12 +4148,12 @@
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>2.02%~2.12%</t>
+          <t>2.15%~2.25%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -4129,31 +4161,23 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="Z18" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>河北省-石家庄市</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金总额不超过1.50亿元(含1.50亿元)。本期债券募集资金扣除发行费用后,拟全部通过直接投资或以基金投资等方式,对科技创新领域的企业进行股权投资,或用于置换发行前12个月内投资于科技创新企业的基金出资或股权投资资金。</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[24建城01,23建城03]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>财达证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD18" s="3" t="inlineStr">
-        <is>
-          <t>湖北省融资担保集团有限责任公司</t>
-        </is>
-      </c>
+          <t>长城证券股份有限公司,东吴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -4171,7 +4195,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>河北国控资本管理有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
+          <t>建湖县城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4192,7 +4216,7 @@
       </c>
       <c r="AM18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AN18" s="3" t="inlineStr">
@@ -4202,31 +4226,47 @@
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="AP18" s="3"/>
-      <c r="AQ18" s="3"/>
-      <c r="AR18" s="3"/>
-      <c r="AS18" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr">
@@ -4244,7 +4284,7 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26建城01</t>
+          <t>26航港01</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4254,62 +4294,62 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>283858.SH</t>
+          <t>283909.SH</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.50</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.19</v>
+        <v>1.68</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>78.78</v>
+        <v>43.47</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26建湖城投PPN003</t>
+          <t>24港投04</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>4.97Y</t>
+          <t>2.91Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>2.1973</t>
+          <t>1.8223</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>--/2.1500</t>
+          <t>--/1.8000</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>建湖县城市建设投资集团有限公司</t>
+          <t>河南航空港投资集团有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.81</t>
+          <t>B- 45.76</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4329,40 +4369,40 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>2.15%~2.25%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>江苏省-盐城市</t>
+          <t>河南省-郑州市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[24建城01,23建城03]</t>
+          <t>本期债券的募集资金在扣除发行费用后,将全部用于偿还到期公司债券本金[21兴港03]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司,东吴证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,国投证券股份有限公司,东方证券股份有限公司,平安证券股份有限公司,中国银河证券股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
@@ -4383,7 +4423,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>建湖县城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>河南航空港投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4393,10 +4433,14 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
-        </is>
-      </c>
-      <c r="AK19" s="3"/>
+          <t>2029-09-08</t>
+        </is>
+      </c>
+      <c r="AK19" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL19" s="3" t="inlineStr">
         <is>
           <t/>
@@ -4404,17 +4448,17 @@
       </c>
       <c r="AM19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP19" s="3" t="inlineStr">
@@ -4424,17 +4468,17 @@
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
@@ -4472,7 +4516,7 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26航港01</t>
+          <t>26东控02</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4482,62 +4526,62 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>283909.SH</t>
+          <t>283923.SH</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>43.47</v>
+        <v>52.78</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>24港投04</t>
+          <t>26东控01</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2.91Y</t>
+          <t>4.76Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.8223</t>
+          <t>1.9406</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/1.8000</t>
+          <t>--/1.9300</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>河南航空港投资集团有限公司</t>
+          <t>东阳市国控控股集团有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>B- 45.76</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4547,7 +4591,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -4557,19 +4601,19 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>1.99%~2.09%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -4580,17 +4624,17 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>河南省-郑州市</t>
+          <t>浙江省-金华市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,将全部用于偿还到期公司债券本金[21兴港03]</t>
+          <t>本期债券的发行总额为不超过人民币5亿元(含5亿元),本期债券的募集资金在扣除发行费用后,拟用于偿还子公司东阳国投回售的公司债券本金。[23 东阳03]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,国投证券股份有限公司,东方证券股份有限公司,平安证券股份有限公司,中国银河证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,财通证券股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
@@ -4611,7 +4655,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>河南航空港投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>东阳市国控控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4621,14 +4665,10 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2029-09-08</t>
-        </is>
-      </c>
-      <c r="AK20" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-09</t>
+        </is>
+      </c>
+      <c r="AK20" s="3"/>
       <c r="AL20" s="3" t="inlineStr">
         <is>
           <t/>
@@ -4641,7 +4681,7 @@
       </c>
       <c r="AN20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO20" s="3" t="inlineStr">
@@ -4651,27 +4691,27 @@
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4704,7 +4744,7 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26东控02</t>
+          <t>26深铁09</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4714,58 +4754,62 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>283923.SH</t>
+          <t>520467.SZ</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>5.0</v>
+        <v>7.5</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>53.47</v>
+      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26东控01</t>
+          <t>26深铁07</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>4.76Y</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.9406</t>
+          <t>1.7764</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>--/1.9300</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>东阳市国控控股集团有限公司</t>
+          <t>深圳市地铁集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>B 55.00</t>
+          <t>C+ 32.18</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4792,12 +4836,12 @@
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.99%~2.09%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -4805,20 +4849,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z21" s="3"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期债券的发行总额为不超过人民币5亿元(含5亿元),本期债券的募集资金在扣除发行费用后,拟用于偿还子公司东阳国投回售的公司债券本金。[23 东阳03]</t>
+          <t>本期债券发行规模不超过15亿元(含)，扣除发行费用后拟用于偿还公司有息债务[23深铁13,25深圳地铁MTN003A,25深圳地铁MTN003B,24深圳地铁MTN007A,24深圳地铁MTN007B]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,财通证券股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
@@ -4834,12 +4882,12 @@
       </c>
       <c r="AG21" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>东阳市国控控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>深圳市地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种一)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -4849,10 +4897,14 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
-        </is>
-      </c>
-      <c r="AK21" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK21" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL21" s="3" t="inlineStr">
         <is>
           <t/>
@@ -4860,7 +4912,7 @@
       </c>
       <c r="AM21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AN21" s="3" t="inlineStr">
@@ -4875,27 +4927,27 @@
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -4928,7 +4980,7 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26深铁09</t>
+          <t>26海兴01</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4938,47 +4990,47 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>520467.SZ</t>
+          <t>283921.SH</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>7.5</v>
+        <v>5.0</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.80 ~ 2.50</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>53.47</v>
+        <v>69.78</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26深铁07</t>
+          <t>25海兴09</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>4.28Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.7764</t>
+          <t>1.9873</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -4988,12 +5040,12 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>深圳市地铁集团有限公司</t>
+          <t>盐城市海兴集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.18</t>
+          <t>C- 17.80</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5013,44 +5065,40 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>2.06%~2.16%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过15亿元(含)，扣除发行费用后拟用于偿还公司有息债务[23深铁13,25深圳地铁MTN003A,25深圳地铁MTN003B,24深圳地铁MTN007A,24深圳地铁MTN007B]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还回售的公司债券本金[23海兴02]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,中邮证券有限责任公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
@@ -5066,12 +5114,12 @@
       </c>
       <c r="AG22" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>深圳市地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种一)</t>
+          <t>盐城市海兴集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5081,14 +5129,10 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK22" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-08</t>
+        </is>
+      </c>
+      <c r="AK22" s="3"/>
       <c r="AL22" s="3" t="inlineStr">
         <is>
           <t/>
@@ -5096,42 +5140,30 @@
       </c>
       <c r="AM22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AQ22" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR22" s="3" t="inlineStr">
-        <is>
-          <t>轨道交通</t>
-        </is>
-      </c>
-      <c r="AS22" s="3" t="inlineStr">
-        <is>
-          <t>轨道交通</t>
-        </is>
-      </c>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3"/>
+      <c r="AR22" s="3"/>
+      <c r="AS22" s="3"/>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5164,7 +5196,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26海兴01</t>
+          <t>26河西02</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5174,62 +5206,62 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>283921.SH</t>
+          <t>283883.SH</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.50</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>69.78</v>
+        <v>45.47</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>25海兴09</t>
+          <t>26河西01</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>4.28Y</t>
+          <t>2.70Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.9873</t>
+          <t>1.7209</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6900</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>盐城市海兴集团有限公司</t>
+          <t>南京市河西新城区国有资产经营控股(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C- 17.80</t>
+          <t>C+ 31.86</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5239,7 +5271,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -5256,33 +5288,33 @@
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>2.06%~2.16%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>江苏省-盐城市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还回售的公司债券本金[23海兴02]</t>
+          <t>本期债券募集资金扣除发行费用后,拟将不超过4.00亿元用于偿还到期公司债券本金[21河西03]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,中邮证券有限责任公司</t>
+          <t>华泰联合证券有限责任公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
@@ -5303,7 +5335,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>盐城市海兴集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>南京市河西新城区国有资产经营控股(集团)有限责任公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5313,10 +5345,14 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
-        </is>
-      </c>
-      <c r="AK23" s="3"/>
+          <t>2029-09-08</t>
+        </is>
+      </c>
+      <c r="AK23" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL23" s="3" t="inlineStr">
         <is>
           <t/>
@@ -5334,17 +5370,29 @@
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ23" s="3"/>
-      <c r="AR23" s="3"/>
-      <c r="AS23" s="3"/>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
           <t>基础建设</t>
@@ -5380,7 +5428,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26河西02</t>
+          <t>26平经03</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5390,62 +5438,62 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>283883.SH</t>
+          <t>283879.SH</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>45.47</v>
+        <v>31.78</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26河西01</t>
+          <t>26平经02</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>2.70Y</t>
+          <t>2.76Y+2.00Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.7209</t>
+          <t>1.7109</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/1.6900</t>
+          <t>1.7600/1.6600</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>南京市河西新城区国有资产经营控股(集团)有限责任公司</t>
+          <t>平湖经济技术开发区投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.86</t>
+          <t>D 3.20</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5455,7 +5503,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -5465,43 +5513,47 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>浙江省-嘉兴市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将不超过4.00亿元用于偿还到期公司债券本金[21河西03]</t>
+          <t>本期债券募集资金扣除发行费用后,公司拟将本期债券募集资金全部用于偿还公司债券本金[23平经03]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD24" s="3"/>
+          <t>中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr">
+        <is>
+          <t>平湖国发投控股集团有限公司</t>
+        </is>
+      </c>
       <c r="AE24" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -5519,7 +5571,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>南京市河西新城区国有资产经营控股(集团)有限责任公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>平湖经济技术开发区投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5529,14 +5581,10 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2029-09-08</t>
-        </is>
-      </c>
-      <c r="AK24" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-09</t>
+        </is>
+      </c>
+      <c r="AK24" s="3"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
           <t/>
@@ -5549,17 +5597,17 @@
       </c>
       <c r="AN24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5*无效</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
@@ -5569,12 +5617,12 @@
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
@@ -5584,17 +5632,17 @@
       </c>
       <c r="AU24" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-09</t>
         </is>
       </c>
       <c r="AV24" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW24" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX24" s="3" t="inlineStr">
@@ -5612,7 +5660,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26平经03</t>
+          <t>26周高01</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5622,64 +5670,52 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>283879.SH</t>
+          <t>283872.SH</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>2.00 ~ 2.80</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.72</v>
+        <v>2.24</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>31.78</v>
+        <v>83.78</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>26平经02</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>2.76Y+2.00Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.7109</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>1.7600/1.6600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>平湖经济技术开发区投资发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t>D 3.20</t>
-        </is>
-      </c>
+          <t>周口高新科技产业发展有限公司</t>
+        </is>
+      </c>
+      <c r="P25" s="3"/>
       <c r="Q25" s="3" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -5687,7 +5723,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -5704,38 +5740,34 @@
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
-        </is>
-      </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+          <t>2.16%~2.26%</t>
+        </is>
+      </c>
+      <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>浙江省-嘉兴市</t>
+          <t>河南省-周口市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,公司拟将本期债券募集资金全部用于偿还公司债券本金[23平经03]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司到期债务等监管机构认可的用途。</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3" t="inlineStr">
         <is>
-          <t>平湖国发投控股集团有限公司</t>
+          <t>河南中豫信用增进有限公司</t>
         </is>
       </c>
       <c r="AE25" s="3" t="inlineStr">
@@ -5755,7 +5787,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>平湖经济技术开发区投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>周口高新科技产业发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5786,37 +5818,21 @@
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>6.5*无效</t>
-        </is>
-      </c>
-      <c r="AQ25" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR25" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS25" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="AP25" s="3"/>
+      <c r="AQ25" s="3"/>
+      <c r="AR25" s="3"/>
+      <c r="AS25" s="3"/>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV25" s="3" t="inlineStr">
@@ -5826,7 +5842,7 @@
       </c>
       <c r="AW25" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX25" s="3" t="inlineStr">
@@ -5844,7 +5860,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26周高01</t>
+          <t>26张高02</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -5854,7 +5870,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>283872.SH</t>
+          <t>283818.SH</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -5863,30 +5879,38 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.80</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.24</v>
+        <v>1.9</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>83.78</v>
+        <v>49.78</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>26张高01</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>4.59Y</t>
+        </is>
+      </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.8746</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -5896,10 +5920,14 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>周口高新科技产业发展有限公司</t>
-        </is>
-      </c>
-      <c r="P26" s="3"/>
+          <t>张家港市高铁投资发展(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>B- 40.33</t>
+        </is>
+      </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -5924,36 +5952,36 @@
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>2.16%~2.26%</t>
-        </is>
-      </c>
-      <c r="Y26" s="3"/>
+          <t>1.96%~2.06%</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>河南省-周口市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司到期债务等监管机构认可的用途。</t>
+          <t>本期债券发行规模为不超过6亿元,募集资金在扣除发行费用后,拟用于偿还公司债券本金[23张高02]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD26" s="3" t="inlineStr">
-        <is>
-          <t>河南中豫信用增进有限公司</t>
-        </is>
-      </c>
+          <t>国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -5971,7 +5999,7 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>周口高新科技产业发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>张家港市高铁投资发展(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6002,16 +6030,32 @@
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="AP26" s="3"/>
-      <c r="AQ26" s="3"/>
-      <c r="AR26" s="3"/>
-      <c r="AS26" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>综合基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>综合基础设施投融资建设</t>
+        </is>
+      </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6021,7 +6065,7 @@
       </c>
       <c r="AV26" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW26" s="3" t="inlineStr">
@@ -6044,7 +6088,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26张高02</t>
+          <t>26西居01</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6054,47 +6098,47 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>283818.SH</t>
+          <t>283842.SH</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>49.78</v>
+        <v>59.47</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>26张高01</t>
+          <t>25西居01</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>4.59Y</t>
+          <t>3.62Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.8746</t>
+          <t>1.9656</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -6104,12 +6148,12 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>张家港市高铁投资发展(集团)有限公司</t>
+          <t>西安市安居建设管理集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>B- 40.33</t>
+          <t>D- 0.83</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6136,28 +6180,28 @@
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.96%~2.06%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过6亿元,募集资金在扣除发行费用后,拟用于偿还公司债券本金[23张高02]</t>
+          <t>本期债券募集资金规模为不超过5亿元(含5亿元),扣除发行费用后,拟全部用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
@@ -6183,7 +6227,7 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>张家港市高铁投资发展(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>西安市安居建设管理集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6193,10 +6237,14 @@
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
-        </is>
-      </c>
-      <c r="AK27" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK27" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL27" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6214,7 +6262,7 @@
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
@@ -6229,12 +6277,12 @@
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
@@ -6272,7 +6320,7 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26西居01</t>
+          <t>26西投K3(取消发行)</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6282,62 +6330,58 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>283842.SH</t>
+          <t>DY283805.SH</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.0</v>
+        <v>2.5</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>59.47</v>
-      </c>
+          <t>1.80 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>25西居01</t>
+          <t>26西投K1</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>3.62Y</t>
+          <t>4.90Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.9656</t>
+          <t>2.3599</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.3600/2.3300</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>西安市安居建设管理集团有限公司</t>
+          <t>西安投资控股有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>D- 0.83</t>
+          <t>C- 23.16</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6347,7 +6391,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -6364,17 +6408,17 @@
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>2.14%~2.24%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z28" s="3"/>
@@ -6385,12 +6429,12 @@
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金规模为不超过5亿元(含5亿元),扣除发行费用后,拟全部用于偿还有息债务。</t>
+          <t>本期债券的募集资金扣除相关发行费用后,拟将不低于70%募集资金用于置换前12个月内科技创新领域的基金出资款,剩余部分用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>中信证券股份有限公司,国投证券股份有限公司,首创证券股份有限公司,开源证券股份有限公司,联储证券股份有限公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
@@ -6411,7 +6455,7 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>西安市安居建设管理集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>西安投资控股有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)(品种二)(取消发行)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6421,14 +6465,10 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK28" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-09</t>
+        </is>
+      </c>
+      <c r="AK28" s="3"/>
       <c r="AL28" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6451,27 +6491,27 @@
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6504,7 +6544,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26西投K3(取消发行)</t>
+          <t>26徐经01</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6514,7 +6554,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>DY283805.SH</t>
+          <t>283791.SH</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -6523,49 +6563,53 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.5</v>
+        <v>13.0</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>52.78</v>
+      </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26西投K1</t>
+          <t>24徐州经开PPN002</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>4.90Y</t>
+          <t>2.88Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>2.3599</t>
+          <t>1.7945</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>2.3600/2.3300</t>
+          <t>1.8200/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>西安投资控股有限公司</t>
+          <t>徐州经济技术开发区国有资产经营有限责任公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C- 23.16</t>
+          <t>C 27.93</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6575,7 +6619,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6597,7 +6641,7 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>2.14%~2.24%</t>
+          <t>1.99%~2.09%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6608,17 +6652,17 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>江苏省-徐州市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金扣除相关发行费用后,拟将不低于70%募集资金用于置换前12个月内科技创新领域的基金出资款,剩余部分用于偿还有息债务</t>
+          <t>本次公司债券募集资金扣除发行费用后,拟将13.00亿元用于偿还到期的公司债券本金。[23徐经01]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国投证券股份有限公司,首创证券股份有限公司,开源证券股份有限公司,联储证券股份有限公司,国金证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司,中国国际金融股份有限公司,东吴证券股份有限公司,广发证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
@@ -6639,7 +6683,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>西安投资控股有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)(品种二)(取消发行)</t>
+          <t>徐州经济技术开发区国有资产经营有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6670,32 +6714,32 @@
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6728,68 +6772,72 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26徐经01</t>
+          <t>26南新06</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>09-07 19:00</t>
+          <t>09-07 18:30</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>283791.SH</t>
+          <t>283665.SH</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>13.0</v>
+        <v>2.6</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>57.47</v>
+      </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>24徐州经开PPN002</t>
+          <t>26南新05</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2.88Y</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.7945</t>
+          <t>1.8290</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>1.8200/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>徐州经济技术开发区国有资产经营有限责任公司</t>
+          <t>重庆市南部新城产业投资集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C 27.93</t>
+          <t>C- 17.10</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6809,19 +6857,19 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.99%~2.09%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -6832,17 +6880,17 @@
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>江苏省-徐州市</t>
+          <t>重庆市-巴南区</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本次公司债券募集资金扣除发行费用后,拟将13.00亿元用于偿还到期的公司债券本金。[23徐经01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,仅全部用于偿还“25南新D6”到期的公司债本金[25 南新D3,21 南新02,23 南司02,21 南司02,25 南新D4,25 南新D5,25 南新D6,23 南新03,26 南新D1]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中国国际金融股份有限公司,东吴证券股份有限公司,广发证券股份有限公司,中信证券股份有限公司</t>
+          <t>华源证券股份有限公司,西南证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
@@ -6863,7 +6911,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>徐州经济技术开发区国有资产经营有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>重庆市南部新城产业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第六期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -6873,10 +6921,14 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
-        </is>
-      </c>
-      <c r="AK30" s="3"/>
+          <t>2029-09-08</t>
+        </is>
+      </c>
+      <c r="AK30" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL30" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6889,7 +6941,7 @@
       </c>
       <c r="AN30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO30" s="3" t="inlineStr">
@@ -6904,22 +6956,22 @@
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -6952,57 +7004,57 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26南新06</t>
+          <t>义乌KY02</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:30</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>283665.SH</t>
+          <t>282563.SH</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.6</v>
+        <v>5.0</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>57.47</v>
+        <v>56.78</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>26南新05</t>
+          <t>26义乌Y1</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>2.73Y+N</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.8290</t>
+          <t>1.8069</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -7012,12 +7064,12 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>重庆市南部新城产业投资集团有限公司</t>
+          <t>义乌市国有资本运营有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C- 17.10</t>
+          <t>B- 35.38</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7044,33 +7096,37 @@
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>1.91%~2.01%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z31" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>重庆市-巴南区</t>
+          <t>浙江省-金华市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,仅全部用于偿还“25南新D6”到期的公司债本金[25 南新D3,21 南新02,23 南司02,21 南司02,25 南新D4,25 南新D5,25 南新D6,23 南新03,26 南新D1]</t>
+          <t>本期债券发行规模不超过5亿元(含5亿元),拟将募集资金不低于70%通过基金出资用于支持科技创新领域发展(含置换发行前12个月内用于支持科技创新领域发展的基金出资),剩余不超过30%用于偿还到期债务。</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>华源证券股份有限公司,西南证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
@@ -7091,7 +7147,7 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>重庆市南部新城产业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第六期)</t>
+          <t>义乌市国有资本运营有限公司2026年面向专业投资者非公开发行科技创新可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7101,14 +7157,10 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2029-09-08</t>
-        </is>
-      </c>
-      <c r="AK31" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-08</t>
+        </is>
+      </c>
+      <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7116,7 +7168,7 @@
       </c>
       <c r="AM31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AN31" s="3" t="inlineStr">
@@ -7166,12 +7218,12 @@
       </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX31" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY31" s="3" t="inlineStr">
@@ -7184,7 +7236,7 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>义乌KY02</t>
+          <t>26资产K2</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7194,12 +7246,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>282563.SH</t>
+          <t>520454.SZ</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
@@ -7208,48 +7260,48 @@
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>56.78</v>
+        <v>89.78</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26义乌Y1</t>
+          <t>26资产K1</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2.73Y+N</t>
+          <t>4.72Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.8069</t>
+          <t>2.1235</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.3900/2.0900</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>义乌市国有资本运营有限公司</t>
+          <t>资阳产业投资集团有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>B- 35.38</t>
+          <t>B+ 56.67</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7269,47 +7321,51 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.91%~2.01%</t>
+          <t>2.27%~2.37%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
+          <t>四川省-资阳市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过5亿元(含5亿元),拟将募集资金不低于70%通过基金出资用于支持科技创新领域发展(含置换发行前12个月内用于支持科技创新领域发展的基金出资),剩余不超过30%用于偿还到期债务。</t>
+          <t>本期公司债券募集资金扣除发行费用后,发行人将不低于(含)3.50亿元的募集资金通过发行人子公司对投资于科技创新类企业的基金出资或用于置换一年以内投资于科技创新企业的基金出资,剩余不超过(含)1.50亿元的募集资金用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD32" s="3"/>
+          <t>天风证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr">
+        <is>
+          <t>中合中小企业融资担保股份有限公司</t>
+        </is>
+      </c>
       <c r="AE32" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -7322,12 +7378,12 @@
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>义乌市国有资本运营有限公司2026年面向专业投资者非公开发行科技创新可续期公司债券(第一期)</t>
+          <t>资阳产业投资集团有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7337,7 +7393,7 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
+          <t>2031-09-09</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
@@ -7348,22 +7404,22 @@
       </c>
       <c r="AM32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
@@ -7373,12 +7429,12 @@
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
@@ -7393,17 +7449,17 @@
       </c>
       <c r="AV32" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX32" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY32" s="3" t="inlineStr">
@@ -7416,7 +7472,7 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26资产K2</t>
+          <t>26西投K2</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7426,62 +7482,62 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>520454.SZ</t>
+          <t>283804.SH</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.0</v>
+        <v>2.5</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.60 ~ 2.30</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>89.78</v>
+        <v>70.47</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26资产K1</t>
+          <t>26西投01</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>4.72Y</t>
+          <t>4.77Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>2.1235</t>
+          <t>2.3710</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>2.3900/2.0900</t>
+          <t>--/2.0900</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>资阳产业投资集团有限公司</t>
+          <t>西安投资控股有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>B+ 56.67</t>
+          <t>C- 23.16</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7491,7 +7547,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -7508,12 +7564,12 @@
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>2.27%~2.37%</t>
+          <t>1.96%~2.06%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -7521,31 +7577,23 @@
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z33" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>四川省-资阳市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,发行人将不低于(含)3.50亿元的募集资金通过发行人子公司对投资于科技创新类企业的基金出资或用于置换一年以内投资于科技创新企业的基金出资,剩余不超过(含)1.50亿元的募集资金用于偿还有息债务。</t>
+          <t>本期债券的募集资金扣除相关发行费用后,拟将不低于70%募集资金用于置换前12个月内科技创新领域的基金出资款,剩余部分用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD33" s="3" t="inlineStr">
-        <is>
-          <t>中合中小企业融资担保股份有限公司</t>
-        </is>
-      </c>
+          <t>中信证券股份有限公司,国投证券股份有限公司,首创证券股份有限公司,开源证券股份有限公司,联储证券股份有限公司,国金证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -7558,12 +7606,12 @@
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>资阳产业投资集团有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)</t>
+          <t>西安投资控股有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7573,10 +7621,14 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
-        </is>
-      </c>
-      <c r="AK33" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK33" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL33" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7599,7 +7651,7 @@
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
@@ -7629,7 +7681,7 @@
       </c>
       <c r="AV33" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW33" s="3" t="inlineStr">
@@ -7652,7 +7704,7 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26西投K2</t>
+          <t>26深铁10</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7662,62 +7714,62 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>283804.SH</t>
+          <t>520468.SZ</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+2</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>70.47</v>
+        <v>46.72</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26西投01</t>
+          <t>26深铁08</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>4.97Y+2.00Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>2.3710</t>
+          <t>2.0276</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>--/2.0900</t>
+          <t>2.1000/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>西安投资控股有限公司</t>
+          <t>深圳市地铁集团有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C- 23.16</t>
+          <t>C+ 32.18</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7744,33 +7796,37 @@
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.96%~2.06%</t>
+          <t>1.98%~2.08%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z34" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金扣除相关发行费用后,拟将不低于70%募集资金用于置换前12个月内科技创新领域的基金出资款,剩余部分用于偿还有息债务</t>
+          <t>本期债券发行规模不超过15亿元(含)，扣除发行费用后拟用于偿还公司有息债务[23深铁13,25深圳地铁MTN003A,25深圳地铁MTN003B,24深圳地铁MTN007A,24深圳地铁MTN007B]</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国投证券股份有限公司,首创证券股份有限公司,开源证券股份有限公司,联储证券股份有限公司,国金证券股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
@@ -7786,12 +7842,12 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>西安投资控股有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)(品种一)</t>
+          <t>深圳市地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种二)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -7801,14 +7857,10 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK34" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2033-09-09</t>
+        </is>
+      </c>
+      <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7816,7 +7868,7 @@
       </c>
       <c r="AM34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AN34" s="3" t="inlineStr">
@@ -7826,37 +7878,37 @@
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-09</t>
         </is>
       </c>
       <c r="AV34" s="3" t="inlineStr">
@@ -7866,7 +7918,7 @@
       </c>
       <c r="AW34" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX34" s="3" t="inlineStr">
@@ -7884,7 +7936,7 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26深铁10</t>
+          <t>26横琴Y3</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -7894,62 +7946,62 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>520468.SZ</t>
+          <t>283861.SH</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>5+2</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>7.5</v>
+        <v>11.0</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>46.72</v>
+        <v>65.47</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>26深铁08</t>
+          <t>26横琴Y2</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>4.97Y+2.00Y</t>
+          <t>2.89Y+N</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>2.0276</t>
+          <t>1.9244</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>2.1000/--</t>
+          <t>--/1.9000</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>深圳市地铁集团有限公司</t>
+          <t>珠海大横琴集团有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.18</t>
+          <t>B- 37.79</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -7959,7 +8011,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -7976,12 +8028,12 @@
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.98%~2.08%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -7989,24 +8041,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z35" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>广东省-珠海市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过15亿元(含)，扣除发行费用后拟用于偿还公司有息债务[23深铁13,25深圳地铁MTN003A,25深圳地铁MTN003B,24深圳地铁MTN007A,24深圳地铁MTN007B]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司有息债务。</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>招商证券股份有限公司,国金证券股份有限公司,华泰联合证券有限责任公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
@@ -8022,12 +8070,12 @@
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>深圳市地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种二)</t>
+          <t>珠海大横琴集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8037,10 +8085,14 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2033-09-09</t>
-        </is>
-      </c>
-      <c r="AK35" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK35" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL35" s="3" t="inlineStr">
         <is>
           <t/>
@@ -8063,7 +8115,7 @@
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
@@ -8073,22 +8125,22 @@
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV35" s="3" t="inlineStr">
@@ -8098,7 +8150,7 @@
       </c>
       <c r="AW35" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX35" s="3" t="inlineStr">
@@ -8116,7 +8168,7 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26横琴Y3</t>
+          <t>26核保02</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8126,62 +8178,62 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>283861.SH</t>
+          <t>246006.SH</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>11.0</v>
+        <v>5.0</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>65.47</v>
+        <v>49.19</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26横琴Y2</t>
+          <t>26核保01</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2.89Y+N</t>
+          <t>1.36Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.9244</t>
+          <t>1.9000</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/1.9000</t>
+          <t>1.9900/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>珠海大横琴集团有限公司</t>
+          <t>中核商业保理有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>B- 37.79</t>
+          <t>D+ 6.12</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8201,40 +8253,40 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>广东省-珠海市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司有息债务。</t>
+          <t>本期债券募集资金5亿元拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>招商证券股份有限公司,国金证券股份有限公司,华泰联合证券有限责任公司</t>
+          <t>招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
@@ -8245,7 +8297,7 @@
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr">
@@ -8255,24 +8307,20 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>珠海大横琴集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第三期)</t>
+          <t>中核商业保理有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK36" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2028-09-08</t>
+        </is>
+      </c>
+      <c r="AK36" s="3"/>
       <c r="AL36" s="3" t="inlineStr">
         <is>
           <t/>
@@ -8280,42 +8328,38 @@
       </c>
       <c r="AM36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AN36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP36" s="3"/>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>保理</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>保理</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8330,7 +8374,7 @@
       </c>
       <c r="AW36" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX36" s="3" t="inlineStr">
@@ -8348,7 +8392,7 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26核保02</t>
+          <t>26德兴01</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8358,12 +8402,12 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>246006.SH</t>
+          <t>283890.SH</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
@@ -8372,48 +8416,48 @@
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.73</v>
+        <v>2.21</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>49.19</v>
+        <v>80.78</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>26核保01</t>
+          <t>25德兴02</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>1.36Y</t>
+          <t>4.19Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.9000</t>
+          <t>2.1649</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>1.9900/--</t>
+          <t>2.2000/--</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>中核商业保理有限公司</t>
+          <t>德兴市投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>D+ 6.12</t>
+          <t>B- 47.40</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8433,43 +8477,51 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>2.25%~2.35%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江西省-上饶市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金5亿元拟用于偿还有息债务</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券的本金[23德兴02]</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>招商证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD37" s="3"/>
+          <t>长城证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr">
+        <is>
+          <t>德兴市铜都国资运营控股发展有限公司</t>
+        </is>
+      </c>
       <c r="AE37" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -8477,7 +8529,7 @@
       </c>
       <c r="AF37" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG37" s="3" t="inlineStr">
@@ -8487,17 +8539,17 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>中核商业保理有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>德兴市投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2028-09-08</t>
+          <t>2031-09-09</t>
         </is>
       </c>
       <c r="AK37" s="3"/>
@@ -8508,38 +8560,42 @@
       </c>
       <c r="AM37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP37" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>保理</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>保理</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8549,7 +8605,7 @@
       </c>
       <c r="AV37" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW37" s="3" t="inlineStr">
@@ -8572,72 +8628,64 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26德兴01</t>
+          <t>26义乌农商三农债01A</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>09-07 19:00</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>283890.SH</t>
-        </is>
-      </c>
+          <t>09-07 18:00</t>
+        </is>
+      </c>
+      <c r="C38" s="3"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>80.78</v>
-      </c>
+          <t>1.40 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>25德兴02</t>
+          <t>24义乌农商三农债02</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>4.19Y</t>
+          <t>1.23Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>2.1649</t>
+          <t>1.5344</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>2.2000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>德兴市投资控股集团有限公司</t>
+          <t>浙江义乌农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>B- 47.40</t>
+          <t>D 4.33</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8647,7 +8695,7 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -8664,17 +8712,17 @@
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>2.25%~2.35%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
@@ -8684,55 +8732,55 @@
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>江西省-上饶市</t>
+          <t>浙江省-金华市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券的本金[23德兴02]</t>
+          <t>本期债券募集资金将依据适用法律和监管部门的批准用于发放涉农贷款</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD38" s="3" t="inlineStr">
-        <is>
-          <t>德兴市铜都国资运营控股发展有限公司</t>
-        </is>
-      </c>
+          <t>中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>德兴市投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>2026年浙江义乌农村商业银行股份有限公司"三农"专项金融债券(品种一)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
-        </is>
-      </c>
-      <c r="AK38" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK38" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL38" s="3" t="inlineStr">
         <is>
           <t/>
@@ -8740,7 +8788,7 @@
       </c>
       <c r="AM38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AN38" s="3" t="inlineStr">
@@ -8750,32 +8798,32 @@
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -8785,7 +8833,7 @@
       </c>
       <c r="AV38" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW38" s="3" t="inlineStr">
@@ -8808,7 +8856,7 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26义乌农商三农债01A</t>
+          <t>26川高速SCP001</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8816,56 +8864,66 @@
           <t>09-07 18:00</t>
         </is>
       </c>
-      <c r="C39" s="3"/>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>012682211.IB</t>
+        </is>
+      </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F39" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
+          <t>1.30 ~ 1.50</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>19.09</v>
+      </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>24义乌农商三农债02</t>
+          <t>21川高速MTN008</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>1.23Y</t>
+          <t>80D</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.5344</t>
+          <t>1.4955</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5000/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>浙江义乌农村商业银行股份有限公司</t>
+          <t>四川高速公路建设开发集团有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>D 4.33</t>
+          <t>C- 20.05</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -8885,55 +8943,55 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U39" s="3"/>
-      <c r="V39" s="3"/>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U39" s="4" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z39" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金将依据适用法律和监管部门的批准用于发放涉农贷款</t>
+          <t>发行人本期债务融资工具拟募集资金10亿元,拟全部用于偿付到期债务融资工具【21川高速MTN007】</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>中国光大银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG39" s="3" t="inlineStr">
@@ -8943,7 +9001,7 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>2026年浙江义乌农村商业银行股份有限公司"三农"专项金融债券(品种一)</t>
+          <t>四川高速公路建设开发集团有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -8953,57 +9011,53 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK39" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="AK39" s="3"/>
       <c r="AL39" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AN39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>农商行</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -9036,70 +9090,70 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26川高速SCP001</t>
+          <t>26沈阳地铁MTN004</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-08 18:00</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>012682211.IB</t>
+          <t>102683539.IB</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>2.00 ~ 2.70</t>
         </is>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>21川高速MTN008</t>
+          <t>24沈阳地铁MTN006B</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>80D</t>
+          <t>4.95Y+N</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.4955</t>
+          <t>2.3096</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>1.5000/--</t>
+          <t>--/2.2500</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>四川高速公路建设开发集团有限公司</t>
+          <t>沈阳地铁集团有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C- 20.05</t>
+          <t>C+ 30.06</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9119,19 +9173,19 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>2.22%~2.32%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -9139,26 +9193,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z40" s="3"/>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>辽宁省-沈阳市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具拟募集资金10亿元,拟全部用于偿付到期债务融资工具【21川高速MTN007】</t>
+          <t>本期中期票据基础发行规模为人民币0亿元,发行金额上限为人民币15亿元,本次债券募集资金拟用于偿还公司有息债务。[24沈阳地铁MTN007,25沈阳地铁MTN004]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>中国邮政储蓄银行股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
@@ -9173,7 +9231,7 @@
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>四川高速公路建设开发集团有限公司2026年度第一期超短期融资券</t>
+          <t>沈阳地铁集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -9183,78 +9241,78 @@
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2031-09-09</t>
         </is>
       </c>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3" t="inlineStr">
         <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AM40" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AN40" s="3" t="inlineStr">
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ40" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>铁路运输</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AX40" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY40" s="3" t="inlineStr">
         <is>
           <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AO40" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP40" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ40" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR40" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AS40" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AT40" s="3" t="inlineStr">
-        <is>
-          <t>高速公路</t>
-        </is>
-      </c>
-      <c r="AU40" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV40" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW40" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX40" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY40" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AZ40" s="3"/>
@@ -9262,70 +9320,74 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26沈阳地铁MTN004</t>
+          <t>26厦门产投MTN003(科创债)</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>09-08 18:00</t>
+          <t>09-07 18:00</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>102683539.IB</t>
+          <t>102683466.IB</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>46.78</v>
+      </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>24沈阳地铁MTN006B</t>
+          <t>26厦门产投MTN002(科创债)</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>4.95Y+N</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>2.3096</t>
+          <t>1.8952</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8900/1.8700</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>沈阳地铁集团有限公司</t>
+          <t>厦门市产业投资有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.06</t>
+          <t>A 70.17</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9335,7 +9397,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 11:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -9345,11 +9407,15 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U41" s="3"/>
-      <c r="V41" s="3"/>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U41" s="4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V41" s="4" t="n">
+        <v>1.2</v>
+      </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
           <t>5-</t>
@@ -9357,7 +9423,7 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>2.22%~2.32%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -9372,17 +9438,17 @@
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>辽宁省-沈阳市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为人民币0亿元,发行金额上限为人民币15亿元,本次债券募集资金拟用于偿还公司有息债务。[24沈阳地铁MTN007,25沈阳地铁MTN004]</t>
+          <t>本期科技创新债券发行金额为5亿元，本期发行的募集资金扣除承销费后，拟全部用于科技创新领域股权投资以及置换发行人本期科技创新债券发行之日起一年以内科技创新领域股权投资；本期债券募集资金中5亿元拟用于对中创新航科技（福建）有限公司的科技创新领域股权投资以及置换一年之内的自有资金投入。</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>中国邮政储蓄银行股份有限公司,光大证券股份有限公司</t>
+          <t>兴业银行股份有限公司,厦门银行股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
@@ -9403,7 +9469,7 @@
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>沈阳地铁集团有限公司2026年度第四期中期票据</t>
+          <t>厦门市产业投资有限公司2026年度第三期科技创新债券</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
@@ -9413,53 +9479,49 @@
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
+          <t>2031-09-08</t>
         </is>
       </c>
       <c r="AK41" s="3"/>
       <c r="AL41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP41" s="3"/>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU41" s="3" t="inlineStr">
@@ -9474,7 +9536,7 @@
       </c>
       <c r="AW41" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX41" s="3" t="inlineStr">
@@ -9484,7 +9546,7 @@
       </c>
       <c r="AY41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AZ41" s="3"/>
@@ -9492,7 +9554,7 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26厦门产投MTN003(科创债)</t>
+          <t>26金融街MTN005A</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -9502,60 +9564,60 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>102683466.IB</t>
+          <t>102683543.IB</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2+2</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>5.0</v>
+        <v>5.3</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>5.0</v>
+        <v>5.3</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>2.05 ~ 2.75</t>
         </is>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>26厦门产投MTN002(科创债)</t>
+          <t>26金融街MTN004A</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>1.93Y+2.00Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.8952</t>
+          <t>2.5181</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>1.8900/1.8700</t>
+          <t>--/2.4800</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>厦门市产业投资有限公司</t>
+          <t>金融街控股股份有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>A 70.17</t>
+          <t>C- 22.25</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9565,7 +9627,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>09-07 11:00</t>
+          <t>09-07 14:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -9582,12 +9644,12 @@
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>2.54%~2.64%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
@@ -9602,17 +9664,17 @@
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债券发行金额为5亿元，本期发行的募集资金扣除承销费后，拟全部用于科技创新领域股权投资以及置换发行人本期科技创新债券发行之日起一年以内科技创新领域股权投资；本期债券募集资金中5亿元拟用于对中创新航科技（福建）有限公司的科技创新领域股权投资以及置换一年之内的自有资金投入。</t>
+          <t>本期中期票据基础发行规模为0亿元，发行规模上限为10.30亿元，拟将募集资金全部用于偿还发行人债务融资工具的本金和利息[23金融街MTN006]</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,厦门银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
@@ -9633,7 +9695,7 @@
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>厦门市产业投资有限公司2026年度第三期科技创新债券</t>
+          <t>金融街控股股份有限公司2026年度第五期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
@@ -9643,10 +9705,14 @@
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
-        </is>
-      </c>
-      <c r="AK42" s="3"/>
+          <t>2030-09-08</t>
+        </is>
+      </c>
+      <c r="AK42" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL42" s="3" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -9664,33 +9730,37 @@
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP42" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>住宅楼房</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU42" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2028-09-08</t>
         </is>
       </c>
       <c r="AV42" s="3" t="inlineStr">
@@ -9700,7 +9770,7 @@
       </c>
       <c r="AW42" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX42" s="3" t="inlineStr">
@@ -9713,77 +9783,77 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AZ42" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ42" s="3"/>
     </row>
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26金融街MTN005A</t>
+          <t>26黄发04</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>102683543.IB</t>
+          <t>283938.SH</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>2+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>5.3</v>
-      </c>
+        <v>6.75</v>
+      </c>
+      <c r="F43" s="3"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2.05 ~ 2.75</t>
-        </is>
-      </c>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>73.78</v>
+      </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>26金融街MTN004A</t>
+          <t>26黄发01</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>1.93Y+2.00Y</t>
+          <t>4.51Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>2.5181</t>
+          <t>2.0891</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>--/2.4800</t>
+          <t>--/2.0900</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司</t>
+          <t>黄石市城市发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C- 22.25</t>
+          <t>B- 37.13</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -9793,7 +9863,7 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>09-07 14:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -9810,43 +9880,39 @@
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>2.54%~2.64%</t>
+          <t>2.19%~2.29%</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z43" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>湖北省-黄石市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为0亿元，发行规模上限为10.30亿元，拟将募集资金全部用于偿还发行人债务融资工具的本金和利息[23金融街MTN006]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金[26黄发D2,26黄发D1]</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司</t>
+          <t>西部证券股份有限公司,华源证券股份有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
@@ -9856,32 +9922,28 @@
       </c>
       <c r="AG43" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司2026年度第五期中期票据(品种一)</t>
+          <t>黄石市城市发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2030-09-08</t>
-        </is>
-      </c>
-      <c r="AK43" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-08</t>
+        </is>
+      </c>
+      <c r="AK43" s="3"/>
       <c r="AL43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t/>
         </is>
       </c>
       <c r="AM43" s="3" t="inlineStr">
@@ -9896,37 +9958,37 @@
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>住宅楼房</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
         <is>
-          <t>2028-09-08</t>
+          <t/>
         </is>
       </c>
       <c r="AV43" s="3" t="inlineStr">
@@ -9936,7 +9998,7 @@
       </c>
       <c r="AW43" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX43" s="3" t="inlineStr">
@@ -9954,7 +10016,7 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26黄发04</t>
+          <t>26光明建发02</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -9964,62 +10026,62 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>283938.SH</t>
+          <t>520463.SZ</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>6.75</v>
+        <v>5.0</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>2.14</v>
+        <v>1.61</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>73.78</v>
+        <v>20.78</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>26黄发01</t>
+          <t>26光明建发01</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>4.51Y</t>
+          <t>2.42Y+2.00Y</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>2.0891</t>
+          <t>1.7626</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>--/2.0900</t>
+          <t>--/1.7000</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>黄石市城市发展投资集团有限公司</t>
+          <t>深圳市光明区建设发展集团有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>B- 37.13</t>
+          <t>B+ 60.00</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10039,19 +10101,19 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>2.19%~2.29%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
@@ -10059,20 +10121,24 @@
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z44" s="3"/>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>湖北省-黄石市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金[26黄发D2,26黄发D1]</t>
+          <t>本期债券发行规模为不超过5亿元(含),发行人拟使用不少于4.7815亿元用于偿还公司有息债务,剩余部分用于补充公司本部及子公司生产经营所需流动资金</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>西部证券股份有限公司,华源证券股份有限公司</t>
+          <t>国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
@@ -10088,12 +10154,12 @@
       </c>
       <c r="AG44" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>黄石市城市发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>深圳市光明区建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -10103,7 +10169,7 @@
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
+          <t>2031-09-10</t>
         </is>
       </c>
       <c r="AK44" s="3"/>
@@ -10119,12 +10185,12 @@
       </c>
       <c r="AN44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP44" s="3" t="inlineStr">
@@ -10134,27 +10200,27 @@
       </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT44" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU44" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-10</t>
         </is>
       </c>
       <c r="AV44" s="3" t="inlineStr">
@@ -10164,7 +10230,7 @@
       </c>
       <c r="AW44" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX44" s="3" t="inlineStr">
@@ -10182,7 +10248,7 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26光明建发02</t>
+          <t>26深城01</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10192,7 +10258,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>520463.SZ</t>
+          <t>520466.SZ</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -10206,48 +10272,48 @@
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>20.78</v>
+        <v>40.78</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>26光明建发01</t>
+          <t>25深汕01</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>2.42Y+2.00Y</t>
+          <t>1.78Y+2.00Y</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.7626</t>
+          <t>1.6744</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>--/1.7000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>深圳市光明区建设发展集团有限公司</t>
+          <t>深圳市深汕特别合作区城市建设投资发展有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>B+ 60.00</t>
+          <t>D+ 8.57</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10257,7 +10323,7 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -10267,31 +10333,23 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3"/>
-      <c r="W45" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="W45" s="3"/>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>广东省-深圳市</t>
@@ -10299,15 +10357,19 @@
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过5亿元(含),发行人拟使用不少于4.7815亿元用于偿还公司有息债务,剩余部分用于补充公司本部及子公司生产经营所需流动资金</t>
+          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还回售的公司债券本金[23深汕01]</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD45" s="3"/>
+          <t>中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr">
+        <is>
+          <t>深圳市深担增信融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE45" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -10325,7 +10387,7 @@
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>深圳市光明区建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>深圳市深汕特别合作区城市建设投资发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
@@ -10335,7 +10397,7 @@
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
+          <t>2031-09-08</t>
         </is>
       </c>
       <c r="AK45" s="3"/>
@@ -10351,7 +10413,7 @@
       </c>
       <c r="AN45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO45" s="3" t="inlineStr">
@@ -10361,7 +10423,7 @@
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
@@ -10371,27 +10433,27 @@
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
         <is>
-          <t>2029-09-10</t>
+          <t>2029-09-08</t>
         </is>
       </c>
       <c r="AV45" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW45" s="3" t="inlineStr">
@@ -10414,7 +10476,7 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26深城01</t>
+          <t>26高城01</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -10424,12 +10486,12 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>520466.SZ</t>
+          <t>520464.SZ</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
@@ -10438,33 +10500,33 @@
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>40.78</v>
+        <v>48.47</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>25深汕01</t>
+          <t>24合高01</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>1.78Y+2.00Y</t>
+          <t>300D+2.00Y</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.6744</t>
+          <t>1.5586</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -10474,12 +10536,12 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>深圳市深汕特别合作区城市建设投资发展有限公司</t>
+          <t>合肥高新城市发展集团有限公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.57</t>
+          <t>C- 18.80</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10504,38 +10566,38 @@
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
-      <c r="W46" s="3"/>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>安徽省-合肥市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还回售的公司债券本金[23深汕01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司有息债务[23合高01]</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD46" s="3" t="inlineStr">
-        <is>
-          <t>深圳市深担增信融资担保有限公司</t>
-        </is>
-      </c>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD46" s="3"/>
       <c r="AE46" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -10553,7 +10615,7 @@
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>深圳市深汕特别合作区城市建设投资发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>合肥高新城市发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
@@ -10563,10 +10625,14 @@
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
-        </is>
-      </c>
-      <c r="AK46" s="3"/>
+          <t>2029-09-08</t>
+        </is>
+      </c>
+      <c r="AK46" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL46" s="3" t="inlineStr">
         <is>
           <t/>
@@ -10584,12 +10650,12 @@
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP46" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ46" s="3" t="inlineStr">
@@ -10599,12 +10665,12 @@
       </c>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT46" s="3" t="inlineStr">
@@ -10614,17 +10680,17 @@
       </c>
       <c r="AU46" s="3" t="inlineStr">
         <is>
-          <t>2029-09-08</t>
+          <t/>
         </is>
       </c>
       <c r="AV46" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW46" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX46" s="3" t="inlineStr">
@@ -10642,7 +10708,7 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26高城01</t>
+          <t>26黔高04</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10652,62 +10718,62 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>520464.SZ</t>
+          <t>246012.SH</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>48.47</v>
+        <v>43.78</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>24合高01</t>
+          <t>26贵州高速MTN003</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>300D+2.00Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>1.5586</t>
+          <t>1.8747</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8700/1.8600</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>合肥高新城市发展集团有限公司</t>
+          <t>贵州高速公路集团有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>C- 18.80</t>
+          <t>B- 45.72</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -10717,7 +10783,7 @@
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
@@ -10727,14 +10793,14 @@
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U47" s="3"/>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X47" s="3" t="inlineStr">
@@ -10744,23 +10810,23 @@
       </c>
       <c r="Y47" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z47" s="3"/>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>安徽省-合肥市</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司有息债务[23合高01]</t>
+          <t>本期债券募集资金10.00亿元拟用于偿还到期公司债券本金[23黔高02]</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>广发证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD47" s="3"/>
@@ -10776,29 +10842,25 @@
       </c>
       <c r="AG47" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>合肥高新城市发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>贵州高速公路集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ47" s="3" t="inlineStr">
         <is>
-          <t>2029-09-08</t>
-        </is>
-      </c>
-      <c r="AK47" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-09</t>
+        </is>
+      </c>
+      <c r="AK47" s="3"/>
       <c r="AL47" s="3" t="inlineStr">
         <is>
           <t/>
@@ -10811,12 +10873,12 @@
       </c>
       <c r="AN47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP47" s="3" t="inlineStr">
@@ -10831,17 +10893,17 @@
       </c>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT47" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU47" s="3" t="inlineStr">
@@ -10874,72 +10936,74 @@
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26黔高04</t>
+          <t>26苏农垦SCP018</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>09-07 19:00</t>
+          <t>09-07 18:00</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>246012.SH</t>
+          <t>012682213.IB</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.24Y</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F48" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>1.84</v>
+        <v>1.38</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>43.78</v>
+        <v>18.09</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>26贵州高速MTN003</t>
+          <t>26苏农垦SCP017</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>73D</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1.8747</t>
+          <t>1.4803</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>1.8700/1.8600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>贵州高速公路集团有限公司</t>
+          <t>江苏省农垦集团有限公司</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>B- 45.72</t>
+          <t>C 29.00</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -10949,7 +11013,7 @@
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
@@ -10959,19 +11023,23 @@
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U48" s="3"/>
-      <c r="V48" s="3"/>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U48" s="4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V48" s="4" t="n">
+        <v>1.08</v>
+      </c>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X48" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y48" s="3" t="inlineStr">
@@ -10982,23 +11050,23 @@
       <c r="Z48" s="3"/>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金10.00亿元拟用于偿还到期公司债券本金[23黔高02]</t>
+          <t>发行人本次拟发行5亿元超短期融资券，用于偿还发行人存量负债。</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>中国建设银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD48" s="3"/>
       <c r="AE48" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF48" s="3" t="inlineStr">
@@ -11008,12 +11076,12 @@
       </c>
       <c r="AG48" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>贵州高速公路集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
+          <t>江苏省农垦集团有限公司2026年度第十八期超短期融资券</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
@@ -11023,13 +11091,13 @@
       </c>
       <c r="AJ48" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="AK48" s="3"/>
       <c r="AL48" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM48" s="3" t="inlineStr">
@@ -11039,37 +11107,37 @@
       </c>
       <c r="AN48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP48" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ48" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>农林牧渔</t>
         </is>
       </c>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>综合农林牧渔</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>综合农林牧渔</t>
         </is>
       </c>
       <c r="AT48" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>种植业</t>
         </is>
       </c>
       <c r="AU48" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-07.xlsx
+++ b/data/credit_bond_all_2026-09-07.xlsx
@@ -700,7 +700,11 @@
           <t>09-07 18:00</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>292680029.IB</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -896,7 +900,11 @@
           <t>09-07 18:00</t>
         </is>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>292680030.IB</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -1583,8 +1591,12 @@
           <t>1.60 ~ 2.40</t>
         </is>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="H7" s="4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>63.19</v>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>2.02</t>
@@ -1640,8 +1652,12 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
+      <c r="U7" s="4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>1.25</v>
+      </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
           <t>8+</t>
@@ -1779,9 +1795,7 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AZ7" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ7" s="3"/>
     </row>
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
@@ -8018,22 +8032,22 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26沈阳地铁MTN004</t>
+          <t>26华电股SCP002</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>09-08 18:00</t>
+          <t>09-07 18:00</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>102683539.IB</t>
+          <t>012682212.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>0.31Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
@@ -8044,44 +8058,48 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
+          <t>1.30 ~ 1.46</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>13.13</v>
+      </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>24沈阳地铁MTN006B</t>
+          <t>24华电股MTN008</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>4.95Y+N</t>
+          <t>72D</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>2.3096</t>
+          <t>1.4600</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>2.6000/2.2000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>沈阳地铁集团有限公司</t>
+          <t>华电国际电力股份有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.03</t>
+          <t>B- 38.46</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8101,19 +8119,23 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U35" s="3"/>
-      <c r="V35" s="3"/>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U35" s="4" t="n">
+        <v>1.2533</v>
+      </c>
+      <c r="V35" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>2.22%~2.32%</t>
+          <t>1.44%~1.48%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -8121,35 +8143,31 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z35" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>辽宁省-沈阳市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为人民币0亿元,发行金额上限为人民币15亿元,本次债券募集资金拟用于偿还公司有息债务。[24沈阳地铁MTN007,25沈阳地铁MTN004]</t>
+          <t>本期发行金额为15亿元,募集资金拟全部用于偿还发行人到期债务及补充流动资金。</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>中国邮政储蓄银行股份有限公司,光大证券股份有限公司</t>
+          <t>中信银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
@@ -8159,7 +8177,7 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>沈阳地铁集团有限公司2026年度第四期中期票据</t>
+          <t>华电国际电力股份有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8169,53 +8187,53 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>火电</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -8230,7 +8248,7 @@
       </c>
       <c r="AW35" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX35" s="3" t="inlineStr">
@@ -8240,7 +8258,7 @@
       </c>
       <c r="AY35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AZ35" s="3"/>
@@ -8248,72 +8266,74 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26光明建发02</t>
+          <t>26沈阳地铁MTN004</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>09-07 19:00</t>
+          <t>09-08 18:00</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>520463.SZ</t>
+          <t>102683539.IB</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F36" s="3"/>
+        <v>15.0</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>15.0</v>
+      </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>2.00 ~ 2.70</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1.61</v>
+        <v>2.29</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>20.78</v>
+        <v>88.28</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26光明建发01</t>
+          <t>24沈阳地铁MTN006B</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2.42Y+2.00Y</t>
+          <t>4.95Y+N</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.7626</t>
+          <t>2.3096</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/1.7000</t>
+          <t>2.6000/2.2000</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>深圳市光明区建设发展集团有限公司</t>
+          <t>沈阳地铁集团有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>S+ 100.00</t>
+          <t>C+ 32.03</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8323,7 +8343,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8333,50 +8353,54 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U36" s="3"/>
-      <c r="V36" s="3"/>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U36" s="4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>1.16</v>
+      </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>2.22%~2.32%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>辽宁省-沈阳市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过5亿元(含),发行人拟使用不少于4.7815亿元用于偿还公司有息债务,剩余部分用于补充公司本部及子公司生产经营所需流动资金</t>
+          <t>本期中期票据基础发行规模为人民币0亿元,发行金额上限为人民币15亿元,本次债券募集资金拟用于偿还公司有息债务。[24沈阳地铁MTN007,25沈阳地铁MTN004]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司</t>
+          <t>中国邮政储蓄银行股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
@@ -8386,75 +8410,75 @@
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>深圳市光明区建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>沈阳地铁集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
+          <t>2031-09-09</t>
         </is>
       </c>
       <c r="AK36" s="3"/>
       <c r="AL36" s="3" t="inlineStr">
         <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>铁路运输</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM36" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AO36" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ36" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR36" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS36" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT36" s="3" t="inlineStr">
-        <is>
-          <t>房地产开发</t>
-        </is>
-      </c>
-      <c r="AU36" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-10</t>
-        </is>
-      </c>
       <c r="AV36" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -8462,7 +8486,7 @@
       </c>
       <c r="AW36" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX36" s="3" t="inlineStr">
@@ -8472,7 +8496,7 @@
       </c>
       <c r="AY36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AZ36" s="3"/>
@@ -8480,7 +8504,7 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26高城01</t>
+          <t>26光明建发02</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8490,64 +8514,62 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>520464.SZ</t>
+          <t>520463.SZ</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F37" s="4" t="n">
-        <v>5.0</v>
-      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>48.47</v>
+        <v>20.78</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>24合高01</t>
+          <t>26光明建发01</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>300D+2.00Y</t>
+          <t>2.42Y+2.00Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.5586</t>
+          <t>1.7626</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7000</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>合肥高新城市发展集团有限公司</t>
+          <t>深圳市光明区建设发展集团有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C- 17.24</t>
+          <t>S+ 100.00</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8557,7 +8579,7 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
@@ -8567,21 +8589,19 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U37" s="4" t="n">
-        <v>3.94</v>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="U37" s="3"/>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -8589,20 +8609,24 @@
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z37" s="3"/>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>安徽省-合肥市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司有息债务[23合高01]</t>
+          <t>本期债券发行规模为不超过5亿元(含),发行人拟使用不少于4.7815亿元用于偿还公司有息债务,剩余部分用于补充公司本部及子公司生产经营所需流动资金</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
@@ -8623,7 +8647,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>合肥高新城市发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>深圳市光明区建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8633,14 +8657,10 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2029-09-08</t>
-        </is>
-      </c>
-      <c r="AK37" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-10</t>
+        </is>
+      </c>
+      <c r="AK37" s="3"/>
       <c r="AL37" s="3" t="inlineStr">
         <is>
           <t/>
@@ -8653,12 +8673,12 @@
       </c>
       <c r="AN37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
@@ -8683,12 +8703,12 @@
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-10</t>
         </is>
       </c>
       <c r="AV37" s="3" t="inlineStr">
@@ -8698,7 +8718,7 @@
       </c>
       <c r="AW37" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX37" s="3" t="inlineStr">
@@ -8716,7 +8736,7 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26黔高04</t>
+          <t>26高城01</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8726,62 +8746,64 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>246012.SH</t>
+          <t>520464.SZ</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F38" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>43.78</v>
+        <v>48.47</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>26贵州高速MTN003</t>
+          <t>24合高01</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>300D+2.00Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.8747</t>
+          <t>1.5586</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>1.8700/1.8600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>贵州高速公路集团有限公司</t>
+          <t>合肥高新城市发展集团有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>B- 42.25</t>
+          <t>C- 17.24</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8791,7 +8813,7 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -8801,14 +8823,16 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U38" s="3"/>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U38" s="4" t="n">
+        <v>3.94</v>
+      </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
@@ -8818,23 +8842,23 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>安徽省-合肥市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金10.00亿元拟用于偿还到期公司债券本金[23黔高02]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司有息债务[23合高01]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
@@ -8850,25 +8874,29 @@
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>贵州高速公路集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
+          <t>合肥高新城市发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
-        </is>
-      </c>
-      <c r="AK38" s="3"/>
+          <t>2029-09-08</t>
+        </is>
+      </c>
+      <c r="AK38" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL38" s="3" t="inlineStr">
         <is>
           <t/>
@@ -8881,12 +8909,12 @@
       </c>
       <c r="AN38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
@@ -8901,17 +8929,17 @@
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -8944,74 +8972,72 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP018</t>
+          <t>26黔高04</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>012682213.IB</t>
+          <t>246012.SH</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>0.24Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F39" s="3"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1.38</v>
+        <v>1.84</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>18.09</v>
+        <v>43.78</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP017</t>
+          <t>26贵州高速MTN003</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>73D</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.4803</t>
+          <t>1.8747</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>1.5100/1.3992</t>
+          <t>1.8700/1.8600</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司</t>
+          <t>贵州高速公路集团有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C 27.39</t>
+          <t>B- 42.25</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9021,7 +9047,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -9031,23 +9057,19 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U39" s="4" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="V39" s="4" t="n">
-        <v>1.08</v>
-      </c>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
@@ -9058,23 +9080,23 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>发行人本次拟发行5亿元超短期融资券，用于偿还发行人存量负债。</t>
+          <t>本期债券募集资金10.00亿元拟用于偿还到期公司债券本金[23黔高02]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,华夏银行股份有限公司</t>
+          <t>广发证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -9084,12 +9106,12 @@
       </c>
       <c r="AG39" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司2026年度第十八期超短期融资券</t>
+          <t>贵州高速公路集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -9099,53 +9121,53 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2031-09-09</t>
         </is>
       </c>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AM39" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>种植业</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -9178,7 +9200,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26江苏广电SCP008</t>
+          <t>26苏农垦SCP018</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -9188,64 +9210,64 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>012682214.IB</t>
+          <t>012682213.IB</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>0.33Y</t>
+          <t>0.24Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.48</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>26.13</v>
+        <v>18.09</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>24苏广K1</t>
+          <t>26苏农垦SCP017</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>140D</t>
+          <t>73D</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.4946</t>
+          <t>1.4803</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>--/1.4700</t>
+          <t>1.5100/1.3992</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>江苏省广电有线信息网络股份有限公司</t>
+          <t>江苏省农垦集团有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C- 18.02</t>
+          <t>C 27.39</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9269,10 +9291,10 @@
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>1.1833</v>
+        <v>2.66</v>
       </c>
       <c r="V40" s="4" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
@@ -9281,7 +9303,7 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.46%~1.50%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -9297,12 +9319,12 @@
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期发行6亿元超短期融资券，全部用于偿还有息债务[26江苏广电SCP005]</t>
+          <t>发行人本次拟发行5亿元超短期融资券，用于偿还发行人存量负债。</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中国建设银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
@@ -9323,7 +9345,7 @@
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>江苏省广电有线信息网络股份有限公司2026年度第八期超短期融资券</t>
+          <t>江苏省农垦集团有限公司2026年度第十八期超短期融资券</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -9333,7 +9355,7 @@
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="AK40" s="3"/>
@@ -9359,27 +9381,27 @@
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>传媒</t>
+          <t>农林牧渔</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>广电</t>
+          <t>综合农林牧渔</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>广电</t>
+          <t>综合农林牧渔</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>种植业</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -9412,7 +9434,7 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26厦门产投MTN003(科创债)</t>
+          <t>26江苏广电SCP008</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9422,64 +9444,64 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>102683466.IB</t>
+          <t>012682214.IB</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.33Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.35 ~ 1.48</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1.87</v>
+        <v>1.48</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>46.78</v>
+        <v>26.13</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>26厦门产投MTN002(科创债)</t>
+          <t>24苏广K1</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>140D</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.8952</t>
+          <t>1.4946</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>1.8900/1.8700</t>
+          <t>--/1.4700</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>厦门市产业投资有限公司</t>
+          <t>江苏省广电有线信息网络股份有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>B 53.76</t>
+          <t>C- 18.02</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9489,7 +9511,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>09-07 11:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -9503,19 +9525,19 @@
         </is>
       </c>
       <c r="U41" s="4" t="n">
-        <v>4.2</v>
+        <v>1.1833</v>
       </c>
       <c r="V41" s="4" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.46%~1.50%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -9523,30 +9545,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z41" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债券发行金额为5亿元，本期发行的募集资金扣除承销费后，拟全部用于科技创新领域股权投资以及置换发行人本期科技创新债券发行之日起一年以内科技创新领域股权投资；本期债券募集资金中5亿元拟用于对中创新航科技（福建）有限公司的科技创新领域股权投资以及置换一年之内的自有资金投入。</t>
+          <t>本期发行6亿元超短期融资券，全部用于偿还有息债务[26江苏广电SCP005]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,厦门银行股份有限公司</t>
+          <t>南京银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF41" s="3" t="inlineStr">
@@ -9561,7 +9579,7 @@
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>厦门市产业投资有限公司2026年度第三期科技创新债券</t>
+          <t>江苏省广电有线信息网络股份有限公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
@@ -9571,7 +9589,7 @@
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
+          <t>2027-01-08</t>
         </is>
       </c>
       <c r="AK41" s="3"/>
@@ -9592,28 +9610,32 @@
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP41" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>传媒</t>
         </is>
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>广电</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>广电</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="AU41" s="3" t="inlineStr">
@@ -9646,7 +9668,7 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26华电股SCP002</t>
+          <t>26厦门产投MTN003(科创债)</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -9656,64 +9678,64 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>012682212.IB</t>
+          <t>102683466.IB</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>0.31Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.46</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1.35</v>
+        <v>1.87</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>13.13</v>
+        <v>46.78</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>24华电股MTN008</t>
+          <t>26厦门产投MTN002(科创债)</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>72D</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.4600</t>
+          <t>1.8952</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>1.4700/--</t>
+          <t>1.8900/1.8700</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>华电国际电力股份有限公司</t>
+          <t>厦门市产业投资有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>B- 38.46</t>
+          <t>B 53.76</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9723,7 +9745,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 11:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -9737,19 +9759,19 @@
         </is>
       </c>
       <c r="U42" s="4" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="V42" s="4" t="n">
-        <v>1.0</v>
+        <v>1.2</v>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>1.44%~1.48%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
@@ -9757,31 +9779,35 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z42" s="3"/>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额为15亿元,募集资金拟全部用于偿还发行人到期债务及补充流动资金。</t>
+          <t>本期科技创新债券发行金额为5亿元，本期发行的募集资金扣除承销费后，拟全部用于科技创新领域股权投资以及置换发行人本期科技创新债券发行之日起一年以内科技创新领域股权投资；本期债券募集资金中5亿元拟用于对中创新航科技（福建）有限公司的科技创新领域股权投资以及置换一年之内的自有资金投入。</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>兴业银行股份有限公司,厦门银行股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF42" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG42" s="3" t="inlineStr">
@@ -9791,7 +9817,7 @@
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>华电国际电力股份有限公司2026年度第二期超短期融资券</t>
+          <t>厦门市产业投资有限公司2026年度第三期科技创新债券</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
@@ -9801,7 +9827,7 @@
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2031-09-08</t>
         </is>
       </c>
       <c r="AK42" s="3"/>
@@ -9822,32 +9848,28 @@
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP42" s="3"/>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>火电</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU42" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-07.xlsx
+++ b/data/credit_bond_all_2026-09-07.xlsx
@@ -6141,7 +6141,7 @@
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>2.75</v>
+        <v>2.746</v>
       </c>
       <c r="V26" s="4" t="n">
         <v>1.25</v>
@@ -7226,7 +7226,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26义乌农商三农债01</t>
+          <t>26义乌农商三农债02</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>2621001.IB</t>
+          <t>2621002.IB</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -7245,10 +7245,10 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -7256,10 +7256,10 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>35.47</v>
+        <v>40.47</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>2026年浙江义乌农村商业银行股份有限公司"三农"专项金融债券(品种一)</t>
+          <t>2026年浙江义乌农村商业银行股份有限公司"三农"专项金融债券(品种二)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7464,74 +7464,72 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26义乌农商三农债02</t>
+          <t>26光明建发02</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>2621002.IB</t>
+          <t>520463.SZ</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F32" s="3"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>40.47</v>
+        <v>20.78</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>24义乌农商三农债02</t>
+          <t>26光明建发01</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>1.23Y</t>
+          <t>2.42Y+2.00Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.5344</t>
+          <t>1.7626</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7000</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>浙江义乌农村商业银行股份有限公司</t>
+          <t>深圳市光明区建设发展集团有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>D 4.00</t>
+          <t>S+ 100.00</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7541,7 +7539,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -7551,19 +7549,19 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7578,73 +7576,69 @@
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金将依据适用法律和监管部门的批准用于发放涉农贷款</t>
+          <t>本期债券发行规模为不超过5亿元(含),发行人拟使用不少于4.7815亿元用于偿还公司有息债务,剩余部分用于补充公司本部及子公司生产经营所需流动资金</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>2026年浙江义乌农村商业银行股份有限公司"三农"专项金融债券(品种二)</t>
+          <t>深圳市光明区建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK32" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-10</t>
+        </is>
+      </c>
+      <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AM32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
@@ -7654,27 +7648,27 @@
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>农商行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-10</t>
         </is>
       </c>
       <c r="AV32" s="3" t="inlineStr">
@@ -7684,7 +7678,7 @@
       </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX32" s="3" t="inlineStr">
@@ -7702,7 +7696,7 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26光明建发02</t>
+          <t>26高城01</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7712,62 +7706,64 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>520463.SZ</t>
+          <t>520464.SZ</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F33" s="3"/>
+      <c r="F33" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>20.78</v>
+        <v>48.47</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26光明建发01</t>
+          <t>24合高01</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>2.42Y+2.00Y</t>
+          <t>300D+2.00Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.7626</t>
+          <t>1.5586</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>--/1.7000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>深圳市光明区建设发展集团有限公司</t>
+          <t>合肥高新城市发展集团有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>S+ 100.00</t>
+          <t>C- 17.65</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7777,7 +7773,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -7787,19 +7783,21 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U33" s="3"/>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U33" s="4" t="n">
+        <v>3.94</v>
+      </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -7807,24 +7805,20 @@
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z33" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+      <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>安徽省-合肥市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过5亿元(含),发行人拟使用不少于4.7815亿元用于偿还公司有息债务,剩余部分用于补充公司本部及子公司生产经营所需流动资金</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司有息债务[23合高01]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
@@ -7845,7 +7839,7 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>深圳市光明区建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>合肥高新城市发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7855,10 +7849,14 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
-        </is>
-      </c>
-      <c r="AK33" s="3"/>
+          <t>2029-09-08</t>
+        </is>
+      </c>
+      <c r="AK33" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL33" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7871,12 +7869,12 @@
       </c>
       <c r="AN33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP33" s="3" t="inlineStr">
@@ -7901,12 +7899,12 @@
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
         <is>
-          <t>2029-09-10</t>
+          <t/>
         </is>
       </c>
       <c r="AV33" s="3" t="inlineStr">
@@ -7916,7 +7914,7 @@
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX33" s="3" t="inlineStr">
@@ -7934,22 +7932,22 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26高城01</t>
+          <t>26苏农垦SCP018</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>09-07 19:00</t>
+          <t>09-07 18:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>520464.SZ</t>
+          <t>012682213.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.24Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
@@ -7960,48 +7958,48 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.73</v>
+        <v>1.38</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>48.47</v>
+        <v>18.09</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>24合高01</t>
+          <t>26苏农垦SCP017</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>300D+2.00Y</t>
+          <t>73D</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.5586</t>
+          <t>1.4803</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5100/1.3992</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>合肥高新城市发展集团有限公司</t>
+          <t>江苏省农垦集团有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C- 17.65</t>
+          <t>C 26.94</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -8011,7 +8009,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -8025,44 +8023,46 @@
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="V34" s="3"/>
+        <v>2.66</v>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>1.08</v>
+      </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>安徽省-合肥市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司有息债务[23合高01]</t>
+          <t>发行人本次拟发行5亿元超短期融资券，用于偿还发行人存量负债。</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>中国建设银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -8072,32 +8072,28 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>合肥高新城市发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>江苏省农垦集团有限公司2026年度第十八期超短期融资券</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2029-09-08</t>
-        </is>
-      </c>
-      <c r="AK34" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2026-12-03</t>
+        </is>
+      </c>
+      <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM34" s="3" t="inlineStr">
@@ -8117,27 +8113,27 @@
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>农林牧渔</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>综合农林牧渔</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>综合农林牧渔</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>种植业</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -8170,7 +8166,7 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP018</t>
+          <t>26江苏广电SCP008</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8180,64 +8176,64 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>012682213.IB</t>
+          <t>012682214.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>0.24Y</t>
+          <t>0.33Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.35 ~ 1.48</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>18.09</v>
+        <v>26.13</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP017</t>
+          <t>24苏广K1</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>73D</t>
+          <t>140D</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.4803</t>
+          <t>1.4946</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>1.5100/1.3992</t>
+          <t>--/1.4700</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司</t>
+          <t>江苏省广电有线信息网络股份有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C 26.94</t>
+          <t>C 25.70</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8261,10 +8257,10 @@
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>2.66</v>
+        <v>1.1833</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
@@ -8273,7 +8269,7 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.46%~1.50%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -8289,12 +8285,12 @@
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>发行人本次拟发行5亿元超短期融资券，用于偿还发行人存量负债。</t>
+          <t>本期发行6亿元超短期融资券，全部用于偿还有息债务[26江苏广电SCP005]</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,华夏银行股份有限公司</t>
+          <t>南京银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
@@ -8315,7 +8311,7 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司2026年度第十八期超短期融资券</t>
+          <t>江苏省广电有线信息网络股份有限公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8325,7 +8321,7 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2027-01-08</t>
         </is>
       </c>
       <c r="AK35" s="3"/>
@@ -8351,27 +8347,27 @@
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>传媒</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>广电</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>广电</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>种植业</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -8404,7 +8400,7 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26江苏广电SCP008</t>
+          <t>26厦门产投MTN003(科创债)</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8414,64 +8410,64 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>012682214.IB</t>
+          <t>102683466.IB</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>0.33Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.48</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1.48</v>
+        <v>1.87</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>26.13</v>
+        <v>46.78</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>24苏广K1</t>
+          <t>26厦门产投MTN002(科创债)</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>140D</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.4946</t>
+          <t>1.8952</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/1.4700</t>
+          <t>1.8900/1.8700</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>江苏省广电有线信息网络股份有限公司</t>
+          <t>厦门市产业投资有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C 25.70</t>
+          <t>B+ 58.93</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8481,7 +8477,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 11:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8495,19 +8491,19 @@
         </is>
       </c>
       <c r="U36" s="4" t="n">
-        <v>1.1833</v>
+        <v>4.18</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.46%~1.50%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -8515,26 +8511,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z36" s="3"/>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期发行6亿元超短期融资券，全部用于偿还有息债务[26江苏广电SCP005]</t>
+          <t>本期科技创新债券发行金额为5亿元，本期发行的募集资金扣除承销费后，拟全部用于科技创新领域股权投资以及置换发行人本期科技创新债券发行之日起一年以内科技创新领域股权投资；本期债券募集资金中5亿元拟用于对中创新航科技（福建）有限公司的科技创新领域股权投资以及置换一年之内的自有资金投入。</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,兴业银行股份有限公司</t>
+          <t>兴业银行股份有限公司,厦门银行股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>江苏省广电有线信息网络股份有限公司2026年度第八期超短期融资券</t>
+          <t>厦门市产业投资有限公司2026年度第三期科技创新债券</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2031-09-08</t>
         </is>
       </c>
       <c r="AK36" s="3"/>
@@ -8580,32 +8580,28 @@
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP36" s="3"/>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>传媒</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>广电</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>广电</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8638,7 +8634,7 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26厦门产投MTN003(科创债)</t>
+          <t>26川高速SCP001</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8648,64 +8644,64 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>102683466.IB</t>
+          <t>012682211.IB</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.87</v>
+        <v>1.39</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>46.78</v>
+        <v>19.09</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>26厦门产投MTN002(科创债)</t>
+          <t>21川高速MTN008</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>80D</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.8952</t>
+          <t>1.4955</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>1.8900/1.8700</t>
+          <t>1.5000/--</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>厦门市产业投资有限公司</t>
+          <t>四川高速公路建设开发集团有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>B+ 58.93</t>
+          <t>C- 18.86</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8715,7 +8711,7 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>09-07 11:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
@@ -8729,19 +8725,19 @@
         </is>
       </c>
       <c r="U37" s="4" t="n">
-        <v>4.18</v>
+        <v>3.42</v>
       </c>
       <c r="V37" s="4" t="n">
-        <v>1.2</v>
+        <v>2.0</v>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -8749,30 +8745,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z37" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债券发行金额为5亿元，本期发行的募集资金扣除承销费后，拟全部用于科技创新领域股权投资以及置换发行人本期科技创新债券发行之日起一年以内科技创新领域股权投资；本期债券募集资金中5亿元拟用于对中创新航科技（福建）有限公司的科技创新领域股权投资以及置换一年之内的自有资金投入。</t>
+          <t>发行人本期债务融资工具拟募集资金10亿元,拟全部用于偿付到期债务融资工具【21川高速MTN007】</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,厦门银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
@@ -8787,7 +8779,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>厦门市产业投资有限公司2026年度第三期科技创新债券</t>
+          <t>四川高速公路建设开发集团有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8797,7 +8789,7 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="AK37" s="3"/>
@@ -8808,7 +8800,7 @@
       </c>
       <c r="AM37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AN37" s="3" t="inlineStr">
@@ -8818,28 +8810,32 @@
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP37" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8872,74 +8868,74 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26川高速SCP001</t>
+          <t>26核保02</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>012682211.IB</t>
+          <t>246006.SH</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>19.09</v>
+        <v>49.19</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>21川高速MTN008</t>
+          <t>26核保01</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>80D</t>
+          <t>1.36Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.4955</t>
+          <t>1.9000</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>1.5000/--</t>
+          <t>1.9900/--</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>四川高速公路建设开发集团有限公司</t>
+          <t>中核商业保理有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C- 18.86</t>
+          <t>D+ 5.09</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8949,7 +8945,7 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -8963,61 +8959,59 @@
         </is>
       </c>
       <c r="U38" s="4" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>5.44</v>
+      </c>
+      <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具拟募集资金10亿元,拟全部用于偿付到期债务融资工具【21川高速MTN007】</t>
+          <t>本期债券募集资金5亿元拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>四川高速公路建设开发集团有限公司2026年度第一期超短期融资券</t>
+          <t>中核商业保理有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -9027,13 +9021,13 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2028-09-08</t>
         </is>
       </c>
       <c r="AK38" s="3"/>
       <c r="AL38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AM38" s="3" t="inlineStr">
@@ -9048,32 +9042,28 @@
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP38" s="3"/>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>保理</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>保理</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -9106,74 +9096,74 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26核保02</t>
+          <t>26闽投MTN007</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>09-07 19:00</t>
+          <t>09-07 18:00</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>246006.SH</t>
+          <t>102683545.IB</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>49.19</v>
+        <v>31.47</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26核保01</t>
+          <t>19闽投MTN006</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>1.36Y</t>
+          <t>3.01Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.9000</t>
+          <t>1.6653</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>1.9900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>中核商业保理有限公司</t>
+          <t>福建省投资开发集团有限责任公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>D+ 5.09</t>
+          <t>C 25.10</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9183,7 +9173,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 10:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -9197,59 +9187,61 @@
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="V39" s="3"/>
+        <v>4.14</v>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金5亿元拟用于偿还有息债务</t>
+          <t>发行人本次发行规模为人民币10.00亿元，均用于偿还发行人有息债务及权属单位补充经营性现金流。</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>招商证券股份有限公司</t>
+          <t>兴业银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG39" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>中核商业保理有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>福建省投资开发集团有限责任公司2026年度第七期中期票据</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -9259,18 +9251,22 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2028-09-08</t>
-        </is>
-      </c>
-      <c r="AK39" s="3"/>
+          <t>2029-09-08</t>
+        </is>
+      </c>
+      <c r="AK39" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN39" s="3" t="inlineStr">
@@ -9280,28 +9276,32 @@
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP39" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>保理</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>保理</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>燃气</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -9334,7 +9334,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26闽投MTN007</t>
+          <t>26大宁MTN002</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -9344,64 +9344,64 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>102683545.IB</t>
+          <t>102683540.IB</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>10.0</v>
+        <v>13.35</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>10.0</v>
+        <v>13.35</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>31.47</v>
+        <v>28.78</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>19闽投MTN006</t>
+          <t>24大宁MTN001</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>3.01Y</t>
+          <t>2.98Y</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.6653</t>
+          <t>1.6973</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7200/--</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>福建省投资开发集团有限责任公司</t>
+          <t>上海大宁资产经营(集团)有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C 25.10</t>
+          <t>C- 14.82</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>09-07 10:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
@@ -9425,14 +9425,14 @@
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>4.14</v>
+        <v>4.2944</v>
       </c>
       <c r="V40" s="4" t="n">
-        <v>1.0</v>
+        <v>1.14</v>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
@@ -9442,23 +9442,23 @@
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>上海市-静安区</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行规模为人民币10.00亿元，均用于偿还发行人有息债务及权属单位补充经营性现金流。</t>
+          <t>发行人本次中期票据发行规模人民币13.35亿元,全部用于偿还发行人到期债务融资工具本金[23大宁MTN001]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,上海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>福建省投资开发集团有限责任公司2026年度第七期中期票据</t>
+          <t>上海大宁资产经营(集团)有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -9489,64 +9489,60 @@
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
+          <t>2031-09-08</t>
+        </is>
+      </c>
+      <c r="AK40" s="3"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ40" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
           <t>2029-09-08</t>
         </is>
       </c>
-      <c r="AK40" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
-      <c r="AL40" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AM40" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AO40" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP40" s="3" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="AQ40" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR40" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS40" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT40" s="3" t="inlineStr">
-        <is>
-          <t>燃气</t>
-        </is>
-      </c>
-      <c r="AU40" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV40" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -9554,7 +9550,7 @@
       </c>
       <c r="AW40" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX40" s="3" t="inlineStr">
@@ -9572,7 +9568,7 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26大宁MTN002</t>
+          <t>26皖交控MTN008</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9582,64 +9578,64 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>102683540.IB</t>
+          <t>102683542.IB</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>30Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>13.35</v>
+        <v>10.0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>13.35</v>
+        <v>10.0</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>2.00 ~ 2.50</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1.69</v>
+        <v>2.34</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>28.78</v>
+        <v>20.75</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>24大宁MTN001</t>
+          <t>26皖交控MTN005</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>2.98Y</t>
+          <t>29.84Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.6973</t>
+          <t>2.3621</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>1.7200/--</t>
+          <t>2.3800/--</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>上海大宁资产经营(集团)有限公司</t>
+          <t>安徽省交通控股集团有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>C- 14.82</t>
+          <t>C- 23.53</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9663,40 +9659,38 @@
         </is>
       </c>
       <c r="U41" s="4" t="n">
-        <v>4.2944</v>
-      </c>
-      <c r="V41" s="4" t="n">
-        <v>1.14</v>
-      </c>
+        <v>2.98</v>
+      </c>
+      <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>2.27%~2.37%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>上海市-静安区</t>
+          <t>安徽省</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据发行规模人民币13.35亿元,全部用于偿还发行人到期债务融资工具本金[23大宁MTN001]</t>
+          <t>本期债券发行规模10亿元，其中37,000万元拟用于补充营运资金，7,057.5万元拟用于偿还银行借款本金，4,300万元拟用于偿还债券利息，51,642.5万元拟用于偿还银行借款利息。[24皖交控MTN005（两新）,25皖交02]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,上海银行股份有限公司</t>
+          <t>招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
@@ -9717,7 +9711,7 @@
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>上海大宁资产经营(集团)有限公司2026年度第二期中期票据</t>
+          <t>安徽省交通控股集团有限公司2026年度第八期中期票据</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
@@ -9727,7 +9721,7 @@
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
+          <t>2056-09-08</t>
         </is>
       </c>
       <c r="AK41" s="3"/>
@@ -9753,7 +9747,7 @@
       </c>
       <c r="AP41" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ41" s="3" t="inlineStr">
@@ -9763,22 +9757,22 @@
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU41" s="3" t="inlineStr">
         <is>
-          <t>2029-09-08</t>
+          <t/>
         </is>
       </c>
       <c r="AV41" s="3" t="inlineStr">
@@ -9788,7 +9782,7 @@
       </c>
       <c r="AW41" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX41" s="3" t="inlineStr">
@@ -9801,12 +9795,14 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AZ41" s="3"/>
+      <c r="AZ41" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26皖交控MTN008</t>
+          <t>26金融街MTN005</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -9816,64 +9812,64 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>102683542.IB</t>
+          <t>102683543.IB</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>30Y</t>
+          <t>2+2</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>10.0</v>
+        <v>5.3</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>10.0</v>
+        <v>10.3</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.50</t>
+          <t>2.05 ~ 2.75</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>20.75</v>
+        <v>124.19</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>26皖交控MTN005</t>
+          <t>26金融街MTN004A</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>29.84Y</t>
+          <t>1.93Y+2.00Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>2.3621</t>
+          <t>2.5181</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>2.3800/--</t>
+          <t>--/2.4800</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>安徽省交通控股集团有限公司</t>
+          <t>金融街控股股份有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C- 23.53</t>
+          <t>C- 22.43</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9883,7 +9879,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 14:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -9897,17 +9893,17 @@
         </is>
       </c>
       <c r="U42" s="4" t="n">
-        <v>2.98</v>
+        <v>1.8641</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>2.27%~2.37%</t>
+          <t>2.54%~2.64%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
@@ -9915,20 +9911,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z42" s="3"/>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>安徽省</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模10亿元，其中37,000万元拟用于补充营运资金，7,057.5万元拟用于偿还银行借款本金，4,300万元拟用于偿还债券利息，51,642.5万元拟用于偿还银行借款利息。[24皖交控MTN005（两新）,25皖交02]</t>
+          <t>本期中期票据基础发行规模为0亿元，发行规模上限为10.30亿元，拟将募集资金全部用于偿还发行人债务融资工具的本金和利息[23金融街MTN006]</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
@@ -9949,7 +9949,7 @@
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>安徽省交通控股集团有限公司2026年度第八期中期票据</t>
+          <t>金融街控股股份有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
@@ -9959,10 +9959,14 @@
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2056-09-08</t>
-        </is>
-      </c>
-      <c r="AK42" s="3"/>
+          <t>2030-09-08</t>
+        </is>
+      </c>
+      <c r="AK42" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL42" s="3" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -9980,37 +9984,37 @@
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>住宅楼房</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU42" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2028-09-08</t>
         </is>
       </c>
       <c r="AV42" s="3" t="inlineStr">
@@ -10020,7 +10024,7 @@
       </c>
       <c r="AW42" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX42" s="3" t="inlineStr">
@@ -10033,81 +10037,79 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AZ42" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ42" s="3"/>
     </row>
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26金融街MTN005</t>
+          <t>26扬子G5</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>102683543.IB</t>
+          <t>246020.SH</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>2+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>5.3</v>
+        <v>6.0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>10.3</v>
+        <v>6.0</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2.05 ~ 2.75</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>2.55</v>
+        <v>1.64</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>124.19</v>
+        <v>39.47</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>26金融街MTN004A</t>
+          <t>26扬子G3</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>1.93Y+2.00Y</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>2.5181</t>
+          <t>1.6665</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>--/2.4800</t>
+          <t>1.6900/--</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司</t>
+          <t>南京扬子国资投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C- 22.43</t>
+          <t>C 26.21</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -10117,7 +10119,7 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>09-07 14:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -10127,21 +10129,21 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U43" s="4" t="n">
-        <v>1.8641</v>
+        <v>6.97</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>2.54%~2.64%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -10149,30 +10151,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z43" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为0亿元，发行规模上限为10.30亿元，拟将募集资金全部用于偿还发行人债务融资工具的本金和利息[23金融街MTN006]</t>
+          <t>本次债券募集资金用途为偿还到期的公司债券本金[23扬子G3]</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,国开证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
@@ -10182,12 +10180,12 @@
       </c>
       <c r="AG43" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司2026年度第五期中期票据</t>
+          <t>南京扬子国资投资集团有限责任公司2026年面向专业投资者公开发行公司债券(第三期)(品种一)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
@@ -10197,7 +10195,7 @@
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2030-09-08</t>
+          <t>2029-09-09</t>
         </is>
       </c>
       <c r="AK43" s="3" t="inlineStr">
@@ -10207,22 +10205,22 @@
       </c>
       <c r="AL43" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AM43" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
@@ -10232,27 +10230,27 @@
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>住宅楼房</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
         <is>
-          <t>2028-09-08</t>
+          <t/>
         </is>
       </c>
       <c r="AV43" s="3" t="inlineStr">
@@ -10262,7 +10260,7 @@
       </c>
       <c r="AW43" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX43" s="3" t="inlineStr">
@@ -10280,74 +10278,74 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26扬子G5</t>
+          <t>26湖州银行永续债01</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>09-07 19:00</t>
+          <t>09-07 18:00</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>246020.SH</t>
+          <t>242680044.IB</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.90 ~ 2.60</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1.64</v>
+        <v>2.15</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>39.47</v>
+        <v>74.78</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>26扬子G3</t>
+          <t>25湖州银行永续债01</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>4.19Y+N</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.6665</t>
+          <t>2.1548</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>1.6900/--</t>
+          <t>2.1700/--</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>南京扬子国资投资集团有限责任公司</t>
+          <t>湖州银行股份有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>C 26.21</t>
+          <t>C- 23.49</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10357,7 +10355,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -10370,45 +10368,47 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="U44" s="4" t="n">
-        <v>6.97</v>
-      </c>
+      <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.91%~2.01%</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z44" s="3"/>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>浙江省-湖州市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本次债券募集资金用途为偿还到期的公司债券本金[23扬子G3]</t>
+          <t>本期债券将依据适用法律和主管部门的批准用于补充发行人其他一级资本</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,国开证券股份有限公司,广发证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行次级债券</t>
         </is>
       </c>
       <c r="AF44" s="3" t="inlineStr">
@@ -10418,12 +10418,12 @@
       </c>
       <c r="AG44" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>南京扬子国资投资集团有限责任公司2026年面向专业投资者公开发行公司债券(第三期)(品种一)</t>
+          <t>湖州银行股份有限公司2026年无固定期限资本债券</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -10433,64 +10433,60 @@
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK44" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-09</t>
+        </is>
+      </c>
+      <c r="AK44" s="3"/>
       <c r="AL44" s="3" t="inlineStr">
         <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>城商行</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM44" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AO44" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ44" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR44" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS44" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT44" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU44" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV44" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -10498,12 +10494,12 @@
       </c>
       <c r="AW44" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX44" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>其他一级资本工具</t>
         </is>
       </c>
       <c r="AY44" s="3" t="inlineStr">
@@ -10516,74 +10512,74 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26湖州银行永续债01</t>
+          <t>26深铁09</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>242680044.IB</t>
+          <t>520467.SZ</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>4.0</v>
+        <v>7.5</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.60</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>74.78</v>
+        <v>53.47</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>25湖州银行永续债01</t>
+          <t>26深铁07</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>4.19Y+N</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>2.1548</t>
+          <t>1.7764</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>2.1700/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>湖州银行股份有限公司</t>
+          <t>深圳市地铁集团有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C- 23.49</t>
+          <t>C 29.57</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10593,7 +10589,7 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -10606,47 +10602,49 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="U45" s="3"/>
+      <c r="U45" s="4" t="n">
+        <v>3.7</v>
+      </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1.91%~2.01%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>浙江省-湖州市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期债券将依据适用法律和主管部门的批准用于补充发行人其他一级资本</t>
+          <t>本期债券发行规模不超过15亿元(含)，扣除发行费用后拟用于偿还公司有息债务[23深铁13,25深圳地铁MTN003A,25深圳地铁MTN003B,24深圳地铁MTN007A,24深圳地铁MTN007B]</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="inlineStr">
         <is>
-          <t>商业银行次级债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF45" s="3" t="inlineStr">
@@ -10656,33 +10654,37 @@
       </c>
       <c r="AG45" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>湖州银行股份有限公司2026年无固定期限资本债券</t>
+          <t>深圳市地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种一)</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
-        </is>
-      </c>
-      <c r="AK45" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK45" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AN45" s="3" t="inlineStr">
@@ -10692,32 +10694,32 @@
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
@@ -10732,12 +10734,12 @@
       </c>
       <c r="AW45" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX45" s="3" t="inlineStr">
         <is>
-          <t>其他一级资本工具</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY45" s="3" t="inlineStr">
@@ -10750,7 +10752,7 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26哈萨克斯坦债02B(BC)</t>
+          <t>26哈萨克斯坦债02A(BC)</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -10760,30 +10762,30 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>292680030.IB</t>
+          <t>292680029.IB</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>16.0</v>
+        <v>50.0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>16.0</v>
+        <v>50.0</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.30</t>
+          <t>1.60 ~ 2.10</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>54.78</v>
+        <v>57.47</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -10807,11 +10809,7 @@
           <t>哈萨克斯坦共和国</t>
         </is>
       </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t>A 80.00</t>
-        </is>
-      </c>
+      <c r="P46" s="3"/>
       <c r="Q46" s="3" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -10833,7 +10831,7 @@
         </is>
       </c>
       <c r="U46" s="4" t="n">
-        <v>2.24</v>
+        <v>2.082</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
@@ -10877,7 +10875,7 @@
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>哈萨克斯坦共和国2026年度第二期人民币债券(债券通)(品种二)</t>
+          <t>哈萨克斯坦共和国2026年度第二期人民币债券(债券通)(品种一)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
@@ -10887,10 +10885,14 @@
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
-        </is>
-      </c>
-      <c r="AK46" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK46" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL46" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
@@ -10946,7 +10948,7 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26哈萨克斯坦债02A(BC)</t>
+          <t>26哈萨克斯坦债02B(BC)</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10956,30 +10958,30 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>292680029.IB</t>
+          <t>292680030.IB</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>50.0</v>
+        <v>16.0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>50.0</v>
+        <v>16.0</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
+          <t>1.80 ~ 2.30</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>57.47</v>
+        <v>54.78</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -11003,11 +11005,7 @@
           <t>哈萨克斯坦共和国</t>
         </is>
       </c>
-      <c r="P47" s="3" t="inlineStr">
-        <is>
-          <t>A 80.00</t>
-        </is>
-      </c>
+      <c r="P47" s="3"/>
       <c r="Q47" s="3" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -11029,7 +11027,7 @@
         </is>
       </c>
       <c r="U47" s="4" t="n">
-        <v>2.08</v>
+        <v>2.2375</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
@@ -11073,7 +11071,7 @@
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>哈萨克斯坦共和国2026年度第二期人民币债券(债券通)(品种一)</t>
+          <t>哈萨克斯坦共和国2026年度第二期人民币债券(债券通)(品种二)</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
@@ -11083,14 +11081,10 @@
       </c>
       <c r="AJ47" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK47" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-09</t>
+        </is>
+      </c>
+      <c r="AK47" s="3"/>
       <c r="AL47" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
@@ -11146,17 +11140,17 @@
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26深铁09</t>
+          <t>26义乌农商三农债01</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>09-07 19:00</t>
+          <t>09-07 18:00</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>520467.SZ</t>
+          <t>2621001.IB</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -11165,40 +11159,40 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>7.5</v>
+        <v>4.0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>53.47</v>
+        <v>35.47</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>26深铁07</t>
+          <t>24义乌农商三农债02</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>1.23Y</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1.7764</t>
+          <t>1.5344</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
@@ -11208,12 +11202,12 @@
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>深圳市地铁集团有限公司</t>
+          <t>浙江义乌农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>C 29.57</t>
+          <t>D 4.00</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -11223,7 +11217,7 @@
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
@@ -11236,69 +11230,67 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="U48" s="4" t="n">
-        <v>3.7</v>
-      </c>
+      <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X48" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y48" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z48" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>浙江省-金华市</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过15亿元(含)，扣除发行费用后拟用于偿还公司有息债务[23深铁13,25深圳地铁MTN003A,25深圳地铁MTN003B,24深圳地铁MTN007A,24深圳地铁MTN007B]</t>
+          <t>本期债券募集资金将依据适用法律和监管部门的批准用于发放涉农贷款</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD48" s="3"/>
       <c r="AE48" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF48" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG48" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>深圳市地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种一)</t>
+          <t>2026年浙江义乌农村商业银行股份有限公司"三农"专项金融债券(品种一)</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ48" s="3" t="inlineStr">
@@ -11313,12 +11305,12 @@
       </c>
       <c r="AL48" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AM48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AN48" s="3" t="inlineStr">
@@ -11328,32 +11320,32 @@
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP48" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ48" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT48" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU48" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-07.xlsx
+++ b/data/credit_bond_all_2026-09-07.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-10" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-11" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       <c r="AK4" s="3"/>
       <c r="AL4" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AM4" s="3" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C- 10.23</t>
+          <t>C- 10.51</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1311,7 +1311,7 @@
       <c r="AK5" s="3"/>
       <c r="AL5" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AM5" s="3" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>B- 45.70</t>
+          <t>B- 44.62</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>B- 36.67</t>
+          <t>C- 20.00</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C 27.76</t>
+          <t>C+ 30.24</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>B- 42.50</t>
+          <t>B- 50.00</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="AL14" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AM14" s="3" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>B- 44.28</t>
+          <t>B- 47.74</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="AL15" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AM15" s="3" t="inlineStr">
@@ -3883,7 +3883,7 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AM16" s="3" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C- 22.43</t>
+          <t>C- 24.87</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4575,7 +4575,7 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AM19" s="3" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>B- 36.34</t>
+          <t>B- 36.39</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>B- 35.50</t>
+          <t>B- 36.40</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C- 18.89</t>
+          <t>C- 20.28</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.44</t>
+          <t>C+ 34.71</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>B- 41.18</t>
+          <t>B- 41.88</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C- 13.69</t>
+          <t>C- 15.40</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>B- 40.31</t>
+          <t>B- 41.18</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6447,7 +6447,7 @@
       <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
@@ -6520,74 +6520,74 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26沈阳地铁MTN004</t>
+          <t>26深铁10</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>09-08 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>102683539.IB</t>
+          <t>520468.SZ</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5+2</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>15.0</v>
+        <v>7.5</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.70</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.29</v>
+        <v>1.99</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>88.28</v>
+        <v>46.72</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>24沈阳地铁MTN006B</t>
+          <t>26深铁08</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>4.95Y+N</t>
+          <t>4.97Y+2.00Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>2.3096</t>
+          <t>2.0276</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>2.6000/2.2000</t>
+          <t>2.1000/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>沈阳地铁集团有限公司</t>
+          <t>深圳市地铁集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.51</t>
+          <t>C+ 30.43</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -6611,19 +6611,17 @@
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>1.16</v>
-      </c>
+        <v>2.68</v>
+      </c>
+      <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>2.22%~2.32%</t>
+          <t>1.98%~2.08%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -6638,23 +6636,23 @@
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>辽宁省-沈阳市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为人民币0亿元,发行金额上限为人民币15亿元,本次债券募集资金拟用于偿还公司有息债务。[24沈阳地铁MTN007,25沈阳地铁MTN004]</t>
+          <t>本期债券发行规模不超过15亿元(含)，扣除发行费用后拟用于偿还公司有息债务[23深铁13,25深圳地铁MTN003A,25深圳地铁MTN003B,24深圳地铁MTN007A,24深圳地铁MTN007B]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>中国邮政储蓄银行股份有限公司,光大证券股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
@@ -6664,33 +6662,33 @@
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>沈阳地铁集团有限公司2026年度第四期中期票据</t>
+          <t>深圳市地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种二)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
+          <t>2033-09-09</t>
         </is>
       </c>
       <c r="AK28" s="3"/>
       <c r="AL28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AN28" s="3" t="inlineStr">
@@ -6700,12 +6698,12 @@
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
@@ -6725,12 +6723,12 @@
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-09</t>
         </is>
       </c>
       <c r="AV28" s="3" t="inlineStr">
@@ -6740,7 +6738,7 @@
       </c>
       <c r="AW28" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX28" s="3" t="inlineStr">
@@ -6750,7 +6748,7 @@
       </c>
       <c r="AY28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AZ28" s="3"/>
@@ -6758,7 +6756,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26深铁10</t>
+          <t>26张高02</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6768,19 +6766,19 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>520468.SZ</t>
+          <t>283818.SH</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>5+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>7.5</v>
+        <v>6.0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -6788,44 +6786,44 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>46.72</v>
+        <v>49.78</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26深铁08</t>
+          <t>26张高01</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>4.97Y+2.00Y</t>
+          <t>4.59Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>2.0276</t>
+          <t>1.8746</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>2.1000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>深圳市地铁集团有限公司</t>
+          <t>张家港市高铁投资发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C 29.57</t>
+          <t>B- 40.61</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6835,7 +6833,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6849,42 +6847,38 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.68</v>
+        <v>3.43</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.98%~2.08%</t>
+          <t>1.96%~2.06%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z29" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过15亿元(含)，扣除发行费用后拟用于偿还公司有息债务[23深铁13,25深圳地铁MTN003A,25深圳地铁MTN003B,24深圳地铁MTN007A,24深圳地铁MTN007B]</t>
+          <t>本期债券发行规模为不超过6亿元,募集资金在扣除发行费用后,拟用于偿还公司债券本金[23张高02]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
@@ -6900,12 +6894,12 @@
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>深圳市地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种二)</t>
+          <t>张家港市高铁投资发展(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6915,7 +6909,7 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2033-09-09</t>
+          <t>2031-09-09</t>
         </is>
       </c>
       <c r="AK29" s="3"/>
@@ -6926,7 +6920,7 @@
       </c>
       <c r="AM29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN29" s="3" t="inlineStr">
@@ -6936,12 +6930,12 @@
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
@@ -6951,22 +6945,22 @@
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV29" s="3" t="inlineStr">
@@ -6976,7 +6970,7 @@
       </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX29" s="3" t="inlineStr">
@@ -6994,59 +6988,59 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26张高02</t>
+          <t>26义乌农商三农债02</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>09-07 19:00</t>
+          <t>09-07 18:00</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>283818.SH</t>
+          <t>2621002.IB</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>49.78</v>
+        <v>40.47</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26张高01</t>
+          <t>24义乌农商三农债02</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>4.59Y</t>
+          <t>1.23Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.8746</t>
+          <t>1.5344</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -7056,12 +7050,12 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>张家港市高铁投资发展(集团)有限公司</t>
+          <t>浙江义乌农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>B- 40.61</t>
+          <t>C- 11.50</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7071,7 +7065,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -7084,18 +7078,16 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="U30" s="4" t="n">
-        <v>3.43</v>
-      </c>
+      <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.96%~2.06%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -7103,62 +7095,70 @@
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z30" s="3"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>浙江省-金华市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过6亿元,募集资金在扣除发行费用后,拟用于偿还公司债券本金[23张高02]</t>
+          <t>本期债券募集资金将依据适用法律和监管部门的批准用于发放涉农贷款</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>张家港市高铁投资发展(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>2026年浙江义乌农村商业银行股份有限公司"三农"专项金融债券(品种二)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
-        </is>
-      </c>
-      <c r="AK30" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK30" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL30" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AM30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AN30" s="3" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
@@ -7178,22 +7178,22 @@
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7226,17 +7226,17 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26义乌农商三农债02</t>
+          <t>26高城01</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>2621002.IB</t>
+          <t>520464.SZ</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -7245,40 +7245,40 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>40.47</v>
+        <v>48.47</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>24义乌农商三农债02</t>
+          <t>24合高01</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>1.23Y</t>
+          <t>300D+2.00Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.5344</t>
+          <t>1.5586</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>浙江义乌农村商业银行股份有限公司</t>
+          <t>合肥高新城市发展集团有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>D 4.00</t>
+          <t>C- 17.65</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -7313,10 +7313,12 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U31" s="3"/>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U31" s="4" t="n">
+        <v>3.94</v>
+      </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
@@ -7325,7 +7327,7 @@
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -7333,80 +7335,76 @@
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z31" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+      <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
+          <t>安徽省-合肥市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金将依据适用法律和监管部门的批准用于发放涉农贷款</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司有息债务[23合高01]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>2026年浙江义乌农村商业银行股份有限公司"三农"专项金融债券(品种二)</t>
+          <t>合肥高新城市发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
+          <t>2029-09-08</t>
         </is>
       </c>
       <c r="AK31" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
@@ -7416,22 +7414,22 @@
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>农商行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7464,72 +7462,74 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26光明建发02</t>
+          <t>26苏农垦SCP018</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>09-07 19:00</t>
+          <t>09-07 18:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>520463.SZ</t>
+          <t>012682213.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>0.24Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F32" s="3"/>
+      <c r="F32" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>20.78</v>
+        <v>18.09</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26光明建发01</t>
+          <t>26苏农垦SCP017</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2.42Y+2.00Y</t>
+          <t>73D</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.7626</t>
+          <t>1.4803</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/1.7000</t>
+          <t>1.5100/1.3992</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>深圳市光明区建设发展集团有限公司</t>
+          <t>江苏省农垦集团有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>S+ 100.00</t>
+          <t>C 28.53</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -7549,50 +7549,50 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U32" s="3"/>
-      <c r="V32" s="3"/>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U32" s="4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>1.08</v>
+      </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过5亿元(含),发行人拟使用不少于4.7815亿元用于偿还公司有息债务,剩余部分用于补充公司本部及子公司生产经营所需流动资金</t>
+          <t>发行人本次拟发行5亿元超短期融资券，用于偿还发行人存量负债。</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司</t>
+          <t>中国建设银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
@@ -7602,75 +7602,75 @@
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>深圳市光明区建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>江苏省农垦集团有限公司2026年度第十八期超短期融资券</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr">
+        <is>
+          <t>农林牧渔</t>
+        </is>
+      </c>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>种植业</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AO32" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ32" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR32" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS32" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>房地产开发</t>
-        </is>
-      </c>
-      <c r="AU32" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-10</t>
-        </is>
-      </c>
       <c r="AV32" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX32" s="3" t="inlineStr">
@@ -7696,74 +7696,74 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26高城01</t>
+          <t>26江苏广电SCP008</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>09-07 19:00</t>
+          <t>09-07 18:00</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>520464.SZ</t>
+          <t>012682214.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.33Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.35 ~ 1.48</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>48.47</v>
+        <v>26.13</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>24合高01</t>
+          <t>24苏广K1</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>300D+2.00Y</t>
+          <t>140D</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.5586</t>
+          <t>1.4946</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4700</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>合肥高新城市发展集团有限公司</t>
+          <t>江苏省广电有线信息网络股份有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C- 17.65</t>
+          <t>C+ 33.11</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -7787,44 +7787,46 @@
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="V33" s="3"/>
+        <v>1.1833</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>1.44</v>
+      </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.46%~1.50%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>安徽省-合肥市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司有息债务[23合高01]</t>
+          <t>本期发行6亿元超短期融资券，全部用于偿还有息债务[26江苏广电SCP005]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>南京银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
@@ -7834,32 +7836,28 @@
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>合肥高新城市发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>江苏省广电有线信息网络股份有限公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2029-09-08</t>
-        </is>
-      </c>
-      <c r="AK33" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-01-08</t>
+        </is>
+      </c>
+      <c r="AK33" s="3"/>
       <c r="AL33" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM33" s="3" t="inlineStr">
@@ -7879,27 +7877,27 @@
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>传媒</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>广电</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>广电</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7932,7 +7930,7 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP018</t>
+          <t>26厦门产投MTN003(科创债)</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7942,12 +7940,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>012682213.IB</t>
+          <t>102683466.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>0.24Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
@@ -7958,48 +7956,48 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.38</v>
+        <v>1.87</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>18.09</v>
+        <v>46.78</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP017</t>
+          <t>26厦门产投MTN002(科创债)</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>73D</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.4803</t>
+          <t>1.8952</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>1.5100/1.3992</t>
+          <t>1.8900/1.8700</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司</t>
+          <t>厦门市产业投资有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C 26.94</t>
+          <t>A- 63.24</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -8009,7 +8007,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 11:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -8023,19 +8021,19 @@
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>2.66</v>
+        <v>4.18</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -8043,26 +8041,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z34" s="3"/>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>发行人本次拟发行5亿元超短期融资券，用于偿还发行人存量负债。</t>
+          <t>本期科技创新债券发行金额为5亿元，本期发行的募集资金扣除承销费后，拟全部用于科技创新领域股权投资以及置换发行人本期科技创新债券发行之日起一年以内科技创新领域股权投资；本期债券募集资金中5亿元拟用于对中创新航科技（福建）有限公司的科技创新领域股权投资以及置换一年之内的自有资金投入。</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,华夏银行股份有限公司</t>
+          <t>兴业银行股份有限公司,厦门银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -8077,7 +8079,7 @@
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司2026年度第十八期超短期融资券</t>
+          <t>厦门市产业投资有限公司2026年度第三期科技创新债券</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -8087,7 +8089,7 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2031-09-08</t>
         </is>
       </c>
       <c r="AK34" s="3"/>
@@ -8108,32 +8110,28 @@
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP34" s="3"/>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>种植业</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -8166,7 +8164,7 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26江苏广电SCP008</t>
+          <t>26川高速SCP001</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8176,64 +8174,64 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>012682214.IB</t>
+          <t>012682211.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>0.33Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.48</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>26.13</v>
+        <v>19.09</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>24苏广K1</t>
+          <t>21川高速MTN008</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>140D</t>
+          <t>80D</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.4946</t>
+          <t>1.4955</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>--/1.4700</t>
+          <t>1.5000/--</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>江苏省广电有线信息网络股份有限公司</t>
+          <t>四川高速公路建设开发集团有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C 25.70</t>
+          <t>C- 20.41</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8257,10 +8255,10 @@
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>1.1833</v>
+        <v>3.42</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>1.44</v>
+        <v>2.0</v>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
@@ -8269,7 +8267,7 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.46%~1.50%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -8280,17 +8278,17 @@
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期发行6亿元超短期融资券，全部用于偿还有息债务[26江苏广电SCP005]</t>
+          <t>发行人本期债务融资工具拟募集资金10亿元,拟全部用于偿付到期债务融资工具【21川高速MTN007】</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
@@ -8311,7 +8309,7 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>江苏省广电有线信息网络股份有限公司2026年度第八期超短期融资券</t>
+          <t>四川高速公路建设开发集团有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8321,7 +8319,7 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="AK35" s="3"/>
@@ -8332,7 +8330,7 @@
       </c>
       <c r="AM35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AN35" s="3" t="inlineStr">
@@ -8342,32 +8340,32 @@
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>传媒</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>广电</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>广电</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -8400,22 +8398,22 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26厦门产投MTN003(科创债)</t>
+          <t>26核保02</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>102683466.IB</t>
+          <t>246006.SH</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
@@ -8426,48 +8424,48 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>46.78</v>
+        <v>49.19</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26厦门产投MTN002(科创债)</t>
+          <t>26核保01</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>1.36Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.8952</t>
+          <t>1.9000</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>1.8900/1.8700</t>
+          <t>1.9900/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>厦门市产业投资有限公司</t>
+          <t>中核商业保理有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>B+ 58.93</t>
+          <t>D+ 5.09</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8477,7 +8475,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>09-07 11:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8491,65 +8489,59 @@
         </is>
       </c>
       <c r="U36" s="4" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>1.2</v>
-      </c>
+        <v>5.44</v>
+      </c>
+      <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z36" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债券发行金额为5亿元，本期发行的募集资金扣除承销费后，拟全部用于科技创新领域股权投资以及置换发行人本期科技创新债券发行之日起一年以内科技创新领域股权投资；本期债券募集资金中5亿元拟用于对中创新航科技（福建）有限公司的科技创新领域股权投资以及置换一年之内的自有资金投入。</t>
+          <t>本期债券募集资金5亿元拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,厦门银行股份有限公司</t>
+          <t>招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>厦门市产业投资有限公司2026年度第三期科技创新债券</t>
+          <t>中核商业保理有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8559,18 +8551,18 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
+          <t>2028-09-08</t>
         </is>
       </c>
       <c r="AK36" s="3"/>
       <c r="AL36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AM36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AN36" s="3" t="inlineStr">
@@ -8591,12 +8583,12 @@
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>保理</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>保理</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
@@ -8634,7 +8626,7 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26川高速SCP001</t>
+          <t>26闽投MTN007</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8644,12 +8636,12 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>012682211.IB</t>
+          <t>102683545.IB</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
@@ -8660,48 +8652,48 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>19.09</v>
+        <v>31.47</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>21川高速MTN008</t>
+          <t>19闽投MTN006</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>80D</t>
+          <t>3.01Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.4955</t>
+          <t>1.6653</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>1.5000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>四川高速公路建设开发集团有限公司</t>
+          <t>福建省投资开发集团有限责任公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C- 18.86</t>
+          <t>C- 24.83</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8711,7 +8703,7 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 10:00</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
@@ -8725,19 +8717,19 @@
         </is>
       </c>
       <c r="U37" s="4" t="n">
-        <v>3.42</v>
+        <v>4.14</v>
       </c>
       <c r="V37" s="4" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -8748,23 +8740,23 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具拟募集资金10亿元,拟全部用于偿付到期债务融资工具【21川高速MTN007】</t>
+          <t>发行人本次发行规模为人民币10.00亿元，均用于偿还发行人有息债务及权属单位补充经营性现金流。</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
@@ -8779,7 +8771,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>四川高速公路建设开发集团有限公司2026年度第一期超短期融资券</t>
+          <t>福建省投资开发集团有限责任公司2026年度第七期中期票据</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8789,10 +8781,14 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
-        </is>
-      </c>
-      <c r="AK37" s="3"/>
+          <t>2029-09-08</t>
+        </is>
+      </c>
+      <c r="AK37" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL37" s="3" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -8800,7 +8796,7 @@
       </c>
       <c r="AM37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN37" s="3" t="inlineStr">
@@ -8810,32 +8806,32 @@
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>燃气</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8868,74 +8864,74 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26核保02</t>
+          <t>26大宁MTN002</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>09-07 19:00</t>
+          <t>09-07 18:00</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>246006.SH</t>
+          <t>102683540.IB</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>5.0</v>
+        <v>13.35</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>5.0</v>
+        <v>13.35</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>49.19</v>
+        <v>28.78</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>26核保01</t>
+          <t>24大宁MTN001</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>1.36Y</t>
+          <t>2.98Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.9000</t>
+          <t>1.6973</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>1.9900/--</t>
+          <t>1.7200/--</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>中核商业保理有限公司</t>
+          <t>上海大宁资产经营(集团)有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>D+ 5.09</t>
+          <t>C- 19.28</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8945,7 +8941,7 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>09-07 15:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -8959,17 +8955,19 @@
         </is>
       </c>
       <c r="U38" s="4" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="V38" s="3"/>
+        <v>4.2944</v>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>1.14</v>
+      </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
@@ -8980,38 +8978,38 @@
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>上海市-静安区</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金5亿元拟用于偿还有息债务</t>
+          <t>发行人本次中期票据发行规模人民币13.35亿元,全部用于偿还发行人到期债务融资工具本金[23大宁MTN001]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>招商证券股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,上海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>中核商业保理有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>上海大宁资产经营(集团)有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -9021,18 +9019,18 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2028-09-08</t>
+          <t>2031-09-08</t>
         </is>
       </c>
       <c r="AK38" s="3"/>
       <c r="AL38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN38" s="3" t="inlineStr">
@@ -9042,33 +9040,37 @@
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP38" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>保理</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>保理</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-08</t>
         </is>
       </c>
       <c r="AV38" s="3" t="inlineStr">
@@ -9078,7 +9080,7 @@
       </c>
       <c r="AW38" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX38" s="3" t="inlineStr">
@@ -9096,7 +9098,7 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26闽投MTN007</t>
+          <t>26皖交控MTN008</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -9106,12 +9108,12 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>102683545.IB</t>
+          <t>102683542.IB</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>30Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
@@ -9122,48 +9124,48 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>2.00 ~ 2.50</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1.56</v>
+        <v>2.34</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>31.47</v>
+        <v>20.75</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>19闽投MTN006</t>
+          <t>26皖交控MTN005</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>3.01Y</t>
+          <t>29.84Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.6653</t>
+          <t>2.3621</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.3800/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>福建省投资开发集团有限责任公司</t>
+          <t>安徽省交通控股集团有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C 25.10</t>
+          <t>C- 23.66</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9173,7 +9175,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>09-07 10:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -9187,11 +9189,9 @@
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="V39" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>2.98</v>
+      </c>
+      <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -9199,7 +9199,7 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>2.27%~2.37%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
@@ -9210,17 +9210,17 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>安徽省</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行规模为人民币10.00亿元，均用于偿还发行人有息债务及权属单位补充经营性现金流。</t>
+          <t>本期债券发行规模10亿元，其中37,000万元拟用于补充营运资金，7,057.5万元拟用于偿还银行借款本金，4,300万元拟用于偿还债券利息，51,642.5万元拟用于偿还银行借款利息。[24皖交控MTN005（两新）,25皖交02]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>福建省投资开发集团有限责任公司2026年度第七期中期票据</t>
+          <t>安徽省交通控股集团有限公司2026年度第八期中期票据</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -9251,14 +9251,10 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2029-09-08</t>
-        </is>
-      </c>
-      <c r="AK39" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2056-09-08</t>
+        </is>
+      </c>
+      <c r="AK39" s="3"/>
       <c r="AL39" s="3" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -9276,32 +9272,32 @@
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -9329,12 +9325,14 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AZ39" s="3"/>
+      <c r="AZ39" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26大宁MTN002</t>
+          <t>26金融街MTN005</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -9344,64 +9342,64 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>102683540.IB</t>
+          <t>102683543.IB</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>2+2</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>13.35</v>
+        <v>5.3</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>13.35</v>
+        <v>10.3</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>2.05 ~ 2.75</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.69</v>
+        <v>2.55</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>28.78</v>
+        <v>124.19</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>24大宁MTN001</t>
+          <t>26金融街MTN004A</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>2.98Y</t>
+          <t>1.93Y+2.00Y</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.6973</t>
+          <t>2.5181</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>1.7200/--</t>
+          <t>--/2.4800</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>上海大宁资产经营(集团)有限公司</t>
+          <t>金融街控股股份有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C- 14.82</t>
+          <t>C- 24.87</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9411,7 +9409,7 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 14:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
@@ -9425,40 +9423,42 @@
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>4.2944</v>
-      </c>
-      <c r="V40" s="4" t="n">
-        <v>1.14</v>
-      </c>
+        <v>1.8641</v>
+      </c>
+      <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>2.54%~2.64%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z40" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>上海市-静安区</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据发行规模人民币13.35亿元,全部用于偿还发行人到期债务融资工具本金[23大宁MTN001]</t>
+          <t>本期中期票据基础发行规模为0亿元，发行规模上限为10.30亿元，拟将募集资金全部用于偿还发行人债务融资工具的本金和利息[23金融街MTN006]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,上海银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>上海大宁资产经营(集团)有限公司2026年度第二期中期票据</t>
+          <t>金融街控股股份有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -9489,10 +9489,14 @@
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
-        </is>
-      </c>
-      <c r="AK40" s="3"/>
+          <t>2030-09-08</t>
+        </is>
+      </c>
+      <c r="AK40" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL40" s="3" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -9510,37 +9514,37 @@
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>住宅楼房</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
         <is>
-          <t>2029-09-08</t>
+          <t>2028-09-08</t>
         </is>
       </c>
       <c r="AV40" s="3" t="inlineStr">
@@ -9568,74 +9572,74 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26皖交控MTN008</t>
+          <t>26扬子G5</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>102683542.IB</t>
+          <t>246020.SH</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>30Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.50</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>2.34</v>
+        <v>1.64</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>20.75</v>
+        <v>39.47</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>26皖交控MTN005</t>
+          <t>26扬子G3</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>29.84Y</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>2.3621</t>
+          <t>1.6665</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>2.3800/--</t>
+          <t>1.6900/--</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>安徽省交通控股集团有限公司</t>
+          <t>南京扬子国资投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>C- 23.53</t>
+          <t>C 26.21</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9645,7 +9649,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 16:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -9655,21 +9659,21 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U41" s="4" t="n">
-        <v>2.98</v>
+        <v>6.97</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>2.27%~2.37%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -9680,23 +9684,23 @@
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>安徽省</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模10亿元，其中37,000万元拟用于补充营运资金，7,057.5万元拟用于偿还银行借款本金，4,300万元拟用于偿还债券利息，51,642.5万元拟用于偿还银行借款利息。[24皖交控MTN005（两新）,25皖交02]</t>
+          <t>本次债券募集资金用途为偿还到期的公司债券本金[23扬子G3]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,国开证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF41" s="3" t="inlineStr">
@@ -9706,12 +9710,12 @@
       </c>
       <c r="AG41" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>安徽省交通控股集团有限公司2026年度第八期中期票据</t>
+          <t>南京扬子国资投资集团有限责任公司2026年面向专业投资者公开发行公司债券(第三期)(品种一)</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
@@ -9721,25 +9725,29 @@
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2056-09-08</t>
-        </is>
-      </c>
-      <c r="AK41" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK41" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL41" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AM41" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>类城投</t>
@@ -9747,7 +9755,7 @@
       </c>
       <c r="AP41" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ41" s="3" t="inlineStr">
@@ -9757,17 +9765,17 @@
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU41" s="3" t="inlineStr">
@@ -9795,14 +9803,12 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AZ41" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ41" s="3"/>
     </row>
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26金融街MTN005</t>
+          <t>26湖州银行永续债01</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -9812,64 +9818,64 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>102683543.IB</t>
+          <t>242680044.IB</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>2+2</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>5.3</v>
+        <v>4.0</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>10.3</v>
+        <v>8.0</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2.05 ~ 2.75</t>
+          <t>1.90 ~ 2.60</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>124.19</v>
+        <v>74.78</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>26金融街MTN004A</t>
+          <t>25湖州银行永续债01</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>1.93Y+2.00Y</t>
+          <t>4.19Y+N</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>2.5181</t>
+          <t>2.1548</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>--/2.4800</t>
+          <t>2.1700/--</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司</t>
+          <t>湖州银行股份有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C- 22.43</t>
+          <t>C- 23.88</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9879,7 +9885,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>09-07 14:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -9889,52 +9895,50 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U42" s="4" t="n">
-        <v>1.8641</v>
-      </c>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>2.54%~2.64%</t>
+          <t>1.91%~2.01%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江省-湖州市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为0亿元，发行规模上限为10.30亿元，拟将募集资金全部用于偿还发行人债务融资工具的本金和利息[23金融街MTN006]</t>
+          <t>本期债券将依据适用法律和主管部门的批准用于补充发行人其他一级资本</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行次级债券</t>
         </is>
       </c>
       <c r="AF42" s="3" t="inlineStr">
@@ -9949,7 +9953,7 @@
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司2026年度第五期中期票据</t>
+          <t>湖州银行股份有限公司2026年无固定期限资本债券</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
@@ -9959,62 +9963,58 @@
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2030-09-08</t>
-        </is>
-      </c>
-      <c r="AK42" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-09</t>
+        </is>
+      </c>
+      <c r="AK42" s="3"/>
       <c r="AL42" s="3" t="inlineStr">
         <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AM42" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>住宅楼房</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU42" s="3" t="inlineStr">
         <is>
-          <t>2028-09-08</t>
+          <t/>
         </is>
       </c>
       <c r="AV42" s="3" t="inlineStr">
@@ -10024,12 +10024,12 @@
       </c>
       <c r="AW42" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX42" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>其他一级资本工具</t>
         </is>
       </c>
       <c r="AY42" s="3" t="inlineStr">
@@ -10042,7 +10042,7 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26扬子G5</t>
+          <t>26深铁09</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>246020.SH</t>
+          <t>520467.SZ</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -10061,30 +10061,30 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>6.0</v>
+        <v>7.5</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>39.47</v>
+        <v>53.47</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>26扬子G3</t>
+          <t>26深铁07</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
@@ -10094,22 +10094,22 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.6665</t>
+          <t>1.7764</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>1.6900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>南京扬子国资投资集团有限责任公司</t>
+          <t>深圳市地铁集团有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C 26.21</t>
+          <t>C+ 30.43</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -10133,17 +10133,17 @@
         </is>
       </c>
       <c r="U43" s="4" t="n">
-        <v>6.97</v>
+        <v>3.7</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -10151,20 +10151,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z43" s="3"/>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本次债券募集资金用途为偿还到期的公司债券本金[23扬子G3]</t>
+          <t>本期债券发行规模不超过15亿元(含)，扣除发行费用后拟用于偿还公司有息债务[23深铁13,25深圳地铁MTN003A,25深圳地铁MTN003B,24深圳地铁MTN007A,24深圳地铁MTN007B]</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,国开证券股份有限公司,广发证券股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
@@ -10180,17 +10184,17 @@
       </c>
       <c r="AG43" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>南京扬子国资投资集团有限责任公司2026年面向专业投资者公开发行公司债券(第三期)(品种一)</t>
+          <t>深圳市地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种一)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ43" s="3" t="inlineStr">
@@ -10210,7 +10214,7 @@
       </c>
       <c r="AM43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AN43" s="3" t="inlineStr">
@@ -10225,7 +10229,7 @@
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
@@ -10235,17 +10239,17 @@
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
@@ -10278,7 +10282,7 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26湖州银行永续债01</t>
+          <t>26哈萨克斯坦债02A(BC)</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -10288,64 +10292,56 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>242680044.IB</t>
+          <t>292680029.IB</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>4.0</v>
+        <v>50.0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>8.0</v>
+        <v>50.0</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.60</t>
+          <t>1.60 ~ 2.10</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>74.78</v>
+        <v>57.47</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>25湖州银行永续债01</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>4.19Y+N</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>2.1548</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>2.1700/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>湖州银行股份有限公司</t>
+          <t>哈萨克斯坦共和国</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>C- 23.49</t>
+          <t>A 80.00</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10368,52 +10364,42 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="U44" s="3"/>
+      <c r="U44" s="4" t="n">
+        <v>2.082</v>
+      </c>
       <c r="V44" s="3"/>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t>1.91%~2.01%</t>
-        </is>
-      </c>
+      <c r="W44" s="3"/>
+      <c r="X44" s="3"/>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="AA44" s="3" t="inlineStr">
-        <is>
-          <t>浙江省-湖州市</t>
-        </is>
-      </c>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="AA44" s="3"/>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期债券将依据适用法律和主管部门的批准用于补充发行人其他一级资本</t>
+          <t>本债券发行的募集资金将汇出中国境外并计入哈萨克斯坦共和国国家银行账户,后续将被兑换为哈萨克斯坦坚戈。该等募集资金将用于哈萨克斯坦共和国的国家预算。</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>中国国际金融股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司,中国进出口银行,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="inlineStr">
         <is>
-          <t>商业银行次级债券</t>
+          <t>外国主权政府人民币债券</t>
         </is>
       </c>
       <c r="AF44" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>其他分类</t>
         </is>
       </c>
       <c r="AG44" s="3" t="inlineStr">
@@ -10423,7 +10409,7 @@
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>湖州银行股份有限公司2026年无固定期限资本债券</t>
+          <t>哈萨克斯坦共和国2026年度第二期人民币债券(债券通)(品种一)</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -10433,10 +10419,14 @@
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
-        </is>
-      </c>
-      <c r="AK44" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK44" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL44" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
@@ -10444,7 +10434,7 @@
       </c>
       <c r="AM44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AN44" s="3" t="inlineStr">
@@ -10454,34 +10444,14 @@
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ44" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR44" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS44" s="3" t="inlineStr">
-        <is>
-          <t>城商行</t>
-        </is>
-      </c>
-      <c r="AT44" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="AP44" s="3"/>
+      <c r="AQ44" s="3"/>
+      <c r="AR44" s="3"/>
+      <c r="AS44" s="3"/>
+      <c r="AT44" s="3"/>
       <c r="AU44" s="3" t="inlineStr">
         <is>
           <t/>
@@ -10494,12 +10464,12 @@
       </c>
       <c r="AW44" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX44" s="3" t="inlineStr">
         <is>
-          <t>其他一级资本工具</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY44" s="3" t="inlineStr">
@@ -10512,59 +10482,51 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26深铁09</t>
+          <t>26哈萨克斯坦债02B(BC)</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>09-07 19:00</t>
+          <t>09-07 18:00</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>520467.SZ</t>
+          <t>292680030.IB</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>7.5</v>
+        <v>16.0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.80 ~ 2.30</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>53.47</v>
+        <v>54.78</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>26深铁07</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t>2.97Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.7764</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -10574,12 +10536,12 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>深圳市地铁集团有限公司</t>
+          <t>哈萨克斯坦共和国</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C 29.57</t>
+          <t>A 80.00</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10589,7 +10551,7 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>09-07 16:00</t>
+          <t>09-07 09:00</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -10603,19 +10565,11 @@
         </is>
       </c>
       <c r="U45" s="4" t="n">
-        <v>3.7</v>
+        <v>2.2375</v>
       </c>
       <c r="V45" s="3"/>
-      <c r="W45" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t>1.78%~1.88%</t>
-        </is>
-      </c>
+      <c r="W45" s="3"/>
+      <c r="X45" s="3"/>
       <c r="Y45" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -10626,65 +10580,57 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="AA45" s="3" t="inlineStr">
-        <is>
-          <t>广东省-深圳市</t>
-        </is>
-      </c>
+      <c r="AA45" s="3"/>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过15亿元(含)，扣除发行费用后拟用于偿还公司有息债务[23深铁13,25深圳地铁MTN003A,25深圳地铁MTN003B,24深圳地铁MTN007A,24深圳地铁MTN007B]</t>
+          <t>本债券发行的募集资金将汇出中国境外并计入哈萨克斯坦共和国国家银行账户,后续将被兑换为哈萨克斯坦坚戈。该等募集资金将用于哈萨克斯坦共和国的国家预算。</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司,中国进出口银行,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>外国主权政府人民币债券</t>
         </is>
       </c>
       <c r="AF45" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>其他分类</t>
         </is>
       </c>
       <c r="AG45" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>深圳市地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第五期)(品种一)</t>
+          <t>哈萨克斯坦共和国2026年度第二期人民币债券(债券通)(品种二)</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK45" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-09</t>
+        </is>
+      </c>
+      <c r="AK45" s="3"/>
       <c r="AL45" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AM45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AN45" s="3" t="inlineStr">
@@ -10694,34 +10640,14 @@
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AQ45" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR45" s="3" t="inlineStr">
-        <is>
-          <t>轨道交通</t>
-        </is>
-      </c>
-      <c r="AS45" s="3" t="inlineStr">
-        <is>
-          <t>轨道交通</t>
-        </is>
-      </c>
-      <c r="AT45" s="3" t="inlineStr">
-        <is>
-          <t>公交</t>
-        </is>
-      </c>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="AP45" s="3"/>
+      <c r="AQ45" s="3"/>
+      <c r="AR45" s="3"/>
+      <c r="AS45" s="3"/>
+      <c r="AT45" s="3"/>
       <c r="AU45" s="3" t="inlineStr">
         <is>
           <t/>
@@ -10752,7 +10678,7 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26哈萨克斯坦债02A(BC)</t>
+          <t>26义乌农商三农债01</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -10762,7 +10688,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>292680029.IB</t>
+          <t>2621001.IB</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -10771,101 +10697,123 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>50.0</v>
+        <v>4.0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>50.0</v>
+        <v>4.0</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>57.47</v>
+        <v>35.47</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>24义乌农商三农债02</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>1.23Y</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>1.5344</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>浙江义乌农村商业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>C- 11.50</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>09-07 09:00</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3"/>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>哈萨克斯坦共和国</t>
-        </is>
-      </c>
-      <c r="P46" s="3"/>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t>09-07 09:00</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="U46" s="4" t="n">
-        <v>2.082</v>
-      </c>
+      <c r="U46" s="3"/>
       <c r="V46" s="3"/>
-      <c r="W46" s="3"/>
-      <c r="X46" s="3"/>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>1.58%~1.68%</t>
+        </is>
+      </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="AA46" s="3"/>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>浙江省-金华市</t>
+        </is>
+      </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本债券发行的募集资金将汇出中国境外并计入哈萨克斯坦共和国国家银行账户,后续将被兑换为哈萨克斯坦坚戈。该等募集资金将用于哈萨克斯坦共和国的国家预算。</t>
+          <t>本期债券募集资金将依据适用法律和监管部门的批准用于发放涉农贷款</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司,中国进出口银行,中国银行股份有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD46" s="3"/>
       <c r="AE46" s="3" t="inlineStr">
         <is>
-          <t>外国主权政府人民币债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF46" s="3" t="inlineStr">
         <is>
-          <t>其他分类</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG46" s="3" t="inlineStr">
@@ -10875,7 +10823,7 @@
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>哈萨克斯坦共和国2026年度第二期人民币债券(债券通)(品种一)</t>
+          <t>2026年浙江义乌农村商业银行股份有限公司"三农"专项金融债券(品种一)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
@@ -10900,7 +10848,7 @@
       </c>
       <c r="AM46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AN46" s="3" t="inlineStr">
@@ -10910,14 +10858,34 @@
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="AP46" s="3"/>
-      <c r="AQ46" s="3"/>
-      <c r="AR46" s="3"/>
-      <c r="AS46" s="3"/>
-      <c r="AT46" s="3"/>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>农商行</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
       <c r="AU46" s="3" t="inlineStr">
         <is>
           <t/>
@@ -10948,90 +10916,112 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26哈萨克斯坦债02B(BC)</t>
+          <t>26沈阳地铁MTN004</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-08 18:00</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>292680030.IB</t>
+          <t>102683539.IB</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.30</t>
+          <t>2.00 ~ 2.70</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>54.78</v>
+        <v>88.28</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>24沈阳地铁MTN006B</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>4.95Y+N</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>2.3096</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>2.6000/2.2000</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>沈阳地铁集团有限公司</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>B- 35.15</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>09-07 09:00</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
-      <c r="M47" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N47" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>哈萨克斯坦共和国</t>
-        </is>
-      </c>
-      <c r="P47" s="3"/>
-      <c r="Q47" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="R47" s="3" t="inlineStr">
-        <is>
-          <t>09-07 09:00</t>
-        </is>
-      </c>
-      <c r="S47" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
       </c>
       <c r="U47" s="4" t="n">
-        <v>2.2375</v>
-      </c>
-      <c r="V47" s="3"/>
-      <c r="W47" s="3"/>
-      <c r="X47" s="3"/>
+        <v>3.1533</v>
+      </c>
+      <c r="V47" s="4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>2.22%~2.32%</t>
+        </is>
+      </c>
       <c r="Y47" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -11042,26 +11032,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="AA47" s="3"/>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>辽宁省-沈阳市</t>
+        </is>
+      </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本债券发行的募集资金将汇出中国境外并计入哈萨克斯坦共和国国家银行账户,后续将被兑换为哈萨克斯坦坚戈。该等募集资金将用于哈萨克斯坦共和国的国家预算。</t>
+          <t>本期中期票据基础发行规模为人民币0亿元,发行金额上限为人民币15亿元,本次债券募集资金拟用于偿还公司有息债务。[24沈阳地铁MTN007,25沈阳地铁MTN004]</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司,中国进出口银行,中国银行股份有限公司</t>
+          <t>中国邮政储蓄银行股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD47" s="3"/>
       <c r="AE47" s="3" t="inlineStr">
         <is>
-          <t>外国主权政府人民币债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF47" s="3" t="inlineStr">
         <is>
-          <t>其他分类</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG47" s="3" t="inlineStr">
@@ -11071,7 +11065,7 @@
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>哈萨克斯坦共和国2026年度第二期人民币债券(债券通)(品种二)</t>
+          <t>沈阳地铁集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
@@ -11102,14 +11096,34 @@
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="AP47" s="3"/>
-      <c r="AQ47" s="3"/>
-      <c r="AR47" s="3"/>
-      <c r="AS47" s="3"/>
-      <c r="AT47" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>铁路运输</t>
+        </is>
+      </c>
       <c r="AU47" s="3" t="inlineStr">
         <is>
           <t/>
@@ -11122,7 +11136,7 @@
       </c>
       <c r="AW47" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX47" s="3" t="inlineStr">
@@ -11132,7 +11146,7 @@
       </c>
       <c r="AY47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AZ47" s="3"/>
@@ -11140,74 +11154,74 @@
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26义乌农商三农债01</t>
+          <t>26光明建发02</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>2621001.IB</t>
+          <t>520463.SZ</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>35.47</v>
+        <v>20.78</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>24义乌农商三农债02</t>
+          <t>26光明建发01</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>1.23Y</t>
+          <t>2.42Y+2.00Y</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1.5344</t>
+          <t>1.7626</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7000</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>浙江义乌农村商业银行股份有限公司</t>
+          <t>深圳市光明区建设发展集团有限公司</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>D 4.00</t>
+          <t>B- 50.00</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -11217,7 +11231,7 @@
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>09-07 09:00</t>
+          <t>09-07 15:00</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
@@ -11227,19 +11241,21 @@
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U48" s="3"/>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="U48" s="4" t="n">
+        <v>3.92</v>
+      </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X48" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y48" s="3" t="inlineStr">
@@ -11254,73 +11270,69 @@
       </c>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金将依据适用法律和监管部门的批准用于发放涉农贷款</t>
+          <t>本期债券发行规模为不超过5亿元(含),发行人拟使用不少于4.7815亿元用于偿还公司有息债务,剩余部分用于补充公司本部及子公司生产经营所需流动资金</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD48" s="3"/>
       <c r="AE48" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF48" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG48" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>2026年浙江义乌农村商业银行股份有限公司"三农"专项金融债券(品种一)</t>
+          <t>深圳市光明区建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ48" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK48" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-10</t>
+        </is>
+      </c>
+      <c r="AK48" s="3"/>
       <c r="AL48" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AM48" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP48" s="3" t="inlineStr">
@@ -11330,27 +11342,27 @@
       </c>
       <c r="AQ48" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
         <is>
-          <t>农商行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT48" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU48" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-10</t>
         </is>
       </c>
       <c r="AV48" s="3" t="inlineStr">
@@ -11360,7 +11372,7 @@
       </c>
       <c r="AW48" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX48" s="3" t="inlineStr">
